--- a/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
+++ b/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hidden\Desktop\Финальный проект_АКАДЕМИЯ ТОП\Мой_ДИПЛОМНЫЙ_ПРОЕКТ\Свод(чек-лист+тест-кейс+баг-репор+автоматизация)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17676D75-BB91-4DB2-AE49-13DC3DA5AF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06239CCF-345B-4EC8-AE76-80DF2CD26DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13476" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Автотесты (1)" sheetId="9" r:id="rId4"/>
     <sheet name="Нагрузочное" sheetId="7" r:id="rId5"/>
     <sheet name="Диаграмма" sheetId="8" r:id="rId6"/>
+    <sheet name="График" sheetId="13" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1886" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="912">
   <si>
     <t>Название</t>
   </si>
@@ -3134,12 +3135,138 @@
 4. Учетная запись успешно создается в базе данных.Выполняется автоматическая аутентификация, перенаправление (редирект) на главную страницу. Кнопка авторизации в шапке сайта динамически изменяет значение на "Мой ЛК", а атрибут ссылки (href) перенаправляет на /myaccoun 
 </t>
   </si>
+  <si>
+    <t>График тестирования сайта Стейк'S.</t>
+  </si>
+  <si>
+    <t>Цикл тестирования</t>
+  </si>
+  <si>
+    <t>08.июн</t>
+  </si>
+  <si>
+    <t>09.июн</t>
+  </si>
+  <si>
+    <t>10.июн</t>
+  </si>
+  <si>
+    <t>11.июн</t>
+  </si>
+  <si>
+    <t>12.июн</t>
+  </si>
+  <si>
+    <t>13.июн</t>
+  </si>
+  <si>
+    <t>14.июн</t>
+  </si>
+  <si>
+    <t>15.июн</t>
+  </si>
+  <si>
+    <t>16.июн</t>
+  </si>
+  <si>
+    <t>17.июн</t>
+  </si>
+  <si>
+    <t>18.июн</t>
+  </si>
+  <si>
+    <t>19.июн</t>
+  </si>
+  <si>
+    <t>20.июн</t>
+  </si>
+  <si>
+    <t>21.июн</t>
+  </si>
+  <si>
+    <t>22.июн</t>
+  </si>
+  <si>
+    <t>23.июн</t>
+  </si>
+  <si>
+    <t>24.июн</t>
+  </si>
+  <si>
+    <t>25.июн</t>
+  </si>
+  <si>
+    <t>26.июн</t>
+  </si>
+  <si>
+    <t>27.июн</t>
+  </si>
+  <si>
+    <t>28.июн</t>
+  </si>
+  <si>
+    <t>29.июн</t>
+  </si>
+  <si>
+    <t>30.июн</t>
+  </si>
+  <si>
+    <t>01.июл</t>
+  </si>
+  <si>
+    <t>02.июл</t>
+  </si>
+  <si>
+    <t>03.июл</t>
+  </si>
+  <si>
+    <t>04.июл</t>
+  </si>
+  <si>
+    <t>05.июл</t>
+  </si>
+  <si>
+    <t>06.июл</t>
+  </si>
+  <si>
+    <t>07.июл</t>
+  </si>
+  <si>
+    <t>08.июл</t>
+  </si>
+  <si>
+    <t>Анализ объекта тестирования</t>
+  </si>
+  <si>
+    <t>Разработка ручных тестовых артефактов (чек-лист и тест-кейсы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проведение ручного функционального тестирования </t>
+  </si>
+  <si>
+    <t>Проведение кроссбраузерного тестирования (Chrome, Firefox, Yandex)</t>
+  </si>
+  <si>
+    <t>Проектирование и написание сценариев автоматизированного тестирования (Python/Selenium)</t>
+  </si>
+  <si>
+    <t>Проведение автоматизированного контроля качества и генерация Allure-отчёта</t>
+  </si>
+  <si>
+    <t>Разработка и проведение нагрузочного тестирования (Locust)</t>
+  </si>
+  <si>
+    <t>Фиксация дефектов и формирование сводного реестра (Bug Report)</t>
+  </si>
+  <si>
+    <t>Составление итоговой отчётной документации (общий отчёт и специализированные приложения)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="50">
+  <fonts count="56">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3491,8 +3618,53 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2" tint="-0.89999084444715716"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Bahnschrift SemiBold"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3634,6 +3806,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DA9E7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3808,15 +3998,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4092,6 +4283,31 @@
     <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="55" fillId="26" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="16" fontId="55" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="16" fontId="52" fillId="25" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="27" borderId="0" xfId="6" applyFill="1"/>
+    <xf numFmtId="0" fontId="50" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="51" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4143,14 +4359,14 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="19" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4179,53 +4395,17 @@
     <xf numFmtId="0" fontId="49" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="8" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="7">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Гиперссылка 2" xfId="4" xr:uid="{C35FA5AD-7901-4047-B489-5365E26E0049}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{832C7595-0CCC-491D-A2F9-D97347A4E95B}"/>
     <cellStyle name="Обычный 3" xfId="3" xr:uid="{7A05575B-82C1-44C4-99A5-569C6DFAC841}"/>
     <cellStyle name="Обычный 4" xfId="5" xr:uid="{9ED7778B-001D-447F-A76A-EB8655A0F709}"/>
+    <cellStyle name="Обычный 5" xfId="6" xr:uid="{48D8B758-FB9B-4BDB-86DF-F4B6C7945B90}"/>
   </cellStyles>
   <dxfs count="30">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="204"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.34998626667073579"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4383,6 +4563,46 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -4480,13 +4700,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
         </top>
@@ -4507,24 +4720,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <charset val="204"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4537,19 +4737,26 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
         <charset val="204"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF8DA9E7"/>
       <color rgb="FF4DED58"/>
       <color rgb="FFEBECE2"/>
     </mruColors>
@@ -8637,16 +8844,16 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EEAB60B-722A-4E46-A4C8-E889847C739E}" name="Таблица25" displayName="Таблица25" ref="A1:G13" totalsRowShown="0" headerRowDxfId="0" dataDxfId="27" headerRowBorderDxfId="25" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{0EEAB60B-722A-4E46-A4C8-E889847C739E}" name="Таблица25" displayName="Таблица25" ref="A1:G13" totalsRowShown="0" headerRowDxfId="29" dataDxfId="27" headerRowBorderDxfId="28" tableBorderDxfId="26">
   <autoFilter ref="A1:G13" xr:uid="{F1F9DFB6-BA34-495B-9332-A7CA9AF5FAC9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{3CF55EB4-BC80-4463-AB1A-C6425B735889}" name="ID :" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{1936CA3C-AB86-4976-BC9C-63ABE9E66A84}" name="Название:" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{3389728C-9D1F-439F-BBBE-EDEBF006427D}" name="Приоритет:" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{C1F6E954-250E-438D-8737-A33BEA40E474}" name="Шаги:" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{656C87B0-202C-4074-BAC4-BBDDD9520B08}" name="Ожидаемый результат:" dataDxfId="20"/>
-    <tableColumn id="6" xr3:uid="{82E04D58-6ED1-4805-A28F-77A587B413CE}" name="Статус автоматизации:" dataDxfId="19"/>
-    <tableColumn id="7" xr3:uid="{ACBECB74-0C60-4EFB-83C7-9D0F898C8E1D}" name="Статус:" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{3CF55EB4-BC80-4463-AB1A-C6425B735889}" name="ID :" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{1936CA3C-AB86-4976-BC9C-63ABE9E66A84}" name="Название:" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{3389728C-9D1F-439F-BBBE-EDEBF006427D}" name="Приоритет:" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{C1F6E954-250E-438D-8737-A33BEA40E474}" name="Шаги:" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{656C87B0-202C-4074-BAC4-BBDDD9520B08}" name="Ожидаемый результат:" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{82E04D58-6ED1-4805-A28F-77A587B413CE}" name="Статус автоматизации:" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{ACBECB74-0C60-4EFB-83C7-9D0F898C8E1D}" name="Статус:" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8656,7 +8863,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B2B0D802-2D9A-4262-A87C-B0F0B4350892}" name="Таблица8" displayName="Таблица8" ref="B1:F8" totalsRowShown="0">
   <autoFilter ref="B1:F8" xr:uid="{B2B0D802-2D9A-4262-A87C-B0F0B4350892}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{1BCEF6C1-2239-4ADF-AFB4-C378D361689C}" name="Параметры нагрузки (Spawn Rate)" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{1BCEF6C1-2239-4ADF-AFB4-C378D361689C}" name="Параметры нагрузки (Spawn Rate)" dataDxfId="18"/>
     <tableColumn id="2" xr3:uid="{FEDB7BEC-029E-46CE-961D-9FC265203CF5}" name="Ожидаемый результат"/>
     <tableColumn id="3" xr3:uid="{AB0D4716-A568-4BB5-95AA-D5FE5C6D1ADF}" name="Фактический RPS (Пик)"/>
     <tableColumn id="4" xr3:uid="{ED88EA6F-82E4-4105-BCA1-4A50B69126A0}" name="Фактический Response Time"/>
@@ -8670,13 +8877,54 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{598A880D-9872-4DB0-AF55-13EBFDE46EE1}" name="Таблица810" displayName="Таблица810" ref="B1:F8" totalsRowShown="0">
   <autoFilter ref="B1:F8" xr:uid="{598A880D-9872-4DB0-AF55-13EBFDE46EE1}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BCF46B61-1E1D-4847-8F36-435A7359E6CA}" name="Параметры нагрузки (Spawn Rate)" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{BCF46B61-1E1D-4847-8F36-435A7359E6CA}" name="Параметры нагрузки (Spawn Rate)" dataDxfId="17"/>
     <tableColumn id="2" xr3:uid="{AAC977D5-1DAD-411D-9633-05B0F8F3EBA0}" name="Ожидаемый результат"/>
     <tableColumn id="3" xr3:uid="{1C847810-A6FB-49A5-B3CE-2EE861BFD566}" name="Фактический RPS (Пик)"/>
     <tableColumn id="4" xr3:uid="{D6285F3D-793A-438B-9CE0-8AD95BF41182}" name="Фактический Response Time"/>
     <tableColumn id="5" xr3:uid="{DB65A334-66FC-4B05-9DDC-63C3CCE5422A}" name="Статус шага"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{31681926-03A8-47C2-9B65-1E17C74085CB}" name="Таблица18" displayName="Таблица18" ref="A5:AF15" totalsRowShown="0">
+  <autoFilter ref="A5:AF15" xr:uid="{6D74DA59-2737-495C-B100-B640CC6B91E9}"/>
+  <tableColumns count="32">
+    <tableColumn id="1" xr3:uid="{C01E700E-677C-49A2-B1BA-EFFB332F284D}" name="Цикл тестирования"/>
+    <tableColumn id="2" xr3:uid="{41A61633-7C4D-42D9-85C3-1154A3E470D8}" name="08.июн"/>
+    <tableColumn id="3" xr3:uid="{1BEF61AA-EF37-4BFE-A444-0826DB7C70DF}" name="09.июн"/>
+    <tableColumn id="4" xr3:uid="{C5E07A3A-4BC2-4CD8-A56A-0C03FEDF1B38}" name="10.июн"/>
+    <tableColumn id="5" xr3:uid="{7F926F51-5E93-4DC9-B0C6-5C71F8602966}" name="11.июн"/>
+    <tableColumn id="6" xr3:uid="{F9F8049C-0087-4F38-A51C-E546ACBFC449}" name="12.июн"/>
+    <tableColumn id="7" xr3:uid="{D48AF6E5-413C-4645-839C-04DBCAEA0D72}" name="13.июн"/>
+    <tableColumn id="8" xr3:uid="{BE0E0085-AD00-4696-B371-D29FFC5A1193}" name="14.июн"/>
+    <tableColumn id="9" xr3:uid="{E1C8867C-D1B3-420C-91A2-1FE0F31463BA}" name="15.июн"/>
+    <tableColumn id="10" xr3:uid="{ED56D57F-C1B5-4D9F-89D9-A4B1C4D76599}" name="16.июн"/>
+    <tableColumn id="11" xr3:uid="{DD52E2FF-1EFA-4AAF-8B21-537A64B8A5F5}" name="17.июн"/>
+    <tableColumn id="12" xr3:uid="{000875C6-A2CD-45CB-BFFB-5472CACF09AC}" name="18.июн"/>
+    <tableColumn id="13" xr3:uid="{CD8B3D55-E0EE-4101-A1D9-64DE077F18AE}" name="19.июн"/>
+    <tableColumn id="14" xr3:uid="{3995E5C6-D2D9-4D4E-9A35-86FF3B5C26A0}" name="20.июн"/>
+    <tableColumn id="15" xr3:uid="{4DD98329-27B8-485D-AD45-D604DABBD75C}" name="21.июн"/>
+    <tableColumn id="16" xr3:uid="{5E4D1BBB-50F0-486C-9746-59C8EE236B1E}" name="22.июн"/>
+    <tableColumn id="17" xr3:uid="{DC7DA274-0FE3-4B24-BDF7-DA81DE4444CF}" name="23.июн"/>
+    <tableColumn id="18" xr3:uid="{EB898D3B-C2C8-472E-84B7-AB5DBD98E02F}" name="24.июн"/>
+    <tableColumn id="19" xr3:uid="{6A8F80E5-8343-4243-965D-34394FEA7F38}" name="25.июн"/>
+    <tableColumn id="20" xr3:uid="{AEC298C9-D4A6-4216-ADF0-ED02C50751A1}" name="26.июн"/>
+    <tableColumn id="21" xr3:uid="{C7506A1A-B0FC-450E-89FC-DEEACAE6165A}" name="27.июн"/>
+    <tableColumn id="22" xr3:uid="{0B35E546-CC8B-49E2-9D78-A5054D8EFFD8}" name="28.июн"/>
+    <tableColumn id="23" xr3:uid="{23392B43-0BB7-47B2-9F77-4B02499423F6}" name="29.июн"/>
+    <tableColumn id="24" xr3:uid="{F930EE84-79EC-4843-8779-ED4F7727D34B}" name="30.июн"/>
+    <tableColumn id="25" xr3:uid="{E4AD63AB-C92C-4124-81E4-20EE1F3008F6}" name="01.июл"/>
+    <tableColumn id="26" xr3:uid="{80E42272-90FB-41E1-845E-2E3138E91145}" name="02.июл"/>
+    <tableColumn id="27" xr3:uid="{6F990746-0D02-4F6F-BB31-28F4DC147BFB}" name="03.июл"/>
+    <tableColumn id="28" xr3:uid="{9BFB8492-67D3-4857-B244-7A34CAFE941D}" name="04.июл"/>
+    <tableColumn id="29" xr3:uid="{93BE7582-FEBA-45F1-BD51-7722F57B7B73}" name="05.июл"/>
+    <tableColumn id="30" xr3:uid="{3EB80E98-6BD4-45A4-8F54-6BF21BE968EC}" name="06.июл"/>
+    <tableColumn id="31" xr3:uid="{A9441F43-2D13-4EB6-A74C-5AFF438A29F1}" name="07.июл"/>
+    <tableColumn id="32" xr3:uid="{B5FC3DF1-51BB-49F9-B9EE-984491CDF1B2}" name="08.июл"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -8895,27 +9143,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="134" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="120"/>
-      <c r="D1" s="124" t="s">
+      <c r="C1" s="135"/>
+      <c r="D1" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="125"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="126" t="s">
+      <c r="E1" s="140"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="141" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="122" t="s">
+      <c r="H1" s="137" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="55.2">
-      <c r="A2" s="118"/>
+      <c r="A2" s="133"/>
       <c r="B2" s="23" t="s">
         <v>5</v>
       </c>
@@ -8931,11 +9179,11 @@
       <c r="F2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="127"/>
-      <c r="H2" s="123"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="138"/>
     </row>
     <row r="3" spans="1:25" ht="13.8">
-      <c r="A3" s="121" t="s">
+      <c r="A3" s="136" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -8957,7 +9205,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:25" ht="13.8">
-      <c r="A4" s="116"/>
+      <c r="A4" s="131"/>
       <c r="B4" s="13" t="s">
         <v>53</v>
       </c>
@@ -8977,7 +9225,7 @@
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:25" ht="13.8">
-      <c r="A5" s="116"/>
+      <c r="A5" s="131"/>
       <c r="B5" s="13" t="s">
         <v>55</v>
       </c>
@@ -8997,7 +9245,7 @@
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:25" ht="27.6">
-      <c r="A6" s="116"/>
+      <c r="A6" s="131"/>
       <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
@@ -9017,7 +9265,7 @@
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:25" ht="27.6">
-      <c r="A7" s="116"/>
+      <c r="A7" s="131"/>
       <c r="B7" s="13" t="s">
         <v>58</v>
       </c>
@@ -9037,7 +9285,7 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:25" ht="41.4">
-      <c r="A8" s="116"/>
+      <c r="A8" s="131"/>
       <c r="B8" s="27" t="s">
         <v>60</v>
       </c>
@@ -9057,7 +9305,7 @@
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:25" ht="55.2">
-      <c r="A9" s="116"/>
+      <c r="A9" s="131"/>
       <c r="B9" s="13" t="s">
         <v>61</v>
       </c>
@@ -9077,7 +9325,7 @@
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:25" ht="69">
-      <c r="A10" s="116"/>
+      <c r="A10" s="131"/>
       <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
@@ -9097,7 +9345,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:25" ht="55.2">
-      <c r="A11" s="116"/>
+      <c r="A11" s="131"/>
       <c r="B11" s="13" t="s">
         <v>66</v>
       </c>
@@ -9134,7 +9382,7 @@
       <c r="Y11" s="2"/>
     </row>
     <row r="12" spans="1:25" ht="55.2">
-      <c r="A12" s="116"/>
+      <c r="A12" s="131"/>
       <c r="B12" s="13" t="s">
         <v>67</v>
       </c>
@@ -9171,7 +9419,7 @@
       <c r="Y12" s="2"/>
     </row>
     <row r="13" spans="1:25" ht="16.8" customHeight="1">
-      <c r="A13" s="121" t="s">
+      <c r="A13" s="136" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -9210,7 +9458,7 @@
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="1:25" ht="30" customHeight="1">
-      <c r="A14" s="116"/>
+      <c r="A14" s="131"/>
       <c r="B14" s="27" t="s">
         <v>71</v>
       </c>
@@ -9247,7 +9495,7 @@
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="27.6">
-      <c r="A15" s="116"/>
+      <c r="A15" s="131"/>
       <c r="B15" s="27" t="s">
         <v>424</v>
       </c>
@@ -9284,7 +9532,7 @@
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="27.6">
-      <c r="A16" s="116"/>
+      <c r="A16" s="131"/>
       <c r="B16" s="27" t="s">
         <v>426</v>
       </c>
@@ -9304,7 +9552,7 @@
       <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="41.4">
-      <c r="A17" s="116"/>
+      <c r="A17" s="131"/>
       <c r="B17" s="27" t="s">
         <v>73</v>
       </c>
@@ -9324,7 +9572,7 @@
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="41.4">
-      <c r="A18" s="116"/>
+      <c r="A18" s="131"/>
       <c r="B18" s="27" t="s">
         <v>76</v>
       </c>
@@ -9344,7 +9592,7 @@
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="27.6">
-      <c r="A19" s="116"/>
+      <c r="A19" s="131"/>
       <c r="B19" s="27" t="s">
         <v>79</v>
       </c>
@@ -9364,7 +9612,7 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="55.2">
-      <c r="A20" s="116"/>
+      <c r="A20" s="131"/>
       <c r="B20" s="27" t="s">
         <v>81</v>
       </c>
@@ -9384,7 +9632,7 @@
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="92.4">
-      <c r="A21" s="116"/>
+      <c r="A21" s="131"/>
       <c r="B21" s="27" t="s">
         <v>82</v>
       </c>
@@ -9408,7 +9656,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="136" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="27" t="s">
@@ -9430,7 +9678,7 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="27.6">
-      <c r="A23" s="116"/>
+      <c r="A23" s="131"/>
       <c r="B23" s="13" t="s">
         <v>179</v>
       </c>
@@ -9450,7 +9698,7 @@
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="27.6">
-      <c r="A24" s="116"/>
+      <c r="A24" s="131"/>
       <c r="B24" s="13" t="s">
         <v>182</v>
       </c>
@@ -9470,7 +9718,7 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="41.4">
-      <c r="A25" s="116"/>
+      <c r="A25" s="131"/>
       <c r="B25" s="13" t="s">
         <v>180</v>
       </c>
@@ -9494,7 +9742,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="52.8">
-      <c r="A26" s="116"/>
+      <c r="A26" s="131"/>
       <c r="B26" s="13" t="s">
         <v>186</v>
       </c>
@@ -9518,7 +9766,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="41.4">
-      <c r="A27" s="116"/>
+      <c r="A27" s="131"/>
       <c r="B27" s="13" t="s">
         <v>190</v>
       </c>
@@ -9538,7 +9786,7 @@
       <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="41.4">
-      <c r="A28" s="116"/>
+      <c r="A28" s="131"/>
       <c r="B28" s="13" t="s">
         <v>192</v>
       </c>
@@ -9558,7 +9806,7 @@
       <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="27.6">
-      <c r="A29" s="116"/>
+      <c r="A29" s="131"/>
       <c r="B29" s="13" t="s">
         <v>194</v>
       </c>
@@ -9578,7 +9826,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="27.6">
-      <c r="A30" s="116"/>
+      <c r="A30" s="131"/>
       <c r="B30" s="13" t="s">
         <v>196</v>
       </c>
@@ -9598,7 +9846,7 @@
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="27.6">
-      <c r="A31" s="116"/>
+      <c r="A31" s="131"/>
       <c r="B31" s="13" t="s">
         <v>200</v>
       </c>
@@ -9618,7 +9866,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="52.8">
-      <c r="A32" s="116"/>
+      <c r="A32" s="131"/>
       <c r="B32" s="13" t="s">
         <v>280</v>
       </c>
@@ -9642,7 +9890,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="55.2">
-      <c r="A33" s="116"/>
+      <c r="A33" s="131"/>
       <c r="B33" s="13" t="s">
         <v>202</v>
       </c>
@@ -9662,7 +9910,7 @@
       <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="41.4">
-      <c r="A34" s="116"/>
+      <c r="A34" s="131"/>
       <c r="B34" s="13" t="s">
         <v>204</v>
       </c>
@@ -9686,7 +9934,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="27.6">
-      <c r="A35" s="121" t="s">
+      <c r="A35" s="136" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -9708,7 +9956,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="13.8">
-      <c r="A36" s="116"/>
+      <c r="A36" s="131"/>
       <c r="B36" s="13" t="s">
         <v>87</v>
       </c>
@@ -9728,7 +9976,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="79.2">
-      <c r="A37" s="116"/>
+      <c r="A37" s="131"/>
       <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
@@ -9752,7 +10000,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="76.2" customHeight="1">
-      <c r="A38" s="116"/>
+      <c r="A38" s="131"/>
       <c r="B38" s="13" t="s">
         <v>276</v>
       </c>
@@ -9776,7 +10024,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="55.2">
-      <c r="A39" s="116"/>
+      <c r="A39" s="131"/>
       <c r="B39" s="13" t="s">
         <v>95</v>
       </c>
@@ -9796,7 +10044,7 @@
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="69">
-      <c r="A40" s="116"/>
+      <c r="A40" s="131"/>
       <c r="B40" s="13" t="s">
         <v>97</v>
       </c>
@@ -9816,7 +10064,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="79.2">
-      <c r="A41" s="116"/>
+      <c r="A41" s="131"/>
       <c r="B41" s="13" t="s">
         <v>99</v>
       </c>
@@ -9840,7 +10088,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="69">
-      <c r="A42" s="116"/>
+      <c r="A42" s="131"/>
       <c r="B42" s="13" t="s">
         <v>104</v>
       </c>
@@ -9860,7 +10108,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="92.4">
-      <c r="A43" s="116"/>
+      <c r="A43" s="131"/>
       <c r="B43" s="13" t="s">
         <v>105</v>
       </c>
@@ -9884,7 +10132,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="27.6">
-      <c r="A44" s="116"/>
+      <c r="A44" s="131"/>
       <c r="B44" s="13" t="s">
         <v>109</v>
       </c>
@@ -9904,7 +10152,7 @@
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="27.6">
-      <c r="A45" s="116"/>
+      <c r="A45" s="131"/>
       <c r="B45" s="13" t="s">
         <v>112</v>
       </c>
@@ -9924,7 +10172,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="27.6">
-      <c r="A46" s="121" t="s">
+      <c r="A46" s="136" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -9946,7 +10194,7 @@
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="27.6">
-      <c r="A47" s="116"/>
+      <c r="A47" s="131"/>
       <c r="B47" s="13" t="s">
         <v>115</v>
       </c>
@@ -9966,7 +10214,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="66">
-      <c r="A48" s="116"/>
+      <c r="A48" s="131"/>
       <c r="B48" s="13" t="s">
         <v>273</v>
       </c>
@@ -9990,7 +10238,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="27.6">
-      <c r="A49" s="116"/>
+      <c r="A49" s="131"/>
       <c r="B49" s="13" t="s">
         <v>117</v>
       </c>
@@ -10010,7 +10258,7 @@
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" ht="27.6">
-      <c r="A50" s="116"/>
+      <c r="A50" s="131"/>
       <c r="B50" s="13" t="s">
         <v>119</v>
       </c>
@@ -10030,7 +10278,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" ht="27.6">
-      <c r="A51" s="116"/>
+      <c r="A51" s="131"/>
       <c r="B51" s="13" t="s">
         <v>121</v>
       </c>
@@ -10050,7 +10298,7 @@
       <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" ht="27.6">
-      <c r="A52" s="116"/>
+      <c r="A52" s="131"/>
       <c r="B52" s="13" t="s">
         <v>123</v>
       </c>
@@ -10070,7 +10318,7 @@
       <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="27.6">
-      <c r="A53" s="116"/>
+      <c r="A53" s="131"/>
       <c r="B53" s="13" t="s">
         <v>125</v>
       </c>
@@ -10090,7 +10338,7 @@
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" ht="27.6">
-      <c r="A54" s="116"/>
+      <c r="A54" s="131"/>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
@@ -10110,7 +10358,7 @@
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" ht="41.4">
-      <c r="A55" s="116"/>
+      <c r="A55" s="131"/>
       <c r="B55" s="13" t="s">
         <v>129</v>
       </c>
@@ -10130,7 +10378,7 @@
       <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" ht="27.6">
-      <c r="A56" s="116"/>
+      <c r="A56" s="131"/>
       <c r="B56" s="13" t="s">
         <v>130</v>
       </c>
@@ -10150,7 +10398,7 @@
       <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" ht="27.6">
-      <c r="A57" s="116"/>
+      <c r="A57" s="131"/>
       <c r="B57" s="13" t="s">
         <v>132</v>
       </c>
@@ -10170,7 +10418,7 @@
       <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8" ht="27.6">
-      <c r="A58" s="116"/>
+      <c r="A58" s="131"/>
       <c r="B58" s="13" t="s">
         <v>134</v>
       </c>
@@ -10190,7 +10438,7 @@
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8" ht="41.4">
-      <c r="A59" s="116"/>
+      <c r="A59" s="131"/>
       <c r="B59" s="13" t="s">
         <v>136</v>
       </c>
@@ -10210,7 +10458,7 @@
       <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" ht="41.4">
-      <c r="A60" s="116"/>
+      <c r="A60" s="131"/>
       <c r="B60" s="13" t="s">
         <v>137</v>
       </c>
@@ -10230,7 +10478,7 @@
       <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A61" s="116"/>
+      <c r="A61" s="131"/>
       <c r="B61" s="13" t="s">
         <v>138</v>
       </c>
@@ -10250,7 +10498,7 @@
       <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8" ht="27.6">
-      <c r="A62" s="116"/>
+      <c r="A62" s="131"/>
       <c r="B62" s="13" t="s">
         <v>140</v>
       </c>
@@ -10270,7 +10518,7 @@
       <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8" ht="27.6">
-      <c r="A63" s="116"/>
+      <c r="A63" s="131"/>
       <c r="B63" s="13" t="s">
         <v>142</v>
       </c>
@@ -10290,7 +10538,7 @@
       <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8" ht="27.6">
-      <c r="A64" s="116"/>
+      <c r="A64" s="131"/>
       <c r="B64" s="13" t="s">
         <v>144</v>
       </c>
@@ -10310,7 +10558,7 @@
       <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:14" ht="52.2" customHeight="1">
-      <c r="A65" s="116"/>
+      <c r="A65" s="131"/>
       <c r="B65" s="13" t="s">
         <v>282</v>
       </c>
@@ -10334,7 +10582,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="41.4">
-      <c r="A66" s="116"/>
+      <c r="A66" s="131"/>
       <c r="B66" s="13" t="s">
         <v>147</v>
       </c>
@@ -10354,7 +10602,7 @@
       <c r="H66" s="16"/>
     </row>
     <row r="67" spans="1:14" ht="27.6">
-      <c r="A67" s="116"/>
+      <c r="A67" s="131"/>
       <c r="B67" s="13" t="s">
         <v>151</v>
       </c>
@@ -10374,7 +10622,7 @@
       <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:14" ht="27.6">
-      <c r="A68" s="116"/>
+      <c r="A68" s="131"/>
       <c r="B68" s="13" t="s">
         <v>149</v>
       </c>
@@ -10394,7 +10642,7 @@
       <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:14" ht="55.2">
-      <c r="A69" s="121" t="s">
+      <c r="A69" s="136" t="s">
         <v>208</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -10416,7 +10664,7 @@
       <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:14" ht="42" customHeight="1">
-      <c r="A70" s="116"/>
+      <c r="A70" s="131"/>
       <c r="B70" s="21" t="s">
         <v>211</v>
       </c>
@@ -10441,7 +10689,7 @@
       <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A71" s="116"/>
+      <c r="A71" s="131"/>
       <c r="B71" s="21" t="s">
         <v>213</v>
       </c>
@@ -10466,7 +10714,7 @@
       <c r="N71" s="4"/>
     </row>
     <row r="72" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A72" s="116"/>
+      <c r="A72" s="131"/>
       <c r="B72" s="21" t="s">
         <v>215</v>
       </c>
@@ -10491,7 +10739,7 @@
       <c r="N72" s="4"/>
     </row>
     <row r="73" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A73" s="116"/>
+      <c r="A73" s="131"/>
       <c r="B73" s="21" t="s">
         <v>217</v>
       </c>
@@ -10516,7 +10764,7 @@
       <c r="N73" s="4"/>
     </row>
     <row r="74" spans="1:14" ht="63.6" customHeight="1">
-      <c r="A74" s="116"/>
+      <c r="A74" s="131"/>
       <c r="B74" s="21" t="s">
         <v>219</v>
       </c>
@@ -10541,7 +10789,7 @@
       <c r="N74" s="4"/>
     </row>
     <row r="75" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A75" s="116"/>
+      <c r="A75" s="131"/>
       <c r="B75" s="21" t="s">
         <v>221</v>
       </c>
@@ -10566,7 +10814,7 @@
       <c r="N75" s="4"/>
     </row>
     <row r="76" spans="1:14" ht="54.6" customHeight="1">
-      <c r="A76" s="116"/>
+      <c r="A76" s="131"/>
       <c r="B76" s="21" t="s">
         <v>223</v>
       </c>
@@ -10591,7 +10839,7 @@
       <c r="N76" s="4"/>
     </row>
     <row r="77" spans="1:14" ht="42" customHeight="1">
-      <c r="A77" s="116"/>
+      <c r="A77" s="131"/>
       <c r="B77" s="21" t="s">
         <v>225</v>
       </c>
@@ -10616,7 +10864,7 @@
       <c r="N77" s="4"/>
     </row>
     <row r="78" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A78" s="116"/>
+      <c r="A78" s="131"/>
       <c r="B78" s="21" t="s">
         <v>227</v>
       </c>
@@ -10641,7 +10889,7 @@
       <c r="N78" s="4"/>
     </row>
     <row r="79" spans="1:14" ht="42.6" customHeight="1">
-      <c r="A79" s="116"/>
+      <c r="A79" s="131"/>
       <c r="B79" s="21" t="s">
         <v>229</v>
       </c>
@@ -10666,7 +10914,7 @@
       <c r="N79" s="4"/>
     </row>
     <row r="80" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A80" s="116"/>
+      <c r="A80" s="131"/>
       <c r="B80" s="21" t="s">
         <v>231</v>
       </c>
@@ -10691,7 +10939,7 @@
       <c r="N80" s="4"/>
     </row>
     <row r="81" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A81" s="116"/>
+      <c r="A81" s="131"/>
       <c r="B81" s="21" t="s">
         <v>233</v>
       </c>
@@ -10716,7 +10964,7 @@
       <c r="N81" s="4"/>
     </row>
     <row r="82" spans="1:14" ht="42" customHeight="1">
-      <c r="A82" s="116"/>
+      <c r="A82" s="131"/>
       <c r="B82" s="21" t="s">
         <v>235</v>
       </c>
@@ -10745,7 +10993,7 @@
       <c r="N82" s="4"/>
     </row>
     <row r="83" spans="1:14" ht="42" customHeight="1">
-      <c r="A83" s="116"/>
+      <c r="A83" s="131"/>
       <c r="B83" s="21" t="s">
         <v>239</v>
       </c>
@@ -10774,7 +11022,7 @@
       <c r="N83" s="4"/>
     </row>
     <row r="84" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A84" s="116"/>
+      <c r="A84" s="131"/>
       <c r="B84" s="21" t="s">
         <v>243</v>
       </c>
@@ -10803,7 +11051,7 @@
       <c r="N84" s="4"/>
     </row>
     <row r="85" spans="1:14" ht="70.2" customHeight="1">
-      <c r="A85" s="116"/>
+      <c r="A85" s="131"/>
       <c r="B85" s="21" t="s">
         <v>245</v>
       </c>
@@ -10832,7 +11080,7 @@
       <c r="N85" s="4"/>
     </row>
     <row r="86" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A86" s="116"/>
+      <c r="A86" s="131"/>
       <c r="B86" s="21" t="s">
         <v>252</v>
       </c>
@@ -10861,7 +11109,7 @@
       <c r="N86" s="4"/>
     </row>
     <row r="87" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A87" s="116"/>
+      <c r="A87" s="131"/>
       <c r="B87" s="21" t="s">
         <v>255</v>
       </c>
@@ -10890,7 +11138,7 @@
       <c r="N87" s="4"/>
     </row>
     <row r="88" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A88" s="116"/>
+      <c r="A88" s="131"/>
       <c r="B88" s="21" t="s">
         <v>258</v>
       </c>
@@ -10915,7 +11163,7 @@
       <c r="N88" s="4"/>
     </row>
     <row r="89" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A89" s="116"/>
+      <c r="A89" s="131"/>
       <c r="B89" s="21" t="s">
         <v>260</v>
       </c>
@@ -10944,7 +11192,7 @@
       <c r="N89" s="4"/>
     </row>
     <row r="90" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A90" s="116"/>
+      <c r="A90" s="131"/>
       <c r="B90" s="21" t="s">
         <v>265</v>
       </c>
@@ -10969,7 +11217,7 @@
       <c r="N90" s="4"/>
     </row>
     <row r="91" spans="1:14" ht="56.4" customHeight="1">
-      <c r="A91" s="116"/>
+      <c r="A91" s="131"/>
       <c r="B91" s="21" t="s">
         <v>269</v>
       </c>
@@ -10998,7 +11246,7 @@
       <c r="N91" s="4"/>
     </row>
     <row r="92" spans="1:14" ht="42" customHeight="1">
-      <c r="A92" s="121" t="s">
+      <c r="A92" s="136" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="27" t="s">
@@ -11025,7 +11273,7 @@
       <c r="N92" s="4"/>
     </row>
     <row r="93" spans="1:14" s="63" customFormat="1" ht="27.6">
-      <c r="A93" s="116"/>
+      <c r="A93" s="131"/>
       <c r="B93" s="27" t="s">
         <v>160</v>
       </c>
@@ -11047,7 +11295,7 @@
       <c r="K93" s="64"/>
     </row>
     <row r="94" spans="1:14" ht="61.2" customHeight="1">
-      <c r="A94" s="116"/>
+      <c r="A94" s="131"/>
       <c r="B94" s="27" t="s">
         <v>586</v>
       </c>
@@ -11072,7 +11320,7 @@
       <c r="N94" s="2"/>
     </row>
     <row r="95" spans="1:14" ht="27.6">
-      <c r="A95" s="116"/>
+      <c r="A95" s="131"/>
       <c r="B95" s="27" t="s">
         <v>161</v>
       </c>
@@ -11097,7 +11345,7 @@
       <c r="N95" s="2"/>
     </row>
     <row r="96" spans="1:14" ht="27.6">
-      <c r="A96" s="116"/>
+      <c r="A96" s="131"/>
       <c r="B96" s="21" t="s">
         <v>155</v>
       </c>
@@ -11122,7 +11370,7 @@
       <c r="N96" s="2"/>
     </row>
     <row r="97" spans="1:14" ht="41.4">
-      <c r="A97" s="116"/>
+      <c r="A97" s="131"/>
       <c r="B97" s="21" t="s">
         <v>156</v>
       </c>
@@ -11147,7 +11395,7 @@
       <c r="N97" s="2"/>
     </row>
     <row r="98" spans="1:14" ht="41.4">
-      <c r="A98" s="116"/>
+      <c r="A98" s="131"/>
       <c r="B98" s="21" t="s">
         <v>158</v>
       </c>
@@ -11172,7 +11420,7 @@
       <c r="N98" s="2"/>
     </row>
     <row r="99" spans="1:14" ht="41.4">
-      <c r="A99" s="116"/>
+      <c r="A99" s="131"/>
       <c r="B99" s="27" t="s">
         <v>162</v>
       </c>
@@ -11197,7 +11445,7 @@
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" ht="41.4">
-      <c r="A100" s="116"/>
+      <c r="A100" s="131"/>
       <c r="B100" s="27" t="s">
         <v>164</v>
       </c>
@@ -11222,7 +11470,7 @@
       <c r="N100" s="2"/>
     </row>
     <row r="101" spans="1:14" ht="39" customHeight="1">
-      <c r="A101" s="116"/>
+      <c r="A101" s="131"/>
       <c r="B101" s="27" t="s">
         <v>587</v>
       </c>
@@ -11247,7 +11495,7 @@
       <c r="N101" s="2"/>
     </row>
     <row r="102" spans="1:14" ht="41.4">
-      <c r="A102" s="116"/>
+      <c r="A102" s="131"/>
       <c r="B102" s="27" t="s">
         <v>166</v>
       </c>
@@ -11272,7 +11520,7 @@
       <c r="N102" s="2"/>
     </row>
     <row r="103" spans="1:14" s="63" customFormat="1" ht="69.599999999999994" customHeight="1">
-      <c r="A103" s="116"/>
+      <c r="A103" s="131"/>
       <c r="B103" s="27" t="s">
         <v>168</v>
       </c>
@@ -11297,7 +11545,7 @@
       <c r="N103" s="65"/>
     </row>
     <row r="104" spans="1:14" ht="27.6">
-      <c r="A104" s="116"/>
+      <c r="A104" s="131"/>
       <c r="B104" s="21" t="s">
         <v>169</v>
       </c>
@@ -11322,7 +11570,7 @@
       <c r="N104" s="2"/>
     </row>
     <row r="105" spans="1:14" ht="55.2">
-      <c r="A105" s="116"/>
+      <c r="A105" s="131"/>
       <c r="B105" s="21" t="s">
         <v>171</v>
       </c>
@@ -11347,7 +11595,7 @@
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A106" s="116"/>
+      <c r="A106" s="131"/>
       <c r="B106" s="27" t="s">
         <v>600</v>
       </c>
@@ -11372,7 +11620,7 @@
       <c r="N106" s="2"/>
     </row>
     <row r="107" spans="1:14" ht="55.2">
-      <c r="A107" s="116"/>
+      <c r="A107" s="131"/>
       <c r="B107" s="21" t="s">
         <v>173</v>
       </c>
@@ -11397,7 +11645,7 @@
       <c r="N107" s="2"/>
     </row>
     <row r="108" spans="1:14" ht="69">
-      <c r="A108" s="116"/>
+      <c r="A108" s="131"/>
       <c r="B108" s="27" t="s">
         <v>175</v>
       </c>
@@ -11422,7 +11670,7 @@
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" ht="61.8" customHeight="1">
-      <c r="A109" s="115" t="s">
+      <c r="A109" s="130" t="s">
         <v>14</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -11449,7 +11697,7 @@
       <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" ht="60" customHeight="1">
-      <c r="A110" s="116"/>
+      <c r="A110" s="131"/>
       <c r="B110" s="21" t="s">
         <v>288</v>
       </c>
@@ -11478,7 +11726,7 @@
       <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" ht="63" customHeight="1">
-      <c r="A111" s="116"/>
+      <c r="A111" s="131"/>
       <c r="B111" s="21" t="s">
         <v>292</v>
       </c>
@@ -11503,7 +11751,7 @@
       <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" ht="74.400000000000006" customHeight="1">
-      <c r="A112" s="116"/>
+      <c r="A112" s="131"/>
       <c r="B112" s="21" t="s">
         <v>294</v>
       </c>
@@ -11532,7 +11780,7 @@
       <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A113" s="116"/>
+      <c r="A113" s="131"/>
       <c r="B113" s="21" t="s">
         <v>299</v>
       </c>
@@ -11557,7 +11805,7 @@
       <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" ht="41.4">
-      <c r="A114" s="116"/>
+      <c r="A114" s="131"/>
       <c r="B114" s="21" t="s">
         <v>300</v>
       </c>
@@ -11582,7 +11830,7 @@
       <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A115" s="116"/>
+      <c r="A115" s="131"/>
       <c r="B115" s="21" t="s">
         <v>302</v>
       </c>
@@ -11607,7 +11855,7 @@
       <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A116" s="116"/>
+      <c r="A116" s="131"/>
       <c r="B116" s="21" t="s">
         <v>304</v>
       </c>
@@ -11632,7 +11880,7 @@
       <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A117" s="116"/>
+      <c r="A117" s="131"/>
       <c r="B117" s="21" t="s">
         <v>306</v>
       </c>
@@ -11657,7 +11905,7 @@
       <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" ht="77.400000000000006" customHeight="1">
-      <c r="A118" s="116"/>
+      <c r="A118" s="131"/>
       <c r="B118" s="21" t="s">
         <v>308</v>
       </c>
@@ -11686,7 +11934,7 @@
       <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" ht="65.400000000000006" customHeight="1">
-      <c r="A119" s="116"/>
+      <c r="A119" s="131"/>
       <c r="B119" s="21" t="s">
         <v>312</v>
       </c>
@@ -11711,7 +11959,7 @@
       <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" ht="60.6" customHeight="1">
-      <c r="A120" s="116"/>
+      <c r="A120" s="131"/>
       <c r="B120" s="21" t="s">
         <v>314</v>
       </c>
@@ -11736,7 +11984,7 @@
       <c r="N120" s="4"/>
     </row>
     <row r="121" spans="1:14" ht="40.200000000000003" customHeight="1">
-      <c r="A121" s="116"/>
+      <c r="A121" s="131"/>
       <c r="B121" s="21" t="s">
         <v>316</v>
       </c>
@@ -11761,7 +12009,7 @@
       <c r="N121" s="4"/>
     </row>
     <row r="122" spans="1:14" ht="69">
-      <c r="A122" s="116"/>
+      <c r="A122" s="131"/>
       <c r="B122" s="21" t="s">
         <v>318</v>
       </c>
@@ -11786,7 +12034,7 @@
       <c r="N122" s="4"/>
     </row>
     <row r="123" spans="1:14" ht="60" customHeight="1">
-      <c r="A123" s="116"/>
+      <c r="A123" s="131"/>
       <c r="B123" s="21" t="s">
         <v>320</v>
       </c>
@@ -11811,7 +12059,7 @@
       <c r="N123" s="4"/>
     </row>
     <row r="124" spans="1:14" ht="69">
-      <c r="A124" s="116"/>
+      <c r="A124" s="131"/>
       <c r="B124" s="21" t="s">
         <v>322</v>
       </c>
@@ -11836,7 +12084,7 @@
       <c r="N124" s="4"/>
     </row>
     <row r="125" spans="1:14" ht="67.8" customHeight="1">
-      <c r="A125" s="116"/>
+      <c r="A125" s="131"/>
       <c r="B125" s="27" t="s">
         <v>324</v>
       </c>
@@ -14803,18 +15051,18 @@
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:F1048576 C2">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:F1048576">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14853,44 +15101,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="148" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="133" t="s">
+      <c r="B1" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="133" t="s">
+      <c r="C1" s="148" t="s">
         <v>367</v>
       </c>
-      <c r="D1" s="133" t="s">
+      <c r="D1" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="133" t="s">
+      <c r="E1" s="148" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="133" t="s">
+      <c r="F1" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="133" t="s">
+      <c r="G1" s="148" t="s">
         <v>836</v>
       </c>
-      <c r="H1" s="128" t="s">
+      <c r="H1" s="143" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="129"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="131" t="s">
+      <c r="I1" s="144"/>
+      <c r="J1" s="145"/>
+      <c r="K1" s="146" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6">
-      <c r="A2" s="132"/>
-      <c r="B2" s="132"/>
-      <c r="C2" s="132"/>
-      <c r="D2" s="132"/>
-      <c r="E2" s="132"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132"/>
+      <c r="A2" s="147"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
+      <c r="G2" s="147"/>
       <c r="H2" s="36" t="s">
         <v>21</v>
       </c>
@@ -14900,10 +15148,10 @@
       <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="132"/>
+      <c r="K2" s="147"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="152" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -14936,7 +15184,7 @@
       <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A4" s="138"/>
+      <c r="A4" s="153"/>
       <c r="B4" s="38" t="s">
         <v>336</v>
       </c>
@@ -14967,7 +15215,7 @@
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="138"/>
+      <c r="A5" s="153"/>
       <c r="B5" s="38" t="s">
         <v>337</v>
       </c>
@@ -14998,7 +15246,7 @@
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="138"/>
+      <c r="A6" s="153"/>
       <c r="B6" s="38" t="s">
         <v>338</v>
       </c>
@@ -15029,7 +15277,7 @@
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="138"/>
+      <c r="A7" s="153"/>
       <c r="B7" s="38" t="s">
         <v>339</v>
       </c>
@@ -15060,7 +15308,7 @@
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="138"/>
+      <c r="A8" s="153"/>
       <c r="B8" s="38" t="s">
         <v>340</v>
       </c>
@@ -15091,7 +15339,7 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="132"/>
+      <c r="A9" s="147"/>
       <c r="B9" s="38" t="s">
         <v>341</v>
       </c>
@@ -15122,7 +15370,7 @@
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="152" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -15155,7 +15403,7 @@
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="138"/>
+      <c r="A11" s="153"/>
       <c r="B11" s="38" t="s">
         <v>343</v>
       </c>
@@ -15186,7 +15434,7 @@
       <c r="K11" s="41"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="138"/>
+      <c r="A12" s="153"/>
       <c r="B12" s="38" t="s">
         <v>344</v>
       </c>
@@ -15217,7 +15465,7 @@
       <c r="K12" s="41"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="138"/>
+      <c r="A13" s="153"/>
       <c r="B13" s="38" t="s">
         <v>345</v>
       </c>
@@ -15248,7 +15496,7 @@
       <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="138"/>
+      <c r="A14" s="153"/>
       <c r="B14" s="38" t="s">
         <v>346</v>
       </c>
@@ -15279,7 +15527,7 @@
       <c r="K14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="138"/>
+      <c r="A15" s="153"/>
       <c r="B15" s="38" t="s">
         <v>347</v>
       </c>
@@ -15310,7 +15558,7 @@
       <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="138"/>
+      <c r="A16" s="153"/>
       <c r="B16" s="38" t="s">
         <v>348</v>
       </c>
@@ -15341,7 +15589,7 @@
       <c r="K16" s="41"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="138"/>
+      <c r="A17" s="153"/>
       <c r="B17" s="38" t="s">
         <v>349</v>
       </c>
@@ -15374,7 +15622,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="138"/>
+      <c r="A18" s="153"/>
       <c r="B18" s="38" t="s">
         <v>436</v>
       </c>
@@ -15405,7 +15653,7 @@
       <c r="K18" s="41"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="132"/>
+      <c r="A19" s="147"/>
       <c r="B19" s="38" t="s">
         <v>437</v>
       </c>
@@ -15436,7 +15684,7 @@
       <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A20" s="137" t="s">
+      <c r="A20" s="152" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -15469,7 +15717,7 @@
       <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="138"/>
+      <c r="A21" s="153"/>
       <c r="B21" s="38" t="s">
         <v>351</v>
       </c>
@@ -15500,7 +15748,7 @@
       <c r="K21" s="41"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A22" s="138"/>
+      <c r="A22" s="153"/>
       <c r="B22" s="38" t="s">
         <v>352</v>
       </c>
@@ -15533,7 +15781,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="138"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="38" t="s">
         <v>353</v>
       </c>
@@ -15566,7 +15814,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A24" s="138"/>
+      <c r="A24" s="153"/>
       <c r="B24" s="38" t="s">
         <v>446</v>
       </c>
@@ -15597,7 +15845,7 @@
       <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A25" s="138"/>
+      <c r="A25" s="153"/>
       <c r="B25" s="38" t="s">
         <v>354</v>
       </c>
@@ -15628,7 +15876,7 @@
       <c r="K25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A26" s="138"/>
+      <c r="A26" s="153"/>
       <c r="B26" s="38" t="s">
         <v>355</v>
       </c>
@@ -15659,7 +15907,7 @@
       <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A27" s="138"/>
+      <c r="A27" s="153"/>
       <c r="B27" s="38" t="s">
         <v>356</v>
       </c>
@@ -15692,7 +15940,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="138"/>
+      <c r="A28" s="153"/>
       <c r="B28" s="38" t="s">
         <v>357</v>
       </c>
@@ -15725,7 +15973,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="138"/>
+      <c r="A29" s="153"/>
       <c r="B29" s="38" t="s">
         <v>389</v>
       </c>
@@ -15756,7 +16004,7 @@
       <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="138"/>
+      <c r="A30" s="153"/>
       <c r="B30" s="38" t="s">
         <v>390</v>
       </c>
@@ -15787,7 +16035,7 @@
       <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="85.8" customHeight="1">
-      <c r="A31" s="139" t="s">
+      <c r="A31" s="154" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
@@ -15820,7 +16068,7 @@
       <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="55.2">
-      <c r="A32" s="138"/>
+      <c r="A32" s="153"/>
       <c r="B32" s="38" t="s">
         <v>451</v>
       </c>
@@ -15853,7 +16101,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="82.8">
-      <c r="A33" s="138"/>
+      <c r="A33" s="153"/>
       <c r="B33" s="38" t="s">
         <v>452</v>
       </c>
@@ -15886,7 +16134,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="96.6">
-      <c r="A34" s="138"/>
+      <c r="A34" s="153"/>
       <c r="B34" s="38" t="s">
         <v>453</v>
       </c>
@@ -15917,7 +16165,7 @@
       <c r="K34" s="41"/>
     </row>
     <row r="35" spans="1:11" ht="82.8">
-      <c r="A35" s="138"/>
+      <c r="A35" s="153"/>
       <c r="B35" s="38" t="s">
         <v>454</v>
       </c>
@@ -15950,7 +16198,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="69">
-      <c r="A36" s="138"/>
+      <c r="A36" s="153"/>
       <c r="B36" s="38" t="s">
         <v>455</v>
       </c>
@@ -15981,7 +16229,7 @@
       <c r="K36" s="41"/>
     </row>
     <row r="37" spans="1:11" ht="57" customHeight="1">
-      <c r="A37" s="138"/>
+      <c r="A37" s="153"/>
       <c r="B37" s="38" t="s">
         <v>456</v>
       </c>
@@ -16014,7 +16262,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="72" customHeight="1">
-      <c r="A38" s="138"/>
+      <c r="A38" s="153"/>
       <c r="B38" s="38" t="s">
         <v>473</v>
       </c>
@@ -16045,7 +16293,7 @@
       <c r="K38" s="41"/>
     </row>
     <row r="39" spans="1:11" ht="92.4">
-      <c r="A39" s="137" t="s">
+      <c r="A39" s="152" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -16078,7 +16326,7 @@
       <c r="K39" s="41"/>
     </row>
     <row r="40" spans="1:11" ht="110.4">
-      <c r="A40" s="138"/>
+      <c r="A40" s="153"/>
       <c r="B40" s="38" t="s">
         <v>482</v>
       </c>
@@ -16109,7 +16357,7 @@
       <c r="K40" s="41"/>
     </row>
     <row r="41" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A41" s="138"/>
+      <c r="A41" s="153"/>
       <c r="B41" s="38" t="s">
         <v>483</v>
       </c>
@@ -16140,7 +16388,7 @@
       <c r="K41" s="41"/>
     </row>
     <row r="42" spans="1:11" ht="61.2" customHeight="1">
-      <c r="A42" s="138"/>
+      <c r="A42" s="153"/>
       <c r="B42" s="38" t="s">
         <v>484</v>
       </c>
@@ -16171,7 +16419,7 @@
       <c r="K42" s="41"/>
     </row>
     <row r="43" spans="1:11" ht="69" customHeight="1">
-      <c r="A43" s="138"/>
+      <c r="A43" s="153"/>
       <c r="B43" s="38" t="s">
         <v>485</v>
       </c>
@@ -16202,7 +16450,7 @@
       <c r="K43" s="41"/>
     </row>
     <row r="44" spans="1:11" ht="73.8" customHeight="1">
-      <c r="A44" s="138"/>
+      <c r="A44" s="153"/>
       <c r="B44" s="38" t="s">
         <v>486</v>
       </c>
@@ -16233,7 +16481,7 @@
       <c r="K44" s="41"/>
     </row>
     <row r="45" spans="1:11" ht="85.2" customHeight="1">
-      <c r="A45" s="138"/>
+      <c r="A45" s="153"/>
       <c r="B45" s="38" t="s">
         <v>487</v>
       </c>
@@ -16264,7 +16512,7 @@
       <c r="K45" s="41"/>
     </row>
     <row r="46" spans="1:11" ht="70.8" customHeight="1">
-      <c r="A46" s="138"/>
+      <c r="A46" s="153"/>
       <c r="B46" s="38" t="s">
         <v>488</v>
       </c>
@@ -16297,7 +16545,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="99" customHeight="1">
-      <c r="A47" s="138"/>
+      <c r="A47" s="153"/>
       <c r="B47" s="38" t="s">
         <v>510</v>
       </c>
@@ -16330,7 +16578,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="92.4" customHeight="1">
-      <c r="A48" s="138"/>
+      <c r="A48" s="153"/>
       <c r="B48" s="38" t="s">
         <v>513</v>
       </c>
@@ -16361,7 +16609,7 @@
       <c r="K48" s="41"/>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1">
-      <c r="A49" s="132"/>
+      <c r="A49" s="147"/>
       <c r="B49" s="38" t="s">
         <v>514</v>
       </c>
@@ -16392,7 +16640,7 @@
       <c r="K49" s="41"/>
     </row>
     <row r="50" spans="1:11" ht="82.8">
-      <c r="A50" s="137" t="s">
+      <c r="A50" s="152" t="s">
         <v>208</v>
       </c>
       <c r="B50" s="38" t="s">
@@ -16425,7 +16673,7 @@
       <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A51" s="138"/>
+      <c r="A51" s="153"/>
       <c r="B51" s="38" t="s">
         <v>522</v>
       </c>
@@ -16456,7 +16704,7 @@
       <c r="K51" s="41"/>
     </row>
     <row r="52" spans="1:11" ht="96.6">
-      <c r="A52" s="138"/>
+      <c r="A52" s="153"/>
       <c r="B52" s="38" t="s">
         <v>523</v>
       </c>
@@ -16487,7 +16735,7 @@
       <c r="K52" s="41"/>
     </row>
     <row r="53" spans="1:11" ht="82.2" customHeight="1">
-      <c r="A53" s="138"/>
+      <c r="A53" s="153"/>
       <c r="B53" s="38" t="s">
         <v>524</v>
       </c>
@@ -16518,7 +16766,7 @@
       <c r="K53" s="44"/>
     </row>
     <row r="54" spans="1:11" ht="82.8">
-      <c r="A54" s="138"/>
+      <c r="A54" s="153"/>
       <c r="B54" s="38" t="s">
         <v>525</v>
       </c>
@@ -16551,7 +16799,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="55.2">
-      <c r="A55" s="138"/>
+      <c r="A55" s="153"/>
       <c r="B55" s="38" t="s">
         <v>526</v>
       </c>
@@ -16584,7 +16832,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="41.4">
-      <c r="A56" s="138"/>
+      <c r="A56" s="153"/>
       <c r="B56" s="38" t="s">
         <v>527</v>
       </c>
@@ -16617,7 +16865,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="55.8">
-      <c r="A57" s="138"/>
+      <c r="A57" s="153"/>
       <c r="B57" s="38" t="s">
         <v>528</v>
       </c>
@@ -16650,7 +16898,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="82.8">
-      <c r="A58" s="138"/>
+      <c r="A58" s="153"/>
       <c r="B58" s="38" t="s">
         <v>529</v>
       </c>
@@ -16681,7 +16929,7 @@
       <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" ht="82.8">
-      <c r="A59" s="138"/>
+      <c r="A59" s="153"/>
       <c r="B59" s="38" t="s">
         <v>530</v>
       </c>
@@ -16714,7 +16962,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="55.2">
-      <c r="A60" s="138"/>
+      <c r="A60" s="153"/>
       <c r="B60" s="38" t="s">
         <v>531</v>
       </c>
@@ -16745,7 +16993,7 @@
       <c r="K60" s="41"/>
     </row>
     <row r="61" spans="1:11" ht="69">
-      <c r="A61" s="138"/>
+      <c r="A61" s="153"/>
       <c r="B61" s="38" t="s">
         <v>532</v>
       </c>
@@ -16778,7 +17026,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" ht="69.599999999999994">
-      <c r="A62" s="138"/>
+      <c r="A62" s="153"/>
       <c r="B62" s="38" t="s">
         <v>533</v>
       </c>
@@ -16809,7 +17057,7 @@
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11" ht="117.6" customHeight="1">
-      <c r="A63" s="138"/>
+      <c r="A63" s="153"/>
       <c r="B63" s="38" t="s">
         <v>534</v>
       </c>
@@ -16840,7 +17088,7 @@
       <c r="K63" s="41"/>
     </row>
     <row r="64" spans="1:11" ht="83.4">
-      <c r="A64" s="137" t="s">
+      <c r="A64" s="152" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -16873,7 +17121,7 @@
       <c r="K64" s="41"/>
     </row>
     <row r="65" spans="1:27" ht="69.599999999999994">
-      <c r="A65" s="138"/>
+      <c r="A65" s="153"/>
       <c r="B65" s="38" t="s">
         <v>574</v>
       </c>
@@ -16920,7 +17168,7 @@
       <c r="AA65" s="2"/>
     </row>
     <row r="66" spans="1:27" ht="83.4">
-      <c r="A66" s="138"/>
+      <c r="A66" s="153"/>
       <c r="B66" s="38" t="s">
         <v>575</v>
       </c>
@@ -16967,7 +17215,7 @@
       <c r="AA66" s="2"/>
     </row>
     <row r="67" spans="1:27" ht="104.4" customHeight="1">
-      <c r="A67" s="138"/>
+      <c r="A67" s="153"/>
       <c r="B67" s="38" t="s">
         <v>576</v>
       </c>
@@ -17014,7 +17262,7 @@
       <c r="AA67" s="2"/>
     </row>
     <row r="68" spans="1:27" ht="75" customHeight="1">
-      <c r="A68" s="138"/>
+      <c r="A68" s="153"/>
       <c r="B68" s="38" t="s">
         <v>577</v>
       </c>
@@ -17061,7 +17309,7 @@
       <c r="AA68" s="2"/>
     </row>
     <row r="69" spans="1:27" ht="83.4">
-      <c r="A69" s="138"/>
+      <c r="A69" s="153"/>
       <c r="B69" s="38" t="s">
         <v>578</v>
       </c>
@@ -17108,7 +17356,7 @@
       <c r="AA69" s="2"/>
     </row>
     <row r="70" spans="1:27" ht="42">
-      <c r="A70" s="138"/>
+      <c r="A70" s="153"/>
       <c r="B70" s="38" t="s">
         <v>579</v>
       </c>
@@ -17155,7 +17403,7 @@
       <c r="AA70" s="2"/>
     </row>
     <row r="71" spans="1:27" ht="78">
-      <c r="A71" s="138"/>
+      <c r="A71" s="153"/>
       <c r="B71" s="38" t="s">
         <v>580</v>
       </c>
@@ -17202,7 +17450,7 @@
       <c r="AA71" s="2"/>
     </row>
     <row r="72" spans="1:27" ht="78">
-      <c r="A72" s="138"/>
+      <c r="A72" s="153"/>
       <c r="B72" s="38" t="s">
         <v>581</v>
       </c>
@@ -17233,7 +17481,7 @@
       <c r="K72" s="41"/>
     </row>
     <row r="73" spans="1:27" ht="94.8" customHeight="1">
-      <c r="A73" s="131" t="s">
+      <c r="A73" s="146" t="s">
         <v>14</v>
       </c>
       <c r="B73" s="38" t="s">
@@ -17266,7 +17514,7 @@
       <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:27" ht="75">
-      <c r="A74" s="134"/>
+      <c r="A74" s="149"/>
       <c r="B74" s="38" t="s">
         <v>621</v>
       </c>
@@ -17299,7 +17547,7 @@
       </c>
     </row>
     <row r="75" spans="1:27" ht="75">
-      <c r="A75" s="134"/>
+      <c r="A75" s="149"/>
       <c r="B75" s="38" t="s">
         <v>622</v>
       </c>
@@ -17332,7 +17580,7 @@
       </c>
     </row>
     <row r="76" spans="1:27" ht="79.2" customHeight="1">
-      <c r="A76" s="134"/>
+      <c r="A76" s="149"/>
       <c r="B76" s="38" t="s">
         <v>623</v>
       </c>
@@ -17363,7 +17611,7 @@
       <c r="K76" s="41"/>
     </row>
     <row r="77" spans="1:27" ht="69" customHeight="1">
-      <c r="A77" s="134"/>
+      <c r="A77" s="149"/>
       <c r="B77" s="38" t="s">
         <v>633</v>
       </c>
@@ -17394,7 +17642,7 @@
       <c r="K77" s="41"/>
     </row>
     <row r="78" spans="1:27" ht="69" customHeight="1">
-      <c r="A78" s="134"/>
+      <c r="A78" s="149"/>
       <c r="B78" s="38" t="s">
         <v>637</v>
       </c>
@@ -17425,7 +17673,7 @@
       <c r="K78" s="41"/>
     </row>
     <row r="79" spans="1:27" ht="69" customHeight="1">
-      <c r="A79" s="134"/>
+      <c r="A79" s="149"/>
       <c r="B79" s="38" t="s">
         <v>641</v>
       </c>
@@ -17458,7 +17706,7 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="75" customHeight="1">
-      <c r="A80" s="134"/>
+      <c r="A80" s="149"/>
       <c r="B80" s="38" t="s">
         <v>645</v>
       </c>
@@ -17489,7 +17737,7 @@
       <c r="K80" s="41"/>
     </row>
     <row r="81" spans="1:11" ht="93" customHeight="1">
-      <c r="A81" s="134"/>
+      <c r="A81" s="149"/>
       <c r="B81" s="38" t="s">
         <v>649</v>
       </c>
@@ -17520,7 +17768,7 @@
       <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A82" s="134"/>
+      <c r="A82" s="149"/>
       <c r="B82" s="38" t="s">
         <v>653</v>
       </c>
@@ -17551,7 +17799,7 @@
       <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" ht="110.4" customHeight="1">
-      <c r="A83" s="134"/>
+      <c r="A83" s="149"/>
       <c r="B83" s="38" t="s">
         <v>657</v>
       </c>
@@ -17582,7 +17830,7 @@
       <c r="K83" s="41"/>
     </row>
     <row r="84" spans="1:11" ht="109.2" customHeight="1">
-      <c r="A84" s="134"/>
+      <c r="A84" s="149"/>
       <c r="B84" s="38" t="s">
         <v>661</v>
       </c>
@@ -17613,7 +17861,7 @@
       <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" ht="67.8" customHeight="1">
-      <c r="A85" s="134"/>
+      <c r="A85" s="149"/>
       <c r="B85" s="38" t="s">
         <v>665</v>
       </c>
@@ -17654,8 +17902,8 @@
     </row>
     <row r="88" spans="1:11" ht="13.2">
       <c r="A88" s="37"/>
-      <c r="B88" s="135"/>
-      <c r="C88" s="136"/>
+      <c r="B88" s="150"/>
+      <c r="C88" s="151"/>
       <c r="D88" s="10"/>
     </row>
     <row r="89" spans="1:11" ht="13.2">
@@ -20634,24 +20882,24 @@
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="Низкий">
+    <cfRule type="containsText" dxfId="12" priority="1" operator="containsText" text="Низкий">
       <formula>NOT(ISERROR(SEARCH("Низкий",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="Средний">
+    <cfRule type="containsText" dxfId="11" priority="2" operator="containsText" text="Средний">
       <formula>NOT(ISERROR(SEARCH("Средний",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="3" operator="containsText" text="Высокий">
+    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="Высокий">
       <formula>NOT(ISERROR(SEARCH("Высокий",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:J1048576">
-    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Passed">
+    <cfRule type="containsText" dxfId="9" priority="4" operator="containsText" text="Passed">
       <formula>NOT(ISERROR(SEARCH("Passed",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Failed">
+    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="Failed">
       <formula>NOT(ISERROR(SEARCH("Failed",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Failed">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="Failed">
       <formula>NOT(ISERROR(SEARCH("Failed",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20693,48 +20941,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.4" customHeight="1">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="155" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="71"/>
-      <c r="C1" s="142" t="s">
+      <c r="C1" s="155" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="150" t="s">
+      <c r="D1" s="165" t="s">
         <v>704</v>
       </c>
-      <c r="E1" s="142" t="s">
+      <c r="E1" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="142" t="s">
+      <c r="F1" s="155" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="142" t="s">
+      <c r="G1" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="142" t="s">
+      <c r="H1" s="155" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="144" t="s">
+      <c r="I1" s="159" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
+      <c r="J1" s="160"/>
+      <c r="K1" s="160"/>
       <c r="L1" s="72" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="42">
-      <c r="A2" s="143"/>
+      <c r="A2" s="156"/>
       <c r="B2" s="71" t="s">
         <v>705</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="151"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
+      <c r="C2" s="156"/>
+      <c r="D2" s="166"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
       <c r="I2" s="74" t="s">
         <v>46</v>
       </c>
@@ -21433,62 +21681,62 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="62.4" customHeight="1">
-      <c r="A21" s="146" t="s">
+      <c r="A21" s="161" t="s">
         <v>843</v>
       </c>
-      <c r="B21" s="146"/>
-      <c r="C21" s="146"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
-      <c r="F21" s="146"/>
-      <c r="G21" s="146"/>
-      <c r="H21" s="146"/>
-      <c r="I21" s="146"/>
-      <c r="J21" s="146"/>
-      <c r="K21" s="146"/>
+      <c r="B21" s="161"/>
+      <c r="C21" s="161"/>
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161"/>
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161"/>
       <c r="L21" s="90"/>
     </row>
     <row r="22" spans="1:12" ht="14.4">
-      <c r="A22" s="147" t="s">
+      <c r="A22" s="162" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="91"/>
-      <c r="C22" s="147" t="s">
+      <c r="C22" s="162" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="147" t="s">
+      <c r="D22" s="162" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="147" t="s">
+      <c r="E22" s="162" t="s">
         <v>808</v>
       </c>
-      <c r="F22" s="147" t="s">
+      <c r="F22" s="162" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="147" t="s">
+      <c r="G22" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="148" t="s">
+      <c r="H22" s="163" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="140" t="s">
+      <c r="I22" s="157" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="141"/>
-      <c r="K22" s="141"/>
+      <c r="J22" s="158"/>
+      <c r="K22" s="158"/>
       <c r="L22" s="92" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="41.4">
-      <c r="A23" s="143"/>
+      <c r="A23" s="156"/>
       <c r="B23" s="91"/>
-      <c r="C23" s="143"/>
-      <c r="D23" s="143"/>
-      <c r="E23" s="143"/>
-      <c r="F23" s="143"/>
-      <c r="G23" s="143"/>
-      <c r="H23" s="149"/>
+      <c r="C23" s="156"/>
+      <c r="D23" s="156"/>
+      <c r="E23" s="156"/>
+      <c r="F23" s="156"/>
+      <c r="G23" s="156"/>
+      <c r="H23" s="164"/>
       <c r="I23" s="93" t="s">
         <v>46</v>
       </c>
@@ -22678,6 +22926,8 @@
     <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="H1:H2"/>
@@ -22693,23 +22943,21 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="Minor">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Minor">
       <formula>NOT(ISERROR(SEARCH("Minor",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="Medium">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="Major">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Major">
       <formula>NOT(ISERROR(SEARCH("Major",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Major">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="Major">
       <formula>NOT(ISERROR(SEARCH("Major",D1)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22762,286 +23010,286 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="154" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" style="154" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" style="154" customWidth="1"/>
-    <col min="4" max="4" width="45.77734375" style="154" customWidth="1"/>
-    <col min="5" max="5" width="49.88671875" style="154" customWidth="1"/>
-    <col min="6" max="6" width="19" style="154" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="154" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="154"/>
+    <col min="1" max="1" width="15.6640625" style="115" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" style="115" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" style="115" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="115" customWidth="1"/>
+    <col min="5" max="5" width="49.88671875" style="115" customWidth="1"/>
+    <col min="6" max="6" width="19" style="115" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" style="115" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="115"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="118" t="s">
         <v>670</v>
       </c>
-      <c r="B1" s="158" t="s">
+      <c r="B1" s="119" t="s">
         <v>671</v>
       </c>
-      <c r="C1" s="158" t="s">
+      <c r="C1" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="158" t="s">
+      <c r="D1" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="158" t="s">
+      <c r="E1" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="158" t="s">
+      <c r="F1" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="158" t="s">
+      <c r="G1" s="119" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="288">
-      <c r="A2" s="156" t="s">
+      <c r="A2" s="117" t="s">
         <v>672</v>
       </c>
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="116" t="s">
         <v>673</v>
       </c>
-      <c r="C2" s="155" t="s">
+      <c r="C2" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="116" t="s">
         <v>674</v>
       </c>
-      <c r="E2" s="155" t="s">
+      <c r="E2" s="116" t="s">
         <v>869</v>
       </c>
-      <c r="F2" s="155" t="s">
+      <c r="F2" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="155" t="s">
+      <c r="G2" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="408.6" customHeight="1">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="117" t="s">
         <v>676</v>
       </c>
-      <c r="B3" s="155" t="s">
+      <c r="B3" s="116" t="s">
         <v>677</v>
       </c>
-      <c r="C3" s="155" t="s">
+      <c r="C3" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="155" t="s">
+      <c r="D3" s="116" t="s">
         <v>678</v>
       </c>
-      <c r="E3" s="155" t="s">
+      <c r="E3" s="116" t="s">
         <v>868</v>
       </c>
-      <c r="F3" s="155" t="s">
+      <c r="F3" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="155" t="s">
+      <c r="G3" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="360">
-      <c r="A4" s="156" t="s">
+      <c r="A4" s="117" t="s">
         <v>679</v>
       </c>
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="116" t="s">
         <v>680</v>
       </c>
-      <c r="C4" s="155" t="s">
+      <c r="C4" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="155" t="s">
+      <c r="D4" s="116" t="s">
         <v>681</v>
       </c>
-      <c r="E4" s="155" t="s">
+      <c r="E4" s="116" t="s">
         <v>867</v>
       </c>
-      <c r="F4" s="155" t="s">
+      <c r="F4" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="155" t="s">
+      <c r="G4" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="345.6">
-      <c r="A5" s="156" t="s">
+      <c r="A5" s="117" t="s">
         <v>682</v>
       </c>
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="116" t="s">
         <v>683</v>
       </c>
-      <c r="C5" s="155" t="s">
+      <c r="C5" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="155" t="s">
+      <c r="D5" s="116" t="s">
         <v>684</v>
       </c>
-      <c r="E5" s="155" t="s">
+      <c r="E5" s="116" t="s">
         <v>866</v>
       </c>
-      <c r="F5" s="155" t="s">
+      <c r="F5" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="155" t="s">
+      <c r="G5" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="325.2" customHeight="1">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="117" t="s">
         <v>685</v>
       </c>
-      <c r="B6" s="155" t="s">
+      <c r="B6" s="116" t="s">
         <v>686</v>
       </c>
-      <c r="C6" s="155" t="s">
+      <c r="C6" s="116" t="s">
         <v>687</v>
       </c>
-      <c r="D6" s="155" t="s">
+      <c r="D6" s="116" t="s">
         <v>688</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="E6" s="116" t="s">
         <v>865</v>
       </c>
-      <c r="F6" s="155" t="s">
+      <c r="F6" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="155" t="s">
+      <c r="G6" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="348.6" customHeight="1">
-      <c r="A7" s="156" t="s">
+      <c r="A7" s="117" t="s">
         <v>689</v>
       </c>
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="116" t="s">
         <v>690</v>
       </c>
-      <c r="C7" s="155" t="s">
+      <c r="C7" s="116" t="s">
         <v>687</v>
       </c>
-      <c r="D7" s="155" t="s">
+      <c r="D7" s="116" t="s">
         <v>691</v>
       </c>
-      <c r="E7" s="155" t="s">
+      <c r="E7" s="116" t="s">
         <v>864</v>
       </c>
-      <c r="F7" s="155" t="s">
+      <c r="F7" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="155" t="s">
+      <c r="G7" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="316.8">
-      <c r="A8" s="156" t="s">
+      <c r="A8" s="117" t="s">
         <v>692</v>
       </c>
-      <c r="B8" s="155" t="s">
+      <c r="B8" s="116" t="s">
         <v>693</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="116" t="s">
         <v>694</v>
       </c>
-      <c r="D8" s="155" t="s">
+      <c r="D8" s="116" t="s">
         <v>695</v>
       </c>
-      <c r="E8" s="155" t="s">
+      <c r="E8" s="116" t="s">
         <v>863</v>
       </c>
-      <c r="F8" s="155" t="s">
+      <c r="F8" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="155" t="s">
+      <c r="G8" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="405" customHeight="1">
-      <c r="A9" s="156" t="s">
+      <c r="A9" s="117" t="s">
         <v>696</v>
       </c>
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="116" t="s">
         <v>697</v>
       </c>
-      <c r="C9" s="155" t="s">
+      <c r="C9" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="155" t="s">
+      <c r="D9" s="116" t="s">
         <v>862</v>
       </c>
-      <c r="E9" s="155" t="s">
+      <c r="E9" s="116" t="s">
         <v>861</v>
       </c>
-      <c r="F9" s="155" t="s">
+      <c r="F9" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="155" t="s">
+      <c r="G9" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="408.6" customHeight="1">
-      <c r="A10" s="156" t="s">
+      <c r="A10" s="117" t="s">
         <v>698</v>
       </c>
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="116" t="s">
         <v>699</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="155" t="s">
+      <c r="D10" s="116" t="s">
         <v>700</v>
       </c>
-      <c r="E10" s="155" t="s">
+      <c r="E10" s="116" t="s">
         <v>860</v>
       </c>
-      <c r="F10" s="155" t="s">
+      <c r="F10" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="155" t="s">
+      <c r="G10" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="403.2">
-      <c r="A11" s="156" t="s">
+      <c r="A11" s="117" t="s">
         <v>701</v>
       </c>
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="116" t="s">
         <v>702</v>
       </c>
-      <c r="C11" s="155" t="s">
+      <c r="C11" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="155" t="s">
+      <c r="D11" s="116" t="s">
         <v>703</v>
       </c>
-      <c r="E11" s="155" t="s">
+      <c r="E11" s="116" t="s">
         <v>859</v>
       </c>
-      <c r="F11" s="155" t="s">
+      <c r="F11" s="116" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="155" t="s">
+      <c r="G11" s="116" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4">
-      <c r="A12" s="156"/>
-      <c r="B12" s="155"/>
-      <c r="C12" s="155"/>
-      <c r="D12" s="155"/>
-      <c r="E12" s="155"/>
-      <c r="F12" s="155"/>
-      <c r="G12" s="155"/>
+      <c r="A12" s="117"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
     </row>
     <row r="13" spans="1:7" ht="14.4">
-      <c r="A13" s="156"/>
-      <c r="B13" s="155"/>
-      <c r="C13" s="155"/>
-      <c r="D13" s="155"/>
-      <c r="E13" s="155"/>
-      <c r="F13" s="155"/>
-      <c r="G13" s="155"/>
+      <c r="A13" s="117"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="116"/>
+      <c r="G13" s="116"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23161,30 +23409,30 @@
       <c r="B8" s="102"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="152" t="s">
+      <c r="A11" s="167" t="s">
         <v>858</v>
       </c>
-      <c r="B11" s="153"/>
-      <c r="C11" s="153"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="153"/>
-      <c r="F11" s="153"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="168"/>
+      <c r="D11" s="168"/>
+      <c r="E11" s="168"/>
+      <c r="F11" s="168"/>
     </row>
     <row r="12" spans="1:6" ht="60.6" customHeight="1">
-      <c r="A12" s="153"/>
-      <c r="B12" s="153"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
+      <c r="A12" s="168"/>
+      <c r="B12" s="168"/>
+      <c r="C12" s="168"/>
+      <c r="D12" s="168"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="168"/>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1">
-      <c r="A13" s="153"/>
-      <c r="B13" s="153"/>
-      <c r="C13" s="153"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="153"/>
-      <c r="F13" s="153"/>
+      <c r="A13" s="168"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="168"/>
+      <c r="D13" s="168"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="168"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="31"/>
@@ -23207,7 +23455,7 @@
     <mergeCell ref="A11:F13"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:F8">
-    <cfRule type="notContainsBlanks" dxfId="2" priority="2">
+    <cfRule type="notContainsBlanks" dxfId="1" priority="2">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23328,7 +23576,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:F8">
-    <cfRule type="notContainsBlanks" dxfId="1" priority="1">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23338,4 +23586,420 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A1B626-16EF-46D6-9F3F-F7F7EC2F1D63}">
+  <dimension ref="A1:AS14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="64.5546875" style="120" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="120" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="120" customWidth="1"/>
+    <col min="4" max="6" width="8.5546875" style="120" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="120" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" style="120" customWidth="1"/>
+    <col min="9" max="9" width="9" style="120" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="120" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="120" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="120" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="120" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="120" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" style="120" customWidth="1"/>
+    <col min="16" max="17" width="8.77734375" style="120" customWidth="1"/>
+    <col min="18" max="18" width="9" style="120" customWidth="1"/>
+    <col min="19" max="19" width="8.5546875" style="120" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="120" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" style="120" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" style="120" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="120" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="120"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:45">
+      <c r="A1" s="127"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="127"/>
+      <c r="P1" s="127"/>
+      <c r="Q1" s="127"/>
+      <c r="R1" s="127"/>
+      <c r="S1" s="127"/>
+      <c r="T1" s="127"/>
+      <c r="U1" s="127"/>
+      <c r="V1" s="127"/>
+      <c r="W1" s="127"/>
+      <c r="X1" s="127"/>
+      <c r="Y1" s="127"/>
+      <c r="Z1" s="127"/>
+      <c r="AA1" s="127"/>
+      <c r="AB1" s="127"/>
+      <c r="AC1" s="127"/>
+      <c r="AD1" s="127"/>
+      <c r="AE1" s="127"/>
+      <c r="AF1" s="127"/>
+      <c r="AG1" s="127"/>
+      <c r="AH1" s="127"/>
+      <c r="AI1" s="127"/>
+      <c r="AJ1" s="127"/>
+      <c r="AK1" s="127"/>
+      <c r="AL1" s="127"/>
+      <c r="AM1" s="127"/>
+      <c r="AN1" s="127"/>
+      <c r="AO1" s="127"/>
+      <c r="AP1" s="127"/>
+      <c r="AQ1" s="127"/>
+      <c r="AR1" s="127"/>
+      <c r="AS1" s="127"/>
+    </row>
+    <row r="2" spans="1:45" ht="17.399999999999999">
+      <c r="A2" s="127"/>
+      <c r="B2" s="127"/>
+      <c r="C2" s="127"/>
+      <c r="D2" s="127"/>
+      <c r="E2" s="127"/>
+      <c r="F2" s="127"/>
+      <c r="G2" s="127"/>
+      <c r="H2" s="128"/>
+      <c r="I2" s="128"/>
+      <c r="J2" s="128"/>
+      <c r="K2" s="128"/>
+      <c r="L2" s="128"/>
+      <c r="M2" s="128"/>
+      <c r="N2" s="128"/>
+      <c r="O2" s="128"/>
+      <c r="P2" s="128"/>
+      <c r="Q2" s="127"/>
+      <c r="R2" s="127"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="127"/>
+      <c r="Y2" s="127"/>
+      <c r="Z2" s="127"/>
+      <c r="AA2" s="127"/>
+      <c r="AB2" s="127"/>
+      <c r="AC2" s="127"/>
+      <c r="AD2" s="127"/>
+      <c r="AE2" s="128"/>
+      <c r="AF2" s="128"/>
+      <c r="AG2" s="128"/>
+      <c r="AH2" s="128"/>
+      <c r="AI2" s="128"/>
+      <c r="AJ2" s="128"/>
+      <c r="AK2" s="128"/>
+      <c r="AL2" s="128"/>
+      <c r="AM2" s="128"/>
+      <c r="AN2" s="127"/>
+      <c r="AO2" s="127"/>
+      <c r="AP2" s="127"/>
+      <c r="AQ2" s="127"/>
+      <c r="AR2" s="127"/>
+      <c r="AS2" s="127"/>
+    </row>
+    <row r="3" spans="1:45" ht="17.399999999999999">
+      <c r="A3" s="127"/>
+      <c r="B3" s="127"/>
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="128"/>
+      <c r="I3" s="128"/>
+      <c r="J3" s="128"/>
+      <c r="K3" s="128"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="127"/>
+      <c r="T3" s="127"/>
+      <c r="U3" s="127"/>
+      <c r="V3" s="127"/>
+      <c r="W3" s="127"/>
+      <c r="X3" s="127"/>
+      <c r="Y3" s="127"/>
+      <c r="Z3" s="127"/>
+      <c r="AA3" s="127"/>
+      <c r="AB3" s="127"/>
+      <c r="AC3" s="127"/>
+      <c r="AD3" s="127"/>
+      <c r="AE3" s="128"/>
+      <c r="AF3" s="128"/>
+      <c r="AG3" s="128"/>
+      <c r="AH3" s="128"/>
+      <c r="AI3" s="128"/>
+      <c r="AJ3" s="128"/>
+      <c r="AK3" s="128"/>
+      <c r="AL3" s="128"/>
+      <c r="AM3" s="128"/>
+      <c r="AN3" s="127"/>
+      <c r="AO3" s="127"/>
+      <c r="AP3" s="127"/>
+      <c r="AQ3" s="127"/>
+      <c r="AR3" s="127"/>
+      <c r="AS3" s="127"/>
+    </row>
+    <row r="4" spans="1:45" ht="24.6">
+      <c r="A4" s="127"/>
+      <c r="B4" s="127"/>
+      <c r="C4" s="127"/>
+      <c r="D4" s="127"/>
+      <c r="E4" s="127"/>
+      <c r="F4" s="127"/>
+      <c r="G4" s="127"/>
+      <c r="H4" s="129" t="s">
+        <v>870</v>
+      </c>
+      <c r="I4" s="128"/>
+      <c r="J4" s="128"/>
+      <c r="K4" s="128"/>
+      <c r="L4" s="128"/>
+      <c r="M4" s="128"/>
+      <c r="N4" s="128"/>
+      <c r="O4" s="128"/>
+      <c r="P4" s="128"/>
+      <c r="Q4" s="127"/>
+      <c r="R4" s="127"/>
+      <c r="S4" s="127"/>
+      <c r="T4" s="127"/>
+      <c r="U4" s="127"/>
+      <c r="V4" s="127"/>
+      <c r="W4" s="127"/>
+      <c r="X4" s="127"/>
+      <c r="Y4" s="127"/>
+      <c r="Z4" s="127"/>
+      <c r="AA4" s="127"/>
+      <c r="AB4" s="127"/>
+      <c r="AC4" s="127"/>
+      <c r="AD4" s="127"/>
+      <c r="AE4" s="129" t="s">
+        <v>870</v>
+      </c>
+      <c r="AF4" s="128"/>
+      <c r="AG4" s="128"/>
+      <c r="AH4" s="128"/>
+      <c r="AI4" s="128"/>
+      <c r="AJ4" s="128"/>
+      <c r="AK4" s="128"/>
+      <c r="AL4" s="128"/>
+      <c r="AM4" s="128"/>
+      <c r="AN4" s="127"/>
+      <c r="AO4" s="127"/>
+      <c r="AP4" s="127"/>
+      <c r="AQ4" s="127"/>
+      <c r="AR4" s="127"/>
+      <c r="AS4" s="127"/>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="A5" s="126" t="s">
+        <v>871</v>
+      </c>
+      <c r="B5" s="125" t="s">
+        <v>872</v>
+      </c>
+      <c r="C5" s="125" t="s">
+        <v>873</v>
+      </c>
+      <c r="D5" s="125" t="s">
+        <v>874</v>
+      </c>
+      <c r="E5" s="125" t="s">
+        <v>875</v>
+      </c>
+      <c r="F5" s="125" t="s">
+        <v>876</v>
+      </c>
+      <c r="G5" s="125" t="s">
+        <v>877</v>
+      </c>
+      <c r="H5" s="125" t="s">
+        <v>878</v>
+      </c>
+      <c r="I5" s="125" t="s">
+        <v>879</v>
+      </c>
+      <c r="J5" s="125" t="s">
+        <v>880</v>
+      </c>
+      <c r="K5" s="125" t="s">
+        <v>881</v>
+      </c>
+      <c r="L5" s="125" t="s">
+        <v>882</v>
+      </c>
+      <c r="M5" s="125" t="s">
+        <v>883</v>
+      </c>
+      <c r="N5" s="125" t="s">
+        <v>884</v>
+      </c>
+      <c r="O5" s="125" t="s">
+        <v>885</v>
+      </c>
+      <c r="P5" s="125" t="s">
+        <v>886</v>
+      </c>
+      <c r="Q5" s="125" t="s">
+        <v>887</v>
+      </c>
+      <c r="R5" s="125" t="s">
+        <v>888</v>
+      </c>
+      <c r="S5" s="125" t="s">
+        <v>889</v>
+      </c>
+      <c r="T5" s="125" t="s">
+        <v>890</v>
+      </c>
+      <c r="U5" s="125" t="s">
+        <v>891</v>
+      </c>
+      <c r="V5" s="125" t="s">
+        <v>892</v>
+      </c>
+      <c r="W5" s="125" t="s">
+        <v>893</v>
+      </c>
+      <c r="X5" s="125" t="s">
+        <v>894</v>
+      </c>
+      <c r="Y5" s="125" t="s">
+        <v>895</v>
+      </c>
+      <c r="Z5" s="125" t="s">
+        <v>896</v>
+      </c>
+      <c r="AA5" s="125" t="s">
+        <v>897</v>
+      </c>
+      <c r="AB5" s="125" t="s">
+        <v>898</v>
+      </c>
+      <c r="AC5" s="125" t="s">
+        <v>899</v>
+      </c>
+      <c r="AD5" s="125" t="s">
+        <v>900</v>
+      </c>
+      <c r="AE5" s="125" t="s">
+        <v>901</v>
+      </c>
+      <c r="AF5" s="125" t="s">
+        <v>902</v>
+      </c>
+      <c r="AG5" s="125"/>
+      <c r="AH5" s="125"/>
+      <c r="AI5" s="125"/>
+      <c r="AJ5" s="125"/>
+      <c r="AK5" s="125"/>
+      <c r="AL5" s="125"/>
+      <c r="AM5" s="125"/>
+      <c r="AN5" s="125"/>
+      <c r="AO5" s="125"/>
+      <c r="AP5" s="125"/>
+      <c r="AQ5" s="125"/>
+      <c r="AR5" s="125"/>
+      <c r="AS5" s="125"/>
+    </row>
+    <row r="6" spans="1:45" ht="15">
+      <c r="A6" s="124" t="s">
+        <v>903</v>
+      </c>
+      <c r="B6" s="121"/>
+      <c r="C6" s="121"/>
+      <c r="D6" s="121"/>
+      <c r="E6" s="121"/>
+    </row>
+    <row r="7" spans="1:45" ht="30">
+      <c r="A7" s="122" t="s">
+        <v>904</v>
+      </c>
+      <c r="F7" s="121"/>
+      <c r="G7" s="121"/>
+      <c r="H7" s="121"/>
+      <c r="I7" s="121"/>
+    </row>
+    <row r="8" spans="1:45" ht="15">
+      <c r="A8" s="123" t="s">
+        <v>905</v>
+      </c>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="121"/>
+    </row>
+    <row r="9" spans="1:45" ht="30">
+      <c r="A9" s="123" t="s">
+        <v>906</v>
+      </c>
+      <c r="N9" s="121"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+    </row>
+    <row r="10" spans="1:45" ht="30">
+      <c r="A10" s="123" t="s">
+        <v>907</v>
+      </c>
+      <c r="R10" s="121"/>
+      <c r="S10" s="121"/>
+      <c r="T10" s="121"/>
+      <c r="U10" s="121"/>
+      <c r="V10" s="121"/>
+      <c r="W10" s="121"/>
+    </row>
+    <row r="11" spans="1:45" ht="30">
+      <c r="A11" s="123" t="s">
+        <v>908</v>
+      </c>
+      <c r="X11" s="121"/>
+    </row>
+    <row r="12" spans="1:45" ht="30">
+      <c r="A12" s="123" t="s">
+        <v>909</v>
+      </c>
+      <c r="Y12" s="121"/>
+      <c r="Z12" s="121"/>
+    </row>
+    <row r="13" spans="1:45" ht="30">
+      <c r="A13" s="122" t="s">
+        <v>910</v>
+      </c>
+      <c r="AA13" s="121"/>
+      <c r="AB13" s="121"/>
+    </row>
+    <row r="14" spans="1:45" ht="30">
+      <c r="A14" s="122" t="s">
+        <v>911</v>
+      </c>
+      <c r="AC14" s="121"/>
+      <c r="AD14" s="121"/>
+      <c r="AE14" s="121"/>
+      <c r="AF14" s="121"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
+++ b/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hidden\Desktop\Финальный проект_АКАДЕМИЯ ТОП\Мой_ДИПЛОМНЫЙ_ПРОЕКТ\Свод(чек-лист+тест-кейс+баг-репор+автоматизация)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06239CCF-345B-4EC8-AE76-80DF2CD26DE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B96163-0C06-4F6A-9DB3-EBD7ADF29799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13476" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="912">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="917">
   <si>
     <t>Название</t>
   </si>
@@ -2486,9 +2486,6 @@
     <t>Компонент / Модуль:</t>
   </si>
   <si>
-    <t>Microsoft Edge (Версия 149.0.4022.69</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Заказать домой/ Поп-ап карточки товара.</t>
   </si>
   <si>
@@ -3260,6 +3257,24 @@
   </si>
   <si>
     <t>Составление итоговой отчётной документации (общий отчёт и специализированные приложения)</t>
+  </si>
+  <si>
+    <t>passed</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t>Major (Значительный)</t>
+  </si>
+  <si>
+    <t>Medium (Средний)</t>
+  </si>
+  <si>
+    <t>Minor (Низкий)</t>
+  </si>
+  <si>
+    <t>Advice (Рекомендации)</t>
   </si>
 </sst>
 </file>
@@ -4007,7 +4022,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4168,9 +4183,6 @@
     <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4218,13 +4230,7 @@
     <xf numFmtId="0" fontId="39" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="19" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="19" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4308,10 +4314,26 @@
     <xf numFmtId="0" fontId="55" fillId="27" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="50" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="51" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4319,33 +4341,8 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4356,13 +4353,28 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="39" fillId="19" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4383,12 +4395,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="49" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5985,6 +5991,1057 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Диаграмма прохождения тест-кейсов</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-3835-443B-8B9F-6F9B8DF789F9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+              <a:sp3d contourW="25400">
+                <a:contourClr>
+                  <a:schemeClr val="lt1"/>
+                </a:contourClr>
+              </a:sp3d>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-3835-443B-8B9F-6F9B8DF789F9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Чек-лист'!$B$227:$B$228</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Чек-лист'!$C$227:$C$228</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>372</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>72</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3835-443B-8B9F-6F9B8DF789F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Распределение дефектов по уровню критичности</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000004-648E-4211-B3B1-C211DFFBC1F1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FFFF00"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-648E-4211-B3B1-C211DFFBC1F1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-648E-4211-B3B1-C211DFFBC1F1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-648E-4211-B3B1-C211DFFBC1F1}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Чек-лист'!$B$256:$B$259</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Major (Значительный)</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Medium (Средний)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minor (Низкий)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Advice (Рекомендации)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Чек-лист'!$C$256:$C$259</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-648E-4211-B3B1-C211DFFBC1F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="60"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C458-4951-9687-1FD95A2501EC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-C458-4951-9687-1FD95A2501EC}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Чек-лист'!$B$289:$B$290</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Чек-лист'!$C$289:$C$290</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>124</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C458-4951-9687-1FD95A2501EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+      </c:pie3DChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="dk1">
@@ -6312,7 +7369,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
@@ -6874,6 +7931,123 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent4"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
@@ -7394,6 +8568,1558 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="262">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="345">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7994,7 +10720,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -8714,6 +11440,114 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>228</xdr:row>
+      <xdr:rowOff>43544</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>3984172</xdr:colOff>
+      <xdr:row>251</xdr:row>
+      <xdr:rowOff>130628</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Диаграмма 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA0B6F80-F4C6-4AB0-F1E9-A09BAD504DA6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>10885</xdr:colOff>
+      <xdr:row>259</xdr:row>
+      <xdr:rowOff>10884</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>21770</xdr:colOff>
+      <xdr:row>282</xdr:row>
+      <xdr:rowOff>54428</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Диаграмма 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F0409D1-CEA7-83EF-D589-EB02E4D43A61}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1121228</xdr:colOff>
+      <xdr:row>290</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>10886</xdr:colOff>
+      <xdr:row>310</xdr:row>
+      <xdr:rowOff>130629</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Диаграмма 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18BAD026-0B84-D506-BBB7-A715074313FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -9143,27 +11977,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="134" t="s">
+      <c r="B1" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="135"/>
-      <c r="D1" s="139" t="s">
+      <c r="C1" s="133"/>
+      <c r="D1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="140"/>
-      <c r="F1" s="135"/>
-      <c r="G1" s="141" t="s">
+      <c r="E1" s="132"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="137" t="s">
+      <c r="H1" s="127" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="55.2">
-      <c r="A2" s="133"/>
+      <c r="A2" s="138"/>
       <c r="B2" s="23" t="s">
         <v>5</v>
       </c>
@@ -9179,11 +12013,11 @@
       <c r="F2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="138"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="128"/>
     </row>
     <row r="3" spans="1:25" ht="13.8">
-      <c r="A3" s="136" t="s">
+      <c r="A3" s="129" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -9205,7 +12039,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:25" ht="13.8">
-      <c r="A4" s="131"/>
+      <c r="A4" s="130"/>
       <c r="B4" s="13" t="s">
         <v>53</v>
       </c>
@@ -9225,7 +12059,7 @@
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:25" ht="13.8">
-      <c r="A5" s="131"/>
+      <c r="A5" s="130"/>
       <c r="B5" s="13" t="s">
         <v>55</v>
       </c>
@@ -9245,7 +12079,7 @@
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:25" ht="27.6">
-      <c r="A6" s="131"/>
+      <c r="A6" s="130"/>
       <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
@@ -9265,7 +12099,7 @@
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:25" ht="27.6">
-      <c r="A7" s="131"/>
+      <c r="A7" s="130"/>
       <c r="B7" s="13" t="s">
         <v>58</v>
       </c>
@@ -9285,7 +12119,7 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:25" ht="41.4">
-      <c r="A8" s="131"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="27" t="s">
         <v>60</v>
       </c>
@@ -9305,7 +12139,7 @@
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:25" ht="55.2">
-      <c r="A9" s="131"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="13" t="s">
         <v>61</v>
       </c>
@@ -9325,7 +12159,7 @@
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:25" ht="69">
-      <c r="A10" s="131"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
@@ -9345,7 +12179,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:25" ht="55.2">
-      <c r="A11" s="131"/>
+      <c r="A11" s="130"/>
       <c r="B11" s="13" t="s">
         <v>66</v>
       </c>
@@ -9382,7 +12216,7 @@
       <c r="Y11" s="2"/>
     </row>
     <row r="12" spans="1:25" ht="55.2">
-      <c r="A12" s="131"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="13" t="s">
         <v>67</v>
       </c>
@@ -9419,7 +12253,7 @@
       <c r="Y12" s="2"/>
     </row>
     <row r="13" spans="1:25" ht="16.8" customHeight="1">
-      <c r="A13" s="136" t="s">
+      <c r="A13" s="129" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -9458,7 +12292,7 @@
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="1:25" ht="30" customHeight="1">
-      <c r="A14" s="131"/>
+      <c r="A14" s="130"/>
       <c r="B14" s="27" t="s">
         <v>71</v>
       </c>
@@ -9495,7 +12329,7 @@
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="27.6">
-      <c r="A15" s="131"/>
+      <c r="A15" s="130"/>
       <c r="B15" s="27" t="s">
         <v>424</v>
       </c>
@@ -9532,7 +12366,7 @@
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="27.6">
-      <c r="A16" s="131"/>
+      <c r="A16" s="130"/>
       <c r="B16" s="27" t="s">
         <v>426</v>
       </c>
@@ -9552,7 +12386,7 @@
       <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="41.4">
-      <c r="A17" s="131"/>
+      <c r="A17" s="130"/>
       <c r="B17" s="27" t="s">
         <v>73</v>
       </c>
@@ -9572,7 +12406,7 @@
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="41.4">
-      <c r="A18" s="131"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="27" t="s">
         <v>76</v>
       </c>
@@ -9592,7 +12426,7 @@
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="27.6">
-      <c r="A19" s="131"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="27" t="s">
         <v>79</v>
       </c>
@@ -9612,7 +12446,7 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="55.2">
-      <c r="A20" s="131"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="27" t="s">
         <v>81</v>
       </c>
@@ -9632,7 +12466,7 @@
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="92.4">
-      <c r="A21" s="131"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="27" t="s">
         <v>82</v>
       </c>
@@ -9656,7 +12490,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6">
-      <c r="A22" s="136" t="s">
+      <c r="A22" s="129" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="27" t="s">
@@ -9678,7 +12512,7 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="27.6">
-      <c r="A23" s="131"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="13" t="s">
         <v>179</v>
       </c>
@@ -9698,7 +12532,7 @@
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="27.6">
-      <c r="A24" s="131"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="13" t="s">
         <v>182</v>
       </c>
@@ -9718,7 +12552,7 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="41.4">
-      <c r="A25" s="131"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="13" t="s">
         <v>180</v>
       </c>
@@ -9742,7 +12576,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="52.8">
-      <c r="A26" s="131"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="13" t="s">
         <v>186</v>
       </c>
@@ -9766,7 +12600,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="41.4">
-      <c r="A27" s="131"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="13" t="s">
         <v>190</v>
       </c>
@@ -9786,7 +12620,7 @@
       <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="41.4">
-      <c r="A28" s="131"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="13" t="s">
         <v>192</v>
       </c>
@@ -9806,7 +12640,7 @@
       <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="27.6">
-      <c r="A29" s="131"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="13" t="s">
         <v>194</v>
       </c>
@@ -9826,7 +12660,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="27.6">
-      <c r="A30" s="131"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="13" t="s">
         <v>196</v>
       </c>
@@ -9846,7 +12680,7 @@
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="27.6">
-      <c r="A31" s="131"/>
+      <c r="A31" s="130"/>
       <c r="B31" s="13" t="s">
         <v>200</v>
       </c>
@@ -9866,7 +12700,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="52.8">
-      <c r="A32" s="131"/>
+      <c r="A32" s="130"/>
       <c r="B32" s="13" t="s">
         <v>280</v>
       </c>
@@ -9890,7 +12724,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="55.2">
-      <c r="A33" s="131"/>
+      <c r="A33" s="130"/>
       <c r="B33" s="13" t="s">
         <v>202</v>
       </c>
@@ -9910,7 +12744,7 @@
       <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="41.4">
-      <c r="A34" s="131"/>
+      <c r="A34" s="130"/>
       <c r="B34" s="13" t="s">
         <v>204</v>
       </c>
@@ -9934,7 +12768,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="27.6">
-      <c r="A35" s="136" t="s">
+      <c r="A35" s="129" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -9956,7 +12790,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="13.8">
-      <c r="A36" s="131"/>
+      <c r="A36" s="130"/>
       <c r="B36" s="13" t="s">
         <v>87</v>
       </c>
@@ -9976,7 +12810,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="79.2">
-      <c r="A37" s="131"/>
+      <c r="A37" s="130"/>
       <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
@@ -10000,7 +12834,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="76.2" customHeight="1">
-      <c r="A38" s="131"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="13" t="s">
         <v>276</v>
       </c>
@@ -10024,7 +12858,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="55.2">
-      <c r="A39" s="131"/>
+      <c r="A39" s="130"/>
       <c r="B39" s="13" t="s">
         <v>95</v>
       </c>
@@ -10044,7 +12878,7 @@
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="69">
-      <c r="A40" s="131"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="13" t="s">
         <v>97</v>
       </c>
@@ -10064,7 +12898,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="79.2">
-      <c r="A41" s="131"/>
+      <c r="A41" s="130"/>
       <c r="B41" s="13" t="s">
         <v>99</v>
       </c>
@@ -10088,7 +12922,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="69">
-      <c r="A42" s="131"/>
+      <c r="A42" s="130"/>
       <c r="B42" s="13" t="s">
         <v>104</v>
       </c>
@@ -10108,7 +12942,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="92.4">
-      <c r="A43" s="131"/>
+      <c r="A43" s="130"/>
       <c r="B43" s="13" t="s">
         <v>105</v>
       </c>
@@ -10132,7 +12966,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="27.6">
-      <c r="A44" s="131"/>
+      <c r="A44" s="130"/>
       <c r="B44" s="13" t="s">
         <v>109</v>
       </c>
@@ -10152,7 +12986,7 @@
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="27.6">
-      <c r="A45" s="131"/>
+      <c r="A45" s="130"/>
       <c r="B45" s="13" t="s">
         <v>112</v>
       </c>
@@ -10172,7 +13006,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="27.6">
-      <c r="A46" s="136" t="s">
+      <c r="A46" s="129" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -10194,7 +13028,7 @@
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="27.6">
-      <c r="A47" s="131"/>
+      <c r="A47" s="130"/>
       <c r="B47" s="13" t="s">
         <v>115</v>
       </c>
@@ -10214,7 +13048,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="66">
-      <c r="A48" s="131"/>
+      <c r="A48" s="130"/>
       <c r="B48" s="13" t="s">
         <v>273</v>
       </c>
@@ -10238,7 +13072,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="27.6">
-      <c r="A49" s="131"/>
+      <c r="A49" s="130"/>
       <c r="B49" s="13" t="s">
         <v>117</v>
       </c>
@@ -10258,7 +13092,7 @@
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" ht="27.6">
-      <c r="A50" s="131"/>
+      <c r="A50" s="130"/>
       <c r="B50" s="13" t="s">
         <v>119</v>
       </c>
@@ -10278,7 +13112,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" ht="27.6">
-      <c r="A51" s="131"/>
+      <c r="A51" s="130"/>
       <c r="B51" s="13" t="s">
         <v>121</v>
       </c>
@@ -10298,7 +13132,7 @@
       <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" ht="27.6">
-      <c r="A52" s="131"/>
+      <c r="A52" s="130"/>
       <c r="B52" s="13" t="s">
         <v>123</v>
       </c>
@@ -10318,7 +13152,7 @@
       <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="27.6">
-      <c r="A53" s="131"/>
+      <c r="A53" s="130"/>
       <c r="B53" s="13" t="s">
         <v>125</v>
       </c>
@@ -10338,7 +13172,7 @@
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" ht="27.6">
-      <c r="A54" s="131"/>
+      <c r="A54" s="130"/>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
@@ -10358,7 +13192,7 @@
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" ht="41.4">
-      <c r="A55" s="131"/>
+      <c r="A55" s="130"/>
       <c r="B55" s="13" t="s">
         <v>129</v>
       </c>
@@ -10378,7 +13212,7 @@
       <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" ht="27.6">
-      <c r="A56" s="131"/>
+      <c r="A56" s="130"/>
       <c r="B56" s="13" t="s">
         <v>130</v>
       </c>
@@ -10398,7 +13232,7 @@
       <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" ht="27.6">
-      <c r="A57" s="131"/>
+      <c r="A57" s="130"/>
       <c r="B57" s="13" t="s">
         <v>132</v>
       </c>
@@ -10418,7 +13252,7 @@
       <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8" ht="27.6">
-      <c r="A58" s="131"/>
+      <c r="A58" s="130"/>
       <c r="B58" s="13" t="s">
         <v>134</v>
       </c>
@@ -10438,7 +13272,7 @@
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8" ht="41.4">
-      <c r="A59" s="131"/>
+      <c r="A59" s="130"/>
       <c r="B59" s="13" t="s">
         <v>136</v>
       </c>
@@ -10458,7 +13292,7 @@
       <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" ht="41.4">
-      <c r="A60" s="131"/>
+      <c r="A60" s="130"/>
       <c r="B60" s="13" t="s">
         <v>137</v>
       </c>
@@ -10478,7 +13312,7 @@
       <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A61" s="131"/>
+      <c r="A61" s="130"/>
       <c r="B61" s="13" t="s">
         <v>138</v>
       </c>
@@ -10498,7 +13332,7 @@
       <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8" ht="27.6">
-      <c r="A62" s="131"/>
+      <c r="A62" s="130"/>
       <c r="B62" s="13" t="s">
         <v>140</v>
       </c>
@@ -10518,7 +13352,7 @@
       <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8" ht="27.6">
-      <c r="A63" s="131"/>
+      <c r="A63" s="130"/>
       <c r="B63" s="13" t="s">
         <v>142</v>
       </c>
@@ -10538,7 +13372,7 @@
       <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8" ht="27.6">
-      <c r="A64" s="131"/>
+      <c r="A64" s="130"/>
       <c r="B64" s="13" t="s">
         <v>144</v>
       </c>
@@ -10558,7 +13392,7 @@
       <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:14" ht="52.2" customHeight="1">
-      <c r="A65" s="131"/>
+      <c r="A65" s="130"/>
       <c r="B65" s="13" t="s">
         <v>282</v>
       </c>
@@ -10582,7 +13416,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="41.4">
-      <c r="A66" s="131"/>
+      <c r="A66" s="130"/>
       <c r="B66" s="13" t="s">
         <v>147</v>
       </c>
@@ -10602,7 +13436,7 @@
       <c r="H66" s="16"/>
     </row>
     <row r="67" spans="1:14" ht="27.6">
-      <c r="A67" s="131"/>
+      <c r="A67" s="130"/>
       <c r="B67" s="13" t="s">
         <v>151</v>
       </c>
@@ -10622,7 +13456,7 @@
       <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:14" ht="27.6">
-      <c r="A68" s="131"/>
+      <c r="A68" s="130"/>
       <c r="B68" s="13" t="s">
         <v>149</v>
       </c>
@@ -10642,7 +13476,7 @@
       <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:14" ht="55.2">
-      <c r="A69" s="136" t="s">
+      <c r="A69" s="129" t="s">
         <v>208</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -10664,7 +13498,7 @@
       <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:14" ht="42" customHeight="1">
-      <c r="A70" s="131"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="21" t="s">
         <v>211</v>
       </c>
@@ -10689,7 +13523,7 @@
       <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A71" s="131"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="21" t="s">
         <v>213</v>
       </c>
@@ -10714,7 +13548,7 @@
       <c r="N71" s="4"/>
     </row>
     <row r="72" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A72" s="131"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="21" t="s">
         <v>215</v>
       </c>
@@ -10739,7 +13573,7 @@
       <c r="N72" s="4"/>
     </row>
     <row r="73" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A73" s="131"/>
+      <c r="A73" s="130"/>
       <c r="B73" s="21" t="s">
         <v>217</v>
       </c>
@@ -10764,7 +13598,7 @@
       <c r="N73" s="4"/>
     </row>
     <row r="74" spans="1:14" ht="63.6" customHeight="1">
-      <c r="A74" s="131"/>
+      <c r="A74" s="130"/>
       <c r="B74" s="21" t="s">
         <v>219</v>
       </c>
@@ -10789,7 +13623,7 @@
       <c r="N74" s="4"/>
     </row>
     <row r="75" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A75" s="131"/>
+      <c r="A75" s="130"/>
       <c r="B75" s="21" t="s">
         <v>221</v>
       </c>
@@ -10814,7 +13648,7 @@
       <c r="N75" s="4"/>
     </row>
     <row r="76" spans="1:14" ht="54.6" customHeight="1">
-      <c r="A76" s="131"/>
+      <c r="A76" s="130"/>
       <c r="B76" s="21" t="s">
         <v>223</v>
       </c>
@@ -10839,7 +13673,7 @@
       <c r="N76" s="4"/>
     </row>
     <row r="77" spans="1:14" ht="42" customHeight="1">
-      <c r="A77" s="131"/>
+      <c r="A77" s="130"/>
       <c r="B77" s="21" t="s">
         <v>225</v>
       </c>
@@ -10864,7 +13698,7 @@
       <c r="N77" s="4"/>
     </row>
     <row r="78" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A78" s="131"/>
+      <c r="A78" s="130"/>
       <c r="B78" s="21" t="s">
         <v>227</v>
       </c>
@@ -10889,7 +13723,7 @@
       <c r="N78" s="4"/>
     </row>
     <row r="79" spans="1:14" ht="42.6" customHeight="1">
-      <c r="A79" s="131"/>
+      <c r="A79" s="130"/>
       <c r="B79" s="21" t="s">
         <v>229</v>
       </c>
@@ -10914,7 +13748,7 @@
       <c r="N79" s="4"/>
     </row>
     <row r="80" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A80" s="131"/>
+      <c r="A80" s="130"/>
       <c r="B80" s="21" t="s">
         <v>231</v>
       </c>
@@ -10939,7 +13773,7 @@
       <c r="N80" s="4"/>
     </row>
     <row r="81" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A81" s="131"/>
+      <c r="A81" s="130"/>
       <c r="B81" s="21" t="s">
         <v>233</v>
       </c>
@@ -10964,7 +13798,7 @@
       <c r="N81" s="4"/>
     </row>
     <row r="82" spans="1:14" ht="42" customHeight="1">
-      <c r="A82" s="131"/>
+      <c r="A82" s="130"/>
       <c r="B82" s="21" t="s">
         <v>235</v>
       </c>
@@ -10993,7 +13827,7 @@
       <c r="N82" s="4"/>
     </row>
     <row r="83" spans="1:14" ht="42" customHeight="1">
-      <c r="A83" s="131"/>
+      <c r="A83" s="130"/>
       <c r="B83" s="21" t="s">
         <v>239</v>
       </c>
@@ -11022,7 +13856,7 @@
       <c r="N83" s="4"/>
     </row>
     <row r="84" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A84" s="131"/>
+      <c r="A84" s="130"/>
       <c r="B84" s="21" t="s">
         <v>243</v>
       </c>
@@ -11051,7 +13885,7 @@
       <c r="N84" s="4"/>
     </row>
     <row r="85" spans="1:14" ht="70.2" customHeight="1">
-      <c r="A85" s="131"/>
+      <c r="A85" s="130"/>
       <c r="B85" s="21" t="s">
         <v>245</v>
       </c>
@@ -11080,7 +13914,7 @@
       <c r="N85" s="4"/>
     </row>
     <row r="86" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A86" s="131"/>
+      <c r="A86" s="130"/>
       <c r="B86" s="21" t="s">
         <v>252</v>
       </c>
@@ -11109,7 +13943,7 @@
       <c r="N86" s="4"/>
     </row>
     <row r="87" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A87" s="131"/>
+      <c r="A87" s="130"/>
       <c r="B87" s="21" t="s">
         <v>255</v>
       </c>
@@ -11138,7 +13972,7 @@
       <c r="N87" s="4"/>
     </row>
     <row r="88" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A88" s="131"/>
+      <c r="A88" s="130"/>
       <c r="B88" s="21" t="s">
         <v>258</v>
       </c>
@@ -11163,7 +13997,7 @@
       <c r="N88" s="4"/>
     </row>
     <row r="89" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A89" s="131"/>
+      <c r="A89" s="130"/>
       <c r="B89" s="21" t="s">
         <v>260</v>
       </c>
@@ -11192,7 +14026,7 @@
       <c r="N89" s="4"/>
     </row>
     <row r="90" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A90" s="131"/>
+      <c r="A90" s="130"/>
       <c r="B90" s="21" t="s">
         <v>265</v>
       </c>
@@ -11217,7 +14051,7 @@
       <c r="N90" s="4"/>
     </row>
     <row r="91" spans="1:14" ht="56.4" customHeight="1">
-      <c r="A91" s="131"/>
+      <c r="A91" s="130"/>
       <c r="B91" s="21" t="s">
         <v>269</v>
       </c>
@@ -11246,7 +14080,7 @@
       <c r="N91" s="4"/>
     </row>
     <row r="92" spans="1:14" ht="42" customHeight="1">
-      <c r="A92" s="136" t="s">
+      <c r="A92" s="129" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="27" t="s">
@@ -11273,7 +14107,7 @@
       <c r="N92" s="4"/>
     </row>
     <row r="93" spans="1:14" s="63" customFormat="1" ht="27.6">
-      <c r="A93" s="131"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="27" t="s">
         <v>160</v>
       </c>
@@ -11295,7 +14129,7 @@
       <c r="K93" s="64"/>
     </row>
     <row r="94" spans="1:14" ht="61.2" customHeight="1">
-      <c r="A94" s="131"/>
+      <c r="A94" s="130"/>
       <c r="B94" s="27" t="s">
         <v>586</v>
       </c>
@@ -11320,7 +14154,7 @@
       <c r="N94" s="2"/>
     </row>
     <row r="95" spans="1:14" ht="27.6">
-      <c r="A95" s="131"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="27" t="s">
         <v>161</v>
       </c>
@@ -11345,7 +14179,7 @@
       <c r="N95" s="2"/>
     </row>
     <row r="96" spans="1:14" ht="27.6">
-      <c r="A96" s="131"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="21" t="s">
         <v>155</v>
       </c>
@@ -11370,7 +14204,7 @@
       <c r="N96" s="2"/>
     </row>
     <row r="97" spans="1:14" ht="41.4">
-      <c r="A97" s="131"/>
+      <c r="A97" s="130"/>
       <c r="B97" s="21" t="s">
         <v>156</v>
       </c>
@@ -11395,7 +14229,7 @@
       <c r="N97" s="2"/>
     </row>
     <row r="98" spans="1:14" ht="41.4">
-      <c r="A98" s="131"/>
+      <c r="A98" s="130"/>
       <c r="B98" s="21" t="s">
         <v>158</v>
       </c>
@@ -11420,7 +14254,7 @@
       <c r="N98" s="2"/>
     </row>
     <row r="99" spans="1:14" ht="41.4">
-      <c r="A99" s="131"/>
+      <c r="A99" s="130"/>
       <c r="B99" s="27" t="s">
         <v>162</v>
       </c>
@@ -11445,7 +14279,7 @@
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" ht="41.4">
-      <c r="A100" s="131"/>
+      <c r="A100" s="130"/>
       <c r="B100" s="27" t="s">
         <v>164</v>
       </c>
@@ -11470,7 +14304,7 @@
       <c r="N100" s="2"/>
     </row>
     <row r="101" spans="1:14" ht="39" customHeight="1">
-      <c r="A101" s="131"/>
+      <c r="A101" s="130"/>
       <c r="B101" s="27" t="s">
         <v>587</v>
       </c>
@@ -11495,7 +14329,7 @@
       <c r="N101" s="2"/>
     </row>
     <row r="102" spans="1:14" ht="41.4">
-      <c r="A102" s="131"/>
+      <c r="A102" s="130"/>
       <c r="B102" s="27" t="s">
         <v>166</v>
       </c>
@@ -11520,12 +14354,12 @@
       <c r="N102" s="2"/>
     </row>
     <row r="103" spans="1:14" s="63" customFormat="1" ht="69.599999999999994" customHeight="1">
-      <c r="A103" s="131"/>
+      <c r="A103" s="130"/>
       <c r="B103" s="27" t="s">
         <v>168</v>
       </c>
       <c r="C103" s="27" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D103" s="60" t="s">
         <v>27</v>
@@ -11545,7 +14379,7 @@
       <c r="N103" s="65"/>
     </row>
     <row r="104" spans="1:14" ht="27.6">
-      <c r="A104" s="131"/>
+      <c r="A104" s="130"/>
       <c r="B104" s="21" t="s">
         <v>169</v>
       </c>
@@ -11570,7 +14404,7 @@
       <c r="N104" s="2"/>
     </row>
     <row r="105" spans="1:14" ht="55.2">
-      <c r="A105" s="131"/>
+      <c r="A105" s="130"/>
       <c r="B105" s="21" t="s">
         <v>171</v>
       </c>
@@ -11595,7 +14429,7 @@
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A106" s="131"/>
+      <c r="A106" s="130"/>
       <c r="B106" s="27" t="s">
         <v>600</v>
       </c>
@@ -11620,7 +14454,7 @@
       <c r="N106" s="2"/>
     </row>
     <row r="107" spans="1:14" ht="55.2">
-      <c r="A107" s="131"/>
+      <c r="A107" s="130"/>
       <c r="B107" s="21" t="s">
         <v>173</v>
       </c>
@@ -11645,7 +14479,7 @@
       <c r="N107" s="2"/>
     </row>
     <row r="108" spans="1:14" ht="69">
-      <c r="A108" s="131"/>
+      <c r="A108" s="130"/>
       <c r="B108" s="27" t="s">
         <v>175</v>
       </c>
@@ -11670,7 +14504,7 @@
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" ht="61.8" customHeight="1">
-      <c r="A109" s="130" t="s">
+      <c r="A109" s="136" t="s">
         <v>14</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -11697,7 +14531,7 @@
       <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" ht="60" customHeight="1">
-      <c r="A110" s="131"/>
+      <c r="A110" s="130"/>
       <c r="B110" s="21" t="s">
         <v>288</v>
       </c>
@@ -11726,7 +14560,7 @@
       <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" ht="63" customHeight="1">
-      <c r="A111" s="131"/>
+      <c r="A111" s="130"/>
       <c r="B111" s="21" t="s">
         <v>292</v>
       </c>
@@ -11751,7 +14585,7 @@
       <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" ht="74.400000000000006" customHeight="1">
-      <c r="A112" s="131"/>
+      <c r="A112" s="130"/>
       <c r="B112" s="21" t="s">
         <v>294</v>
       </c>
@@ -11780,7 +14614,7 @@
       <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A113" s="131"/>
+      <c r="A113" s="130"/>
       <c r="B113" s="21" t="s">
         <v>299</v>
       </c>
@@ -11805,7 +14639,7 @@
       <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" ht="41.4">
-      <c r="A114" s="131"/>
+      <c r="A114" s="130"/>
       <c r="B114" s="21" t="s">
         <v>300</v>
       </c>
@@ -11830,7 +14664,7 @@
       <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A115" s="131"/>
+      <c r="A115" s="130"/>
       <c r="B115" s="21" t="s">
         <v>302</v>
       </c>
@@ -11855,7 +14689,7 @@
       <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A116" s="131"/>
+      <c r="A116" s="130"/>
       <c r="B116" s="21" t="s">
         <v>304</v>
       </c>
@@ -11880,7 +14714,7 @@
       <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A117" s="131"/>
+      <c r="A117" s="130"/>
       <c r="B117" s="21" t="s">
         <v>306</v>
       </c>
@@ -11905,7 +14739,7 @@
       <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" ht="77.400000000000006" customHeight="1">
-      <c r="A118" s="131"/>
+      <c r="A118" s="130"/>
       <c r="B118" s="21" t="s">
         <v>308</v>
       </c>
@@ -11934,7 +14768,7 @@
       <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" ht="65.400000000000006" customHeight="1">
-      <c r="A119" s="131"/>
+      <c r="A119" s="130"/>
       <c r="B119" s="21" t="s">
         <v>312</v>
       </c>
@@ -11959,7 +14793,7 @@
       <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" ht="60.6" customHeight="1">
-      <c r="A120" s="131"/>
+      <c r="A120" s="130"/>
       <c r="B120" s="21" t="s">
         <v>314</v>
       </c>
@@ -11984,7 +14818,7 @@
       <c r="N120" s="4"/>
     </row>
     <row r="121" spans="1:14" ht="40.200000000000003" customHeight="1">
-      <c r="A121" s="131"/>
+      <c r="A121" s="130"/>
       <c r="B121" s="21" t="s">
         <v>316</v>
       </c>
@@ -12009,7 +14843,7 @@
       <c r="N121" s="4"/>
     </row>
     <row r="122" spans="1:14" ht="69">
-      <c r="A122" s="131"/>
+      <c r="A122" s="130"/>
       <c r="B122" s="21" t="s">
         <v>318</v>
       </c>
@@ -12034,7 +14868,7 @@
       <c r="N122" s="4"/>
     </row>
     <row r="123" spans="1:14" ht="60" customHeight="1">
-      <c r="A123" s="131"/>
+      <c r="A123" s="130"/>
       <c r="B123" s="21" t="s">
         <v>320</v>
       </c>
@@ -12059,7 +14893,7 @@
       <c r="N123" s="4"/>
     </row>
     <row r="124" spans="1:14" ht="69">
-      <c r="A124" s="131"/>
+      <c r="A124" s="130"/>
       <c r="B124" s="21" t="s">
         <v>322</v>
       </c>
@@ -12084,7 +14918,7 @@
       <c r="N124" s="4"/>
     </row>
     <row r="125" spans="1:14" ht="67.8" customHeight="1">
-      <c r="A125" s="131"/>
+      <c r="A125" s="130"/>
       <c r="B125" s="27" t="s">
         <v>324</v>
       </c>
@@ -12123,7 +14957,7 @@
     <row r="128" spans="1:14" ht="16.8">
       <c r="A128" s="26"/>
       <c r="B128" s="35" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C128" s="33">
         <v>444</v>
@@ -12619,10 +15453,22 @@
     </row>
     <row r="227" spans="1:7" ht="13.2">
       <c r="A227" s="26"/>
+      <c r="B227" t="s">
+        <v>911</v>
+      </c>
+      <c r="C227">
+        <v>372</v>
+      </c>
       <c r="G227" s="4"/>
     </row>
     <row r="228" spans="1:7" ht="13.2">
       <c r="A228" s="26"/>
+      <c r="B228" t="s">
+        <v>912</v>
+      </c>
+      <c r="C228">
+        <v>72</v>
+      </c>
       <c r="G228" s="4"/>
     </row>
     <row r="229" spans="1:7" ht="13.2">
@@ -12735,18 +15581,42 @@
     </row>
     <row r="256" spans="1:7" ht="13.2">
       <c r="A256" s="26"/>
+      <c r="B256" t="s">
+        <v>913</v>
+      </c>
+      <c r="C256">
+        <v>3</v>
+      </c>
       <c r="G256" s="4"/>
     </row>
     <row r="257" spans="1:7" ht="13.2">
       <c r="A257" s="26"/>
+      <c r="B257" t="s">
+        <v>914</v>
+      </c>
+      <c r="C257">
+        <v>10</v>
+      </c>
       <c r="G257" s="4"/>
     </row>
     <row r="258" spans="1:7" ht="13.2">
       <c r="A258" s="26"/>
+      <c r="B258" t="s">
+        <v>915</v>
+      </c>
+      <c r="C258">
+        <v>5</v>
+      </c>
       <c r="G258" s="4"/>
     </row>
     <row r="259" spans="1:7" ht="13.2">
       <c r="A259" s="26"/>
+      <c r="B259" t="s">
+        <v>916</v>
+      </c>
+      <c r="C259">
+        <v>5</v>
+      </c>
       <c r="G259" s="4"/>
     </row>
     <row r="260" spans="1:7" ht="13.2">
@@ -12867,10 +15737,22 @@
     </row>
     <row r="289" spans="1:7" ht="13.2">
       <c r="A289" s="26"/>
+      <c r="B289" t="s">
+        <v>27</v>
+      </c>
+      <c r="C289">
+        <v>124</v>
+      </c>
       <c r="G289" s="4"/>
     </row>
     <row r="290" spans="1:7" ht="13.2">
       <c r="A290" s="26"/>
+      <c r="B290" t="s">
+        <v>49</v>
+      </c>
+      <c r="C290">
+        <v>24</v>
+      </c>
       <c r="G290" s="4"/>
     </row>
     <row r="291" spans="1:7" ht="13.2">
@@ -15035,12 +17917,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A92:A108"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A109:A125"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -15048,6 +17924,12 @@
     <mergeCell ref="A35:A45"/>
     <mergeCell ref="A46:A68"/>
     <mergeCell ref="A69:A91"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A92:A108"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:F1048576 C2">
@@ -15101,44 +17983,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="151" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="148" t="s">
+      <c r="B1" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="151" t="s">
         <v>367</v>
       </c>
-      <c r="D1" s="148" t="s">
+      <c r="D1" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="148" t="s">
+      <c r="E1" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="148" t="s">
+      <c r="F1" s="151" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="148" t="s">
-        <v>836</v>
-      </c>
-      <c r="H1" s="143" t="s">
+      <c r="G1" s="151" t="s">
+        <v>835</v>
+      </c>
+      <c r="H1" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="144"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="146" t="s">
+      <c r="I1" s="149"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="140" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6">
-      <c r="A2" s="147"/>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
       <c r="H2" s="36" t="s">
         <v>21</v>
       </c>
@@ -15148,10 +18030,10 @@
       <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="147"/>
+      <c r="K2" s="146"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="152" t="s">
+      <c r="A3" s="144" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -15184,7 +18066,7 @@
       <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A4" s="153"/>
+      <c r="A4" s="145"/>
       <c r="B4" s="38" t="s">
         <v>336</v>
       </c>
@@ -15215,7 +18097,7 @@
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="153"/>
+      <c r="A5" s="145"/>
       <c r="B5" s="38" t="s">
         <v>337</v>
       </c>
@@ -15246,7 +18128,7 @@
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="153"/>
+      <c r="A6" s="145"/>
       <c r="B6" s="38" t="s">
         <v>338</v>
       </c>
@@ -15277,7 +18159,7 @@
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="153"/>
+      <c r="A7" s="145"/>
       <c r="B7" s="38" t="s">
         <v>339</v>
       </c>
@@ -15308,7 +18190,7 @@
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="153"/>
+      <c r="A8" s="145"/>
       <c r="B8" s="38" t="s">
         <v>340</v>
       </c>
@@ -15339,7 +18221,7 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="147"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="38" t="s">
         <v>341</v>
       </c>
@@ -15370,7 +18252,7 @@
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="152" t="s">
+      <c r="A10" s="144" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -15403,7 +18285,7 @@
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="153"/>
+      <c r="A11" s="145"/>
       <c r="B11" s="38" t="s">
         <v>343</v>
       </c>
@@ -15434,7 +18316,7 @@
       <c r="K11" s="41"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="153"/>
+      <c r="A12" s="145"/>
       <c r="B12" s="38" t="s">
         <v>344</v>
       </c>
@@ -15465,7 +18347,7 @@
       <c r="K12" s="41"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="153"/>
+      <c r="A13" s="145"/>
       <c r="B13" s="38" t="s">
         <v>345</v>
       </c>
@@ -15496,7 +18378,7 @@
       <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="153"/>
+      <c r="A14" s="145"/>
       <c r="B14" s="38" t="s">
         <v>346</v>
       </c>
@@ -15527,7 +18409,7 @@
       <c r="K14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="153"/>
+      <c r="A15" s="145"/>
       <c r="B15" s="38" t="s">
         <v>347</v>
       </c>
@@ -15558,7 +18440,7 @@
       <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="153"/>
+      <c r="A16" s="145"/>
       <c r="B16" s="38" t="s">
         <v>348</v>
       </c>
@@ -15589,7 +18471,7 @@
       <c r="K16" s="41"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="153"/>
+      <c r="A17" s="145"/>
       <c r="B17" s="38" t="s">
         <v>349</v>
       </c>
@@ -15622,7 +18504,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="153"/>
+      <c r="A18" s="145"/>
       <c r="B18" s="38" t="s">
         <v>436</v>
       </c>
@@ -15653,7 +18535,7 @@
       <c r="K18" s="41"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="147"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="38" t="s">
         <v>437</v>
       </c>
@@ -15684,7 +18566,7 @@
       <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A20" s="152" t="s">
+      <c r="A20" s="144" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -15717,7 +18599,7 @@
       <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="153"/>
+      <c r="A21" s="145"/>
       <c r="B21" s="38" t="s">
         <v>351</v>
       </c>
@@ -15748,7 +18630,7 @@
       <c r="K21" s="41"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A22" s="153"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="38" t="s">
         <v>352</v>
       </c>
@@ -15781,7 +18663,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="153"/>
+      <c r="A23" s="145"/>
       <c r="B23" s="38" t="s">
         <v>353</v>
       </c>
@@ -15814,7 +18696,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A24" s="153"/>
+      <c r="A24" s="145"/>
       <c r="B24" s="38" t="s">
         <v>446</v>
       </c>
@@ -15845,7 +18727,7 @@
       <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A25" s="153"/>
+      <c r="A25" s="145"/>
       <c r="B25" s="38" t="s">
         <v>354</v>
       </c>
@@ -15876,7 +18758,7 @@
       <c r="K25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A26" s="153"/>
+      <c r="A26" s="145"/>
       <c r="B26" s="38" t="s">
         <v>355</v>
       </c>
@@ -15907,7 +18789,7 @@
       <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A27" s="153"/>
+      <c r="A27" s="145"/>
       <c r="B27" s="38" t="s">
         <v>356</v>
       </c>
@@ -15940,7 +18822,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="153"/>
+      <c r="A28" s="145"/>
       <c r="B28" s="38" t="s">
         <v>357</v>
       </c>
@@ -15973,7 +18855,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="153"/>
+      <c r="A29" s="145"/>
       <c r="B29" s="38" t="s">
         <v>389</v>
       </c>
@@ -16004,7 +18886,7 @@
       <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="153"/>
+      <c r="A30" s="145"/>
       <c r="B30" s="38" t="s">
         <v>390</v>
       </c>
@@ -16035,7 +18917,7 @@
       <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="85.8" customHeight="1">
-      <c r="A31" s="154" t="s">
+      <c r="A31" s="147" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
@@ -16068,7 +18950,7 @@
       <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="55.2">
-      <c r="A32" s="153"/>
+      <c r="A32" s="145"/>
       <c r="B32" s="38" t="s">
         <v>451</v>
       </c>
@@ -16101,7 +18983,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="82.8">
-      <c r="A33" s="153"/>
+      <c r="A33" s="145"/>
       <c r="B33" s="38" t="s">
         <v>452</v>
       </c>
@@ -16134,7 +19016,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="96.6">
-      <c r="A34" s="153"/>
+      <c r="A34" s="145"/>
       <c r="B34" s="38" t="s">
         <v>453</v>
       </c>
@@ -16165,7 +19047,7 @@
       <c r="K34" s="41"/>
     </row>
     <row r="35" spans="1:11" ht="82.8">
-      <c r="A35" s="153"/>
+      <c r="A35" s="145"/>
       <c r="B35" s="38" t="s">
         <v>454</v>
       </c>
@@ -16198,7 +19080,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="69">
-      <c r="A36" s="153"/>
+      <c r="A36" s="145"/>
       <c r="B36" s="38" t="s">
         <v>455</v>
       </c>
@@ -16229,7 +19111,7 @@
       <c r="K36" s="41"/>
     </row>
     <row r="37" spans="1:11" ht="57" customHeight="1">
-      <c r="A37" s="153"/>
+      <c r="A37" s="145"/>
       <c r="B37" s="38" t="s">
         <v>456</v>
       </c>
@@ -16262,7 +19144,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="72" customHeight="1">
-      <c r="A38" s="153"/>
+      <c r="A38" s="145"/>
       <c r="B38" s="38" t="s">
         <v>473</v>
       </c>
@@ -16293,7 +19175,7 @@
       <c r="K38" s="41"/>
     </row>
     <row r="39" spans="1:11" ht="92.4">
-      <c r="A39" s="152" t="s">
+      <c r="A39" s="144" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -16326,7 +19208,7 @@
       <c r="K39" s="41"/>
     </row>
     <row r="40" spans="1:11" ht="110.4">
-      <c r="A40" s="153"/>
+      <c r="A40" s="145"/>
       <c r="B40" s="38" t="s">
         <v>482</v>
       </c>
@@ -16357,7 +19239,7 @@
       <c r="K40" s="41"/>
     </row>
     <row r="41" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A41" s="153"/>
+      <c r="A41" s="145"/>
       <c r="B41" s="38" t="s">
         <v>483</v>
       </c>
@@ -16388,7 +19270,7 @@
       <c r="K41" s="41"/>
     </row>
     <row r="42" spans="1:11" ht="61.2" customHeight="1">
-      <c r="A42" s="153"/>
+      <c r="A42" s="145"/>
       <c r="B42" s="38" t="s">
         <v>484</v>
       </c>
@@ -16419,7 +19301,7 @@
       <c r="K42" s="41"/>
     </row>
     <row r="43" spans="1:11" ht="69" customHeight="1">
-      <c r="A43" s="153"/>
+      <c r="A43" s="145"/>
       <c r="B43" s="38" t="s">
         <v>485</v>
       </c>
@@ -16450,7 +19332,7 @@
       <c r="K43" s="41"/>
     </row>
     <row r="44" spans="1:11" ht="73.8" customHeight="1">
-      <c r="A44" s="153"/>
+      <c r="A44" s="145"/>
       <c r="B44" s="38" t="s">
         <v>486</v>
       </c>
@@ -16481,7 +19363,7 @@
       <c r="K44" s="41"/>
     </row>
     <row r="45" spans="1:11" ht="85.2" customHeight="1">
-      <c r="A45" s="153"/>
+      <c r="A45" s="145"/>
       <c r="B45" s="38" t="s">
         <v>487</v>
       </c>
@@ -16512,7 +19394,7 @@
       <c r="K45" s="41"/>
     </row>
     <row r="46" spans="1:11" ht="70.8" customHeight="1">
-      <c r="A46" s="153"/>
+      <c r="A46" s="145"/>
       <c r="B46" s="38" t="s">
         <v>488</v>
       </c>
@@ -16545,7 +19427,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="99" customHeight="1">
-      <c r="A47" s="153"/>
+      <c r="A47" s="145"/>
       <c r="B47" s="38" t="s">
         <v>510</v>
       </c>
@@ -16578,7 +19460,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="92.4" customHeight="1">
-      <c r="A48" s="153"/>
+      <c r="A48" s="145"/>
       <c r="B48" s="38" t="s">
         <v>513</v>
       </c>
@@ -16609,7 +19491,7 @@
       <c r="K48" s="41"/>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1">
-      <c r="A49" s="147"/>
+      <c r="A49" s="146"/>
       <c r="B49" s="38" t="s">
         <v>514</v>
       </c>
@@ -16640,7 +19522,7 @@
       <c r="K49" s="41"/>
     </row>
     <row r="50" spans="1:11" ht="82.8">
-      <c r="A50" s="152" t="s">
+      <c r="A50" s="144" t="s">
         <v>208</v>
       </c>
       <c r="B50" s="38" t="s">
@@ -16673,7 +19555,7 @@
       <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A51" s="153"/>
+      <c r="A51" s="145"/>
       <c r="B51" s="38" t="s">
         <v>522</v>
       </c>
@@ -16704,7 +19586,7 @@
       <c r="K51" s="41"/>
     </row>
     <row r="52" spans="1:11" ht="96.6">
-      <c r="A52" s="153"/>
+      <c r="A52" s="145"/>
       <c r="B52" s="38" t="s">
         <v>523</v>
       </c>
@@ -16735,7 +19617,7 @@
       <c r="K52" s="41"/>
     </row>
     <row r="53" spans="1:11" ht="82.2" customHeight="1">
-      <c r="A53" s="153"/>
+      <c r="A53" s="145"/>
       <c r="B53" s="38" t="s">
         <v>524</v>
       </c>
@@ -16766,7 +19648,7 @@
       <c r="K53" s="44"/>
     </row>
     <row r="54" spans="1:11" ht="82.8">
-      <c r="A54" s="153"/>
+      <c r="A54" s="145"/>
       <c r="B54" s="38" t="s">
         <v>525</v>
       </c>
@@ -16799,7 +19681,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="55.2">
-      <c r="A55" s="153"/>
+      <c r="A55" s="145"/>
       <c r="B55" s="38" t="s">
         <v>526</v>
       </c>
@@ -16832,7 +19714,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="41.4">
-      <c r="A56" s="153"/>
+      <c r="A56" s="145"/>
       <c r="B56" s="38" t="s">
         <v>527</v>
       </c>
@@ -16865,7 +19747,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="55.8">
-      <c r="A57" s="153"/>
+      <c r="A57" s="145"/>
       <c r="B57" s="38" t="s">
         <v>528</v>
       </c>
@@ -16898,7 +19780,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="82.8">
-      <c r="A58" s="153"/>
+      <c r="A58" s="145"/>
       <c r="B58" s="38" t="s">
         <v>529</v>
       </c>
@@ -16929,7 +19811,7 @@
       <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" ht="82.8">
-      <c r="A59" s="153"/>
+      <c r="A59" s="145"/>
       <c r="B59" s="38" t="s">
         <v>530</v>
       </c>
@@ -16962,7 +19844,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="55.2">
-      <c r="A60" s="153"/>
+      <c r="A60" s="145"/>
       <c r="B60" s="38" t="s">
         <v>531</v>
       </c>
@@ -16993,7 +19875,7 @@
       <c r="K60" s="41"/>
     </row>
     <row r="61" spans="1:11" ht="69">
-      <c r="A61" s="153"/>
+      <c r="A61" s="145"/>
       <c r="B61" s="38" t="s">
         <v>532</v>
       </c>
@@ -17026,7 +19908,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" ht="69.599999999999994">
-      <c r="A62" s="153"/>
+      <c r="A62" s="145"/>
       <c r="B62" s="38" t="s">
         <v>533</v>
       </c>
@@ -17057,7 +19939,7 @@
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11" ht="117.6" customHeight="1">
-      <c r="A63" s="153"/>
+      <c r="A63" s="145"/>
       <c r="B63" s="38" t="s">
         <v>534</v>
       </c>
@@ -17088,7 +19970,7 @@
       <c r="K63" s="41"/>
     </row>
     <row r="64" spans="1:11" ht="83.4">
-      <c r="A64" s="152" t="s">
+      <c r="A64" s="144" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -17121,7 +20003,7 @@
       <c r="K64" s="41"/>
     </row>
     <row r="65" spans="1:27" ht="69.599999999999994">
-      <c r="A65" s="153"/>
+      <c r="A65" s="145"/>
       <c r="B65" s="38" t="s">
         <v>574</v>
       </c>
@@ -17168,7 +20050,7 @@
       <c r="AA65" s="2"/>
     </row>
     <row r="66" spans="1:27" ht="83.4">
-      <c r="A66" s="153"/>
+      <c r="A66" s="145"/>
       <c r="B66" s="38" t="s">
         <v>575</v>
       </c>
@@ -17215,7 +20097,7 @@
       <c r="AA66" s="2"/>
     </row>
     <row r="67" spans="1:27" ht="104.4" customHeight="1">
-      <c r="A67" s="153"/>
+      <c r="A67" s="145"/>
       <c r="B67" s="38" t="s">
         <v>576</v>
       </c>
@@ -17262,7 +20144,7 @@
       <c r="AA67" s="2"/>
     </row>
     <row r="68" spans="1:27" ht="75" customHeight="1">
-      <c r="A68" s="153"/>
+      <c r="A68" s="145"/>
       <c r="B68" s="38" t="s">
         <v>577</v>
       </c>
@@ -17309,7 +20191,7 @@
       <c r="AA68" s="2"/>
     </row>
     <row r="69" spans="1:27" ht="83.4">
-      <c r="A69" s="153"/>
+      <c r="A69" s="145"/>
       <c r="B69" s="38" t="s">
         <v>578</v>
       </c>
@@ -17356,7 +20238,7 @@
       <c r="AA69" s="2"/>
     </row>
     <row r="70" spans="1:27" ht="42">
-      <c r="A70" s="153"/>
+      <c r="A70" s="145"/>
       <c r="B70" s="38" t="s">
         <v>579</v>
       </c>
@@ -17403,7 +20285,7 @@
       <c r="AA70" s="2"/>
     </row>
     <row r="71" spans="1:27" ht="78">
-      <c r="A71" s="153"/>
+      <c r="A71" s="145"/>
       <c r="B71" s="38" t="s">
         <v>580</v>
       </c>
@@ -17450,7 +20332,7 @@
       <c r="AA71" s="2"/>
     </row>
     <row r="72" spans="1:27" ht="78">
-      <c r="A72" s="153"/>
+      <c r="A72" s="145"/>
       <c r="B72" s="38" t="s">
         <v>581</v>
       </c>
@@ -17481,7 +20363,7 @@
       <c r="K72" s="41"/>
     </row>
     <row r="73" spans="1:27" ht="94.8" customHeight="1">
-      <c r="A73" s="146" t="s">
+      <c r="A73" s="140" t="s">
         <v>14</v>
       </c>
       <c r="B73" s="38" t="s">
@@ -17514,7 +20396,7 @@
       <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:27" ht="75">
-      <c r="A74" s="149"/>
+      <c r="A74" s="141"/>
       <c r="B74" s="38" t="s">
         <v>621</v>
       </c>
@@ -17547,7 +20429,7 @@
       </c>
     </row>
     <row r="75" spans="1:27" ht="75">
-      <c r="A75" s="149"/>
+      <c r="A75" s="141"/>
       <c r="B75" s="38" t="s">
         <v>622</v>
       </c>
@@ -17580,7 +20462,7 @@
       </c>
     </row>
     <row r="76" spans="1:27" ht="79.2" customHeight="1">
-      <c r="A76" s="149"/>
+      <c r="A76" s="141"/>
       <c r="B76" s="38" t="s">
         <v>623</v>
       </c>
@@ -17611,7 +20493,7 @@
       <c r="K76" s="41"/>
     </row>
     <row r="77" spans="1:27" ht="69" customHeight="1">
-      <c r="A77" s="149"/>
+      <c r="A77" s="141"/>
       <c r="B77" s="38" t="s">
         <v>633</v>
       </c>
@@ -17642,7 +20524,7 @@
       <c r="K77" s="41"/>
     </row>
     <row r="78" spans="1:27" ht="69" customHeight="1">
-      <c r="A78" s="149"/>
+      <c r="A78" s="141"/>
       <c r="B78" s="38" t="s">
         <v>637</v>
       </c>
@@ -17673,7 +20555,7 @@
       <c r="K78" s="41"/>
     </row>
     <row r="79" spans="1:27" ht="69" customHeight="1">
-      <c r="A79" s="149"/>
+      <c r="A79" s="141"/>
       <c r="B79" s="38" t="s">
         <v>641</v>
       </c>
@@ -17706,7 +20588,7 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="75" customHeight="1">
-      <c r="A80" s="149"/>
+      <c r="A80" s="141"/>
       <c r="B80" s="38" t="s">
         <v>645</v>
       </c>
@@ -17737,7 +20619,7 @@
       <c r="K80" s="41"/>
     </row>
     <row r="81" spans="1:11" ht="93" customHeight="1">
-      <c r="A81" s="149"/>
+      <c r="A81" s="141"/>
       <c r="B81" s="38" t="s">
         <v>649</v>
       </c>
@@ -17768,7 +20650,7 @@
       <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A82" s="149"/>
+      <c r="A82" s="141"/>
       <c r="B82" s="38" t="s">
         <v>653</v>
       </c>
@@ -17799,7 +20681,7 @@
       <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" ht="110.4" customHeight="1">
-      <c r="A83" s="149"/>
+      <c r="A83" s="141"/>
       <c r="B83" s="38" t="s">
         <v>657</v>
       </c>
@@ -17830,7 +20712,7 @@
       <c r="K83" s="41"/>
     </row>
     <row r="84" spans="1:11" ht="109.2" customHeight="1">
-      <c r="A84" s="149"/>
+      <c r="A84" s="141"/>
       <c r="B84" s="38" t="s">
         <v>661</v>
       </c>
@@ -17861,7 +20743,7 @@
       <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" ht="67.8" customHeight="1">
-      <c r="A85" s="149"/>
+      <c r="A85" s="141"/>
       <c r="B85" s="38" t="s">
         <v>665</v>
       </c>
@@ -17902,8 +20784,8 @@
     </row>
     <row r="88" spans="1:11" ht="13.2">
       <c r="A88" s="37"/>
-      <c r="B88" s="150"/>
-      <c r="C88" s="151"/>
+      <c r="B88" s="142"/>
+      <c r="C88" s="143"/>
       <c r="D88" s="10"/>
     </row>
     <row r="89" spans="1:11" ht="13.2">
@@ -17918,20 +20800,20 @@
     </row>
     <row r="91" spans="1:11" ht="13.2">
       <c r="A91" s="37"/>
-      <c r="B91" s="100" t="s">
+      <c r="B91" s="97" t="s">
         <v>669</v>
       </c>
-      <c r="C91" s="100">
+      <c r="C91" s="97">
         <f>COUNTA(H2:J34)</f>
         <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="13.2">
       <c r="A92" s="37"/>
-      <c r="B92" s="100" t="s">
+      <c r="B92" s="97" t="s">
         <v>328</v>
       </c>
-      <c r="C92" s="100">
+      <c r="C92" s="97">
         <f>COUNTIF(H2:J34, "Passed")</f>
         <v>75</v>
       </c>
@@ -20861,6 +23743,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A73:A85"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="A3:A9"/>
@@ -20870,15 +23761,6 @@
     <mergeCell ref="A39:A49"/>
     <mergeCell ref="A50:A63"/>
     <mergeCell ref="A64:A72"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
@@ -20921,1032 +23803,948 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661A785B-8B38-43CF-98A8-58AC29FD88EC}">
-  <dimension ref="A1:L1009"/>
+  <dimension ref="A1:K1009"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3" style="73" customWidth="1"/>
-    <col min="2" max="2" width="20.77734375" style="73" customWidth="1"/>
-    <col min="3" max="3" width="31.88671875" style="73" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="73" customWidth="1"/>
-    <col min="5" max="5" width="45.109375" style="73" customWidth="1"/>
-    <col min="6" max="6" width="39.88671875" style="73" customWidth="1"/>
-    <col min="7" max="7" width="30.88671875" style="73" customWidth="1"/>
-    <col min="8" max="8" width="30.6640625" style="73" customWidth="1"/>
-    <col min="9" max="9" width="16.5546875" style="73" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" style="73" customWidth="1"/>
-    <col min="11" max="11" width="18" style="73" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" style="73" customWidth="1"/>
-    <col min="13" max="23" width="8.6640625" style="73" customWidth="1"/>
-    <col min="24" max="16384" width="14.44140625" style="73"/>
+    <col min="1" max="1" width="3" style="72" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" style="72" customWidth="1"/>
+    <col min="3" max="3" width="31.88671875" style="72" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="72" customWidth="1"/>
+    <col min="5" max="5" width="45.109375" style="72" customWidth="1"/>
+    <col min="6" max="6" width="39.88671875" style="72" customWidth="1"/>
+    <col min="7" max="7" width="30.88671875" style="72" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" style="72" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" style="72" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="72" customWidth="1"/>
+    <col min="11" max="11" width="18" style="72" customWidth="1"/>
+    <col min="12" max="22" width="8.6640625" style="72" customWidth="1"/>
+    <col min="23" max="16384" width="14.44140625" style="72"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.4" customHeight="1">
-      <c r="A1" s="155" t="s">
+    <row r="1" spans="1:11" ht="14.4" customHeight="1">
+      <c r="A1" s="152" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="71"/>
-      <c r="C1" s="155" t="s">
+      <c r="C1" s="152" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="165" t="s">
+      <c r="D1" s="154" t="s">
         <v>704</v>
       </c>
-      <c r="E1" s="155" t="s">
+      <c r="E1" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="155" t="s">
+      <c r="F1" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="155" t="s">
+      <c r="G1" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="155" t="s">
+      <c r="H1" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="159" t="s">
+      <c r="I1" s="158" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="160"/>
-      <c r="K1" s="160"/>
-      <c r="L1" s="72" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="42">
-      <c r="A2" s="156"/>
+      <c r="J1" s="159"/>
+      <c r="K1" s="159"/>
+    </row>
+    <row r="2" spans="1:11" ht="55.8">
+      <c r="A2" s="153"/>
       <c r="B2" s="71" t="s">
         <v>705</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="166"/>
-      <c r="E2" s="156"/>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-      <c r="I2" s="74" t="s">
+      <c r="C2" s="153"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="73" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="74" t="s">
+      <c r="J2" s="73" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="74" t="s">
+      <c r="K2" s="73" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="74" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="95.4" customHeight="1">
+      <c r="A3" s="74">
+        <v>1</v>
+      </c>
+      <c r="B3" s="75" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="95.4" customHeight="1">
-      <c r="A3" s="75">
+      <c r="C3" s="76" t="s">
+        <v>707</v>
+      </c>
+      <c r="D3" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E3" s="78" t="s">
+        <v>708</v>
+      </c>
+      <c r="F3" s="76" t="s">
+        <v>709</v>
+      </c>
+      <c r="G3" s="76" t="s">
+        <v>710</v>
+      </c>
+      <c r="H3" s="79" t="s">
+        <v>711</v>
+      </c>
+      <c r="I3" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="80" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" s="80" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="118.2" customHeight="1">
+      <c r="A4" s="74">
+        <v>2</v>
+      </c>
+      <c r="B4" s="81" t="s">
+        <v>712</v>
+      </c>
+      <c r="C4" s="76" t="s">
+        <v>713</v>
+      </c>
+      <c r="D4" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E4" s="78" t="s">
+        <v>714</v>
+      </c>
+      <c r="F4" s="76" t="s">
+        <v>715</v>
+      </c>
+      <c r="G4" s="76" t="s">
+        <v>716</v>
+      </c>
+      <c r="H4" s="79" t="s">
+        <v>717</v>
+      </c>
+      <c r="I4" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="J4" s="80" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="80" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="159" customHeight="1">
+      <c r="A5" s="74">
+        <v>3</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>718</v>
+      </c>
+      <c r="C5" s="76" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E5" s="82" t="s">
+        <v>720</v>
+      </c>
+      <c r="F5" s="76" t="s">
+        <v>721</v>
+      </c>
+      <c r="G5" s="76" t="s">
+        <v>722</v>
+      </c>
+      <c r="H5" s="82" t="s">
+        <v>723</v>
+      </c>
+      <c r="I5" s="80" t="s">
+        <v>247</v>
+      </c>
+      <c r="J5" s="80" t="s">
+        <v>247</v>
+      </c>
+      <c r="K5" s="80" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="124.8">
+      <c r="A6" s="74">
+        <v>4</v>
+      </c>
+      <c r="B6" s="83" t="s">
+        <v>724</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>725</v>
+      </c>
+      <c r="D6" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="84" t="s">
+        <v>726</v>
+      </c>
+      <c r="F6" s="76" t="s">
+        <v>727</v>
+      </c>
+      <c r="G6" s="76" t="s">
+        <v>728</v>
+      </c>
+      <c r="H6" s="79" t="s">
+        <v>729</v>
+      </c>
+      <c r="I6" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="J6" s="80" t="s">
+        <v>251</v>
+      </c>
+      <c r="K6" s="80" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="126.6" customHeight="1">
+      <c r="A7" s="85">
+        <v>5</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>730</v>
+      </c>
+      <c r="C7" s="87" t="s">
+        <v>731</v>
+      </c>
+      <c r="D7" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>732</v>
+      </c>
+      <c r="F7" s="87" t="s">
+        <v>733</v>
+      </c>
+      <c r="G7" s="87" t="s">
+        <v>734</v>
+      </c>
+      <c r="H7" s="82" t="s">
+        <v>735</v>
+      </c>
+      <c r="I7" s="88" t="s">
+        <v>241</v>
+      </c>
+      <c r="J7" s="88" t="s">
+        <v>241</v>
+      </c>
+      <c r="K7" s="88" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="83.4">
+      <c r="A8" s="74">
+        <v>6</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" s="76" t="s">
+        <v>737</v>
+      </c>
+      <c r="D8" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="79" t="s">
+        <v>738</v>
+      </c>
+      <c r="F8" s="76" t="s">
+        <v>739</v>
+      </c>
+      <c r="G8" s="76" t="s">
+        <v>740</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>741</v>
+      </c>
+      <c r="I8" s="80" t="s">
+        <v>254</v>
+      </c>
+      <c r="J8" s="80" t="s">
+        <v>254</v>
+      </c>
+      <c r="K8" s="80" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="118.2" customHeight="1">
+      <c r="A9" s="74">
+        <v>7</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>742</v>
+      </c>
+      <c r="C9" s="76" t="s">
+        <v>743</v>
+      </c>
+      <c r="D9" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="79" t="s">
+        <v>744</v>
+      </c>
+      <c r="F9" s="76" t="s">
+        <v>745</v>
+      </c>
+      <c r="G9" s="76" t="s">
+        <v>746</v>
+      </c>
+      <c r="H9" s="82" t="s">
+        <v>747</v>
+      </c>
+      <c r="I9" s="80" t="s">
+        <v>262</v>
+      </c>
+      <c r="J9" s="80" t="s">
+        <v>262</v>
+      </c>
+      <c r="K9" s="80" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="94.8" customHeight="1">
+      <c r="A10" s="74">
+        <v>8</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>748</v>
+      </c>
+      <c r="C10" s="76" t="s">
+        <v>749</v>
+      </c>
+      <c r="D10" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E10" s="79" t="s">
+        <v>750</v>
+      </c>
+      <c r="F10" s="76" t="s">
+        <v>751</v>
+      </c>
+      <c r="G10" s="76" t="s">
+        <v>752</v>
+      </c>
+      <c r="H10" s="79" t="s">
+        <v>753</v>
+      </c>
+      <c r="I10" s="80" t="s">
+        <v>267</v>
+      </c>
+      <c r="J10" s="80" t="s">
+        <v>267</v>
+      </c>
+      <c r="K10" s="80" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="175.2" customHeight="1">
+      <c r="A11" s="74">
+        <v>9</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>754</v>
+      </c>
+      <c r="C11" s="76" t="s">
+        <v>755</v>
+      </c>
+      <c r="D11" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>756</v>
+      </c>
+      <c r="F11" s="76" t="s">
+        <v>757</v>
+      </c>
+      <c r="G11" s="76" t="s">
+        <v>758</v>
+      </c>
+      <c r="H11" s="79" t="s">
+        <v>759</v>
+      </c>
+      <c r="I11" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="J11" s="80" t="s">
+        <v>272</v>
+      </c>
+      <c r="K11" s="80" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="172.8" customHeight="1">
+      <c r="A12" s="74">
+        <v>10</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>760</v>
+      </c>
+      <c r="C12" s="76" t="s">
+        <v>761</v>
+      </c>
+      <c r="D12" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>762</v>
+      </c>
+      <c r="F12" s="76" t="s">
+        <v>763</v>
+      </c>
+      <c r="G12" s="76" t="s">
+        <v>764</v>
+      </c>
+      <c r="H12" s="79" t="s">
+        <v>765</v>
+      </c>
+      <c r="I12" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="80" t="s">
+        <v>108</v>
+      </c>
+      <c r="K12" s="80" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="120" customHeight="1">
+      <c r="A13" s="74">
+        <v>11</v>
+      </c>
+      <c r="B13" s="81" t="s">
+        <v>766</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>767</v>
+      </c>
+      <c r="D13" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>768</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>769</v>
+      </c>
+      <c r="G13" s="76" t="s">
+        <v>770</v>
+      </c>
+      <c r="H13" s="79" t="s">
+        <v>771</v>
+      </c>
+      <c r="I13" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="J13" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="80" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="92.4" customHeight="1">
+      <c r="A14" s="74">
+        <v>12</v>
+      </c>
+      <c r="B14" s="81" t="s">
+        <v>766</v>
+      </c>
+      <c r="C14" s="76" t="s">
+        <v>772</v>
+      </c>
+      <c r="D14" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E14" s="79" t="s">
+        <v>773</v>
+      </c>
+      <c r="F14" s="76" t="s">
+        <v>774</v>
+      </c>
+      <c r="G14" s="76" t="s">
+        <v>775</v>
+      </c>
+      <c r="H14" s="79" t="s">
+        <v>776</v>
+      </c>
+      <c r="I14" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="K14" s="80" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="157.19999999999999" customHeight="1">
+      <c r="A15" s="74">
+        <v>13</v>
+      </c>
+      <c r="B15" s="81" t="s">
+        <v>777</v>
+      </c>
+      <c r="C15" s="76" t="s">
+        <v>778</v>
+      </c>
+      <c r="D15" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E15" s="79" t="s">
+        <v>779</v>
+      </c>
+      <c r="F15" s="76" t="s">
+        <v>780</v>
+      </c>
+      <c r="G15" s="76" t="s">
+        <v>781</v>
+      </c>
+      <c r="H15" s="79" t="s">
+        <v>782</v>
+      </c>
+      <c r="I15" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="J15" s="80" t="s">
+        <v>199</v>
+      </c>
+      <c r="K15" s="80" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="104.4" customHeight="1">
+      <c r="A16" s="74">
+        <v>14</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>783</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>784</v>
+      </c>
+      <c r="D16" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="79" t="s">
+        <v>785</v>
+      </c>
+      <c r="F16" s="76" t="s">
+        <v>786</v>
+      </c>
+      <c r="G16" s="76" t="s">
+        <v>787</v>
+      </c>
+      <c r="H16" s="79" t="s">
+        <v>788</v>
+      </c>
+      <c r="I16" s="80" t="s">
+        <v>206</v>
+      </c>
+      <c r="J16" s="80" t="s">
+        <v>206</v>
+      </c>
+      <c r="K16" s="80" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="115.8" customHeight="1">
+      <c r="A17" s="74">
+        <v>15</v>
+      </c>
+      <c r="B17" s="81" t="s">
+        <v>789</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>790</v>
+      </c>
+      <c r="D17" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>791</v>
+      </c>
+      <c r="F17" s="76" t="s">
+        <v>792</v>
+      </c>
+      <c r="G17" s="76" t="s">
+        <v>793</v>
+      </c>
+      <c r="H17" s="79" t="s">
+        <v>794</v>
+      </c>
+      <c r="I17" s="80" t="s">
+        <v>249</v>
+      </c>
+      <c r="J17" s="80" t="s">
+        <v>249</v>
+      </c>
+      <c r="K17" s="80" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="117" customHeight="1">
+      <c r="A18" s="74">
+        <v>16</v>
+      </c>
+      <c r="B18" s="81" t="s">
+        <v>795</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>796</v>
+      </c>
+      <c r="D18" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="79" t="s">
+        <v>797</v>
+      </c>
+      <c r="F18" s="76" t="s">
+        <v>277</v>
+      </c>
+      <c r="G18" s="76" t="s">
+        <v>278</v>
+      </c>
+      <c r="H18" s="79" t="s">
+        <v>798</v>
+      </c>
+      <c r="I18" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="J18" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="K18" s="80" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="117" customHeight="1">
+      <c r="A19" s="74">
+        <v>17</v>
+      </c>
+      <c r="B19" s="81" t="s">
+        <v>799</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>800</v>
+      </c>
+      <c r="D19" s="77" t="s">
+        <v>694</v>
+      </c>
+      <c r="E19" s="79" t="s">
+        <v>801</v>
+      </c>
+      <c r="F19" s="76" t="s">
+        <v>289</v>
+      </c>
+      <c r="G19" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="H19" s="79" t="s">
+        <v>802</v>
+      </c>
+      <c r="I19" s="80" t="s">
+        <v>291</v>
+      </c>
+      <c r="J19" s="80" t="s">
+        <v>291</v>
+      </c>
+      <c r="K19" s="80" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="133.19999999999999" customHeight="1">
+      <c r="A20" s="74">
+        <v>18</v>
+      </c>
+      <c r="B20" s="81" t="s">
+        <v>803</v>
+      </c>
+      <c r="C20" s="76" t="s">
+        <v>804</v>
+      </c>
+      <c r="D20" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="82" t="s">
+        <v>805</v>
+      </c>
+      <c r="F20" s="76" t="s">
+        <v>309</v>
+      </c>
+      <c r="G20" s="76" t="s">
+        <v>310</v>
+      </c>
+      <c r="H20" s="79" t="s">
+        <v>806</v>
+      </c>
+      <c r="I20" s="80" t="s">
+        <v>311</v>
+      </c>
+      <c r="J20" s="80" t="s">
+        <v>311</v>
+      </c>
+      <c r="K20" s="80" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="62.4" customHeight="1">
+      <c r="A21" s="160" t="s">
+        <v>842</v>
+      </c>
+      <c r="B21" s="160"/>
+      <c r="C21" s="160"/>
+      <c r="D21" s="160"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="160"/>
+      <c r="G21" s="160"/>
+      <c r="H21" s="160"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="160"/>
+      <c r="K21" s="160"/>
+    </row>
+    <row r="22" spans="1:11" ht="14.4">
+      <c r="A22" s="161" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="89"/>
+      <c r="C22" s="161" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="161" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="161" t="s">
+        <v>807</v>
+      </c>
+      <c r="F22" s="161" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="161" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="162" t="s">
+        <v>45</v>
+      </c>
+      <c r="I22" s="156" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="157"/>
+      <c r="K22" s="157"/>
+    </row>
+    <row r="23" spans="1:11" ht="55.2">
+      <c r="A23" s="153"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="163"/>
+      <c r="I23" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="90" t="s">
+        <v>47</v>
+      </c>
+      <c r="K23" s="90" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="178.2" customHeight="1">
+      <c r="A24" s="91">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="s">
-        <v>707</v>
-      </c>
-      <c r="C3" s="77" t="s">
-        <v>708</v>
-      </c>
-      <c r="D3" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E3" s="79" t="s">
-        <v>709</v>
-      </c>
-      <c r="F3" s="77" t="s">
-        <v>710</v>
-      </c>
-      <c r="G3" s="77" t="s">
-        <v>711</v>
-      </c>
-      <c r="H3" s="80" t="s">
-        <v>712</v>
-      </c>
-      <c r="I3" s="81" t="s">
-        <v>102</v>
-      </c>
-      <c r="J3" s="81" t="s">
-        <v>102</v>
-      </c>
-      <c r="K3" s="81" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="81" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="118.2" customHeight="1">
-      <c r="A4" s="75">
+      <c r="B24" s="91"/>
+      <c r="C24" s="92" t="s">
+        <v>808</v>
+      </c>
+      <c r="D24" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="92" t="s">
+        <v>809</v>
+      </c>
+      <c r="F24" s="91" t="s">
+        <v>810</v>
+      </c>
+      <c r="G24" s="92" t="s">
+        <v>811</v>
+      </c>
+      <c r="H24" s="92" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" s="93" t="s">
+        <v>812</v>
+      </c>
+      <c r="J24" s="93" t="s">
+        <v>812</v>
+      </c>
+      <c r="K24" s="93" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="115.8" customHeight="1">
+      <c r="A25" s="91">
         <v>2</v>
       </c>
-      <c r="B4" s="82" t="s">
-        <v>713</v>
-      </c>
-      <c r="C4" s="77" t="s">
-        <v>714</v>
-      </c>
-      <c r="D4" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E4" s="79" t="s">
-        <v>715</v>
-      </c>
-      <c r="F4" s="77" t="s">
-        <v>716</v>
-      </c>
-      <c r="G4" s="77" t="s">
-        <v>717</v>
-      </c>
-      <c r="H4" s="80" t="s">
-        <v>718</v>
-      </c>
-      <c r="I4" s="81" t="s">
-        <v>237</v>
-      </c>
-      <c r="J4" s="81" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" s="81" t="s">
-        <v>237</v>
-      </c>
-      <c r="L4" s="81" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="159" customHeight="1">
-      <c r="A5" s="75">
+      <c r="B25" s="91"/>
+      <c r="C25" s="94" t="s">
+        <v>813</v>
+      </c>
+      <c r="D25" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="92" t="s">
+        <v>814</v>
+      </c>
+      <c r="F25" s="92" t="s">
+        <v>815</v>
+      </c>
+      <c r="G25" s="92" t="s">
+        <v>816</v>
+      </c>
+      <c r="H25" s="92" t="s">
+        <v>817</v>
+      </c>
+      <c r="I25" s="93" t="s">
+        <v>818</v>
+      </c>
+      <c r="J25" s="93" t="s">
+        <v>818</v>
+      </c>
+      <c r="K25" s="93" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="118.2" customHeight="1">
+      <c r="A26" s="91">
         <v>3</v>
       </c>
-      <c r="B5" s="82" t="s">
-        <v>719</v>
-      </c>
-      <c r="C5" s="77" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E5" s="83" t="s">
-        <v>721</v>
-      </c>
-      <c r="F5" s="77" t="s">
-        <v>722</v>
-      </c>
-      <c r="G5" s="77" t="s">
-        <v>723</v>
-      </c>
-      <c r="H5" s="83" t="s">
-        <v>724</v>
-      </c>
-      <c r="I5" s="81" t="s">
-        <v>247</v>
-      </c>
-      <c r="J5" s="81" t="s">
-        <v>247</v>
-      </c>
-      <c r="K5" s="81" t="s">
-        <v>247</v>
-      </c>
-      <c r="L5" s="81" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="115.2">
-      <c r="A6" s="75">
+      <c r="B26" s="91"/>
+      <c r="C26" s="92" t="s">
+        <v>819</v>
+      </c>
+      <c r="D26" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="95" t="s">
+        <v>820</v>
+      </c>
+      <c r="F26" s="92" t="s">
+        <v>821</v>
+      </c>
+      <c r="G26" s="92" t="s">
+        <v>822</v>
+      </c>
+      <c r="H26" s="92" t="s">
+        <v>823</v>
+      </c>
+      <c r="I26" s="93" t="s">
+        <v>824</v>
+      </c>
+      <c r="J26" s="93" t="s">
+        <v>824</v>
+      </c>
+      <c r="K26" s="93" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="109.2" customHeight="1">
+      <c r="A27" s="91">
         <v>4</v>
       </c>
-      <c r="B6" s="84" t="s">
-        <v>725</v>
-      </c>
-      <c r="C6" s="77" t="s">
-        <v>726</v>
-      </c>
-      <c r="D6" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="85" t="s">
-        <v>727</v>
-      </c>
-      <c r="F6" s="77" t="s">
-        <v>728</v>
-      </c>
-      <c r="G6" s="77" t="s">
-        <v>729</v>
-      </c>
-      <c r="H6" s="80" t="s">
-        <v>730</v>
-      </c>
-      <c r="I6" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="J6" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="K6" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="L6" s="81" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="126.6" customHeight="1">
-      <c r="A7" s="86">
+      <c r="B27" s="91"/>
+      <c r="C27" s="92" t="s">
+        <v>825</v>
+      </c>
+      <c r="D27" s="92" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="92" t="s">
+        <v>826</v>
+      </c>
+      <c r="F27" s="94" t="s">
+        <v>827</v>
+      </c>
+      <c r="G27" s="92" t="s">
+        <v>828</v>
+      </c>
+      <c r="H27" s="92" t="s">
+        <v>829</v>
+      </c>
+      <c r="I27" s="93" t="s">
+        <v>830</v>
+      </c>
+      <c r="J27" s="93" t="s">
+        <v>830</v>
+      </c>
+      <c r="K27" s="93" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="115.8" customHeight="1">
+      <c r="A28" s="91">
         <v>5</v>
       </c>
-      <c r="B7" s="87" t="s">
-        <v>731</v>
-      </c>
-      <c r="C7" s="88" t="s">
-        <v>732</v>
-      </c>
-      <c r="D7" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E7" s="83" t="s">
-        <v>733</v>
-      </c>
-      <c r="F7" s="88" t="s">
-        <v>734</v>
-      </c>
-      <c r="G7" s="88" t="s">
-        <v>735</v>
-      </c>
-      <c r="H7" s="83" t="s">
-        <v>736</v>
-      </c>
-      <c r="I7" s="89" t="s">
-        <v>241</v>
-      </c>
-      <c r="J7" s="89" t="s">
-        <v>241</v>
-      </c>
-      <c r="K7" s="89" t="s">
-        <v>241</v>
-      </c>
-      <c r="L7" s="89" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="83.4">
-      <c r="A8" s="75">
-        <v>6</v>
-      </c>
-      <c r="B8" s="82" t="s">
-        <v>737</v>
-      </c>
-      <c r="C8" s="77" t="s">
-        <v>738</v>
-      </c>
-      <c r="D8" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="80" t="s">
-        <v>739</v>
-      </c>
-      <c r="F8" s="77" t="s">
-        <v>740</v>
-      </c>
-      <c r="G8" s="77" t="s">
-        <v>741</v>
-      </c>
-      <c r="H8" s="83" t="s">
-        <v>742</v>
-      </c>
-      <c r="I8" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="J8" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="K8" s="81" t="s">
-        <v>254</v>
-      </c>
-      <c r="L8" s="81" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="118.2" customHeight="1">
-      <c r="A9" s="75">
-        <v>7</v>
-      </c>
-      <c r="B9" s="82" t="s">
-        <v>743</v>
-      </c>
-      <c r="C9" s="77" t="s">
-        <v>744</v>
-      </c>
-      <c r="D9" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="80" t="s">
-        <v>745</v>
-      </c>
-      <c r="F9" s="77" t="s">
-        <v>746</v>
-      </c>
-      <c r="G9" s="77" t="s">
-        <v>747</v>
-      </c>
-      <c r="H9" s="83" t="s">
-        <v>748</v>
-      </c>
-      <c r="I9" s="81" t="s">
-        <v>262</v>
-      </c>
-      <c r="J9" s="81" t="s">
-        <v>262</v>
-      </c>
-      <c r="K9" s="81" t="s">
-        <v>262</v>
-      </c>
-      <c r="L9" s="81" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="94.8" customHeight="1">
-      <c r="A10" s="75">
-        <v>8</v>
-      </c>
-      <c r="B10" s="82" t="s">
-        <v>749</v>
-      </c>
-      <c r="C10" s="77" t="s">
-        <v>750</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E10" s="80" t="s">
-        <v>751</v>
-      </c>
-      <c r="F10" s="77" t="s">
-        <v>752</v>
-      </c>
-      <c r="G10" s="77" t="s">
-        <v>753</v>
-      </c>
-      <c r="H10" s="80" t="s">
-        <v>754</v>
-      </c>
-      <c r="I10" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="J10" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="K10" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="L10" s="81" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="175.2" customHeight="1">
-      <c r="A11" s="75">
-        <v>9</v>
-      </c>
-      <c r="B11" s="82" t="s">
-        <v>755</v>
-      </c>
-      <c r="C11" s="77" t="s">
-        <v>756</v>
-      </c>
-      <c r="D11" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E11" s="80" t="s">
-        <v>757</v>
-      </c>
-      <c r="F11" s="77" t="s">
-        <v>758</v>
-      </c>
-      <c r="G11" s="77" t="s">
-        <v>759</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>760</v>
-      </c>
-      <c r="I11" s="81" t="s">
-        <v>272</v>
-      </c>
-      <c r="J11" s="81" t="s">
-        <v>272</v>
-      </c>
-      <c r="K11" s="81" t="s">
-        <v>272</v>
-      </c>
-      <c r="L11" s="81" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="172.8" customHeight="1">
-      <c r="A12" s="75">
-        <v>10</v>
-      </c>
-      <c r="B12" s="82" t="s">
-        <v>761</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>762</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E12" s="80" t="s">
-        <v>763</v>
-      </c>
-      <c r="F12" s="77" t="s">
-        <v>764</v>
-      </c>
-      <c r="G12" s="77" t="s">
-        <v>765</v>
-      </c>
-      <c r="H12" s="80" t="s">
-        <v>766</v>
-      </c>
-      <c r="I12" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="J12" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="K12" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="L12" s="81" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="120" customHeight="1">
-      <c r="A13" s="75">
-        <v>11</v>
-      </c>
-      <c r="B13" s="82" t="s">
-        <v>767</v>
-      </c>
-      <c r="C13" s="77" t="s">
-        <v>768</v>
-      </c>
-      <c r="D13" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="80" t="s">
-        <v>769</v>
-      </c>
-      <c r="F13" s="77" t="s">
-        <v>770</v>
-      </c>
-      <c r="G13" s="77" t="s">
-        <v>771</v>
-      </c>
-      <c r="H13" s="80" t="s">
-        <v>772</v>
-      </c>
-      <c r="I13" s="81" t="s">
-        <v>184</v>
-      </c>
-      <c r="J13" s="81" t="s">
-        <v>184</v>
-      </c>
-      <c r="K13" s="81" t="s">
-        <v>184</v>
-      </c>
-      <c r="L13" s="81" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="92.4" customHeight="1">
-      <c r="A14" s="75">
-        <v>12</v>
-      </c>
-      <c r="B14" s="82" t="s">
-        <v>767</v>
-      </c>
-      <c r="C14" s="77" t="s">
-        <v>773</v>
-      </c>
-      <c r="D14" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E14" s="80" t="s">
-        <v>774</v>
-      </c>
-      <c r="F14" s="77" t="s">
-        <v>775</v>
-      </c>
-      <c r="G14" s="77" t="s">
-        <v>776</v>
-      </c>
-      <c r="H14" s="80" t="s">
-        <v>777</v>
-      </c>
-      <c r="I14" s="81" t="s">
-        <v>187</v>
-      </c>
-      <c r="J14" s="81" t="s">
-        <v>187</v>
-      </c>
-      <c r="K14" s="81" t="s">
-        <v>187</v>
-      </c>
-      <c r="L14" s="81" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="157.19999999999999" customHeight="1">
-      <c r="A15" s="75">
-        <v>13</v>
-      </c>
-      <c r="B15" s="82" t="s">
-        <v>778</v>
-      </c>
-      <c r="C15" s="77" t="s">
-        <v>779</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>780</v>
-      </c>
-      <c r="F15" s="77" t="s">
-        <v>781</v>
-      </c>
-      <c r="G15" s="77" t="s">
-        <v>782</v>
-      </c>
-      <c r="H15" s="80" t="s">
-        <v>783</v>
-      </c>
-      <c r="I15" s="81" t="s">
-        <v>199</v>
-      </c>
-      <c r="J15" s="81" t="s">
-        <v>199</v>
-      </c>
-      <c r="K15" s="81" t="s">
-        <v>199</v>
-      </c>
-      <c r="L15" s="81" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="104.4" customHeight="1">
-      <c r="A16" s="75">
-        <v>14</v>
-      </c>
-      <c r="B16" s="82" t="s">
-        <v>784</v>
-      </c>
-      <c r="C16" s="77" t="s">
-        <v>785</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="80" t="s">
-        <v>786</v>
-      </c>
-      <c r="F16" s="77" t="s">
-        <v>787</v>
-      </c>
-      <c r="G16" s="77" t="s">
-        <v>788</v>
-      </c>
-      <c r="H16" s="80" t="s">
-        <v>789</v>
-      </c>
-      <c r="I16" s="81" t="s">
-        <v>206</v>
-      </c>
-      <c r="J16" s="81" t="s">
-        <v>206</v>
-      </c>
-      <c r="K16" s="81" t="s">
-        <v>206</v>
-      </c>
-      <c r="L16" s="81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="115.8" customHeight="1">
-      <c r="A17" s="75">
-        <v>15</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>790</v>
-      </c>
-      <c r="C17" s="77" t="s">
-        <v>791</v>
-      </c>
-      <c r="D17" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E17" s="80" t="s">
-        <v>792</v>
-      </c>
-      <c r="F17" s="77" t="s">
-        <v>793</v>
-      </c>
-      <c r="G17" s="77" t="s">
-        <v>794</v>
-      </c>
-      <c r="H17" s="80" t="s">
-        <v>795</v>
-      </c>
-      <c r="I17" s="81" t="s">
-        <v>249</v>
-      </c>
-      <c r="J17" s="81" t="s">
-        <v>249</v>
-      </c>
-      <c r="K17" s="81" t="s">
-        <v>249</v>
-      </c>
-      <c r="L17" s="81" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="117" customHeight="1">
-      <c r="A18" s="75">
-        <v>16</v>
-      </c>
-      <c r="B18" s="82" t="s">
-        <v>796</v>
-      </c>
-      <c r="C18" s="77" t="s">
-        <v>797</v>
-      </c>
-      <c r="D18" s="78" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="80" t="s">
-        <v>798</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>277</v>
-      </c>
-      <c r="G18" s="77" t="s">
-        <v>278</v>
-      </c>
-      <c r="H18" s="80" t="s">
-        <v>799</v>
-      </c>
-      <c r="I18" s="81" t="s">
-        <v>279</v>
-      </c>
-      <c r="J18" s="81" t="s">
-        <v>279</v>
-      </c>
-      <c r="K18" s="81" t="s">
-        <v>279</v>
-      </c>
-      <c r="L18" s="81" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="117" customHeight="1">
-      <c r="A19" s="75">
-        <v>17</v>
-      </c>
-      <c r="B19" s="82" t="s">
-        <v>800</v>
-      </c>
-      <c r="C19" s="77" t="s">
-        <v>801</v>
-      </c>
-      <c r="D19" s="78" t="s">
-        <v>694</v>
-      </c>
-      <c r="E19" s="80" t="s">
-        <v>802</v>
-      </c>
-      <c r="F19" s="77" t="s">
-        <v>289</v>
-      </c>
-      <c r="G19" s="77" t="s">
-        <v>290</v>
-      </c>
-      <c r="H19" s="80" t="s">
-        <v>803</v>
-      </c>
-      <c r="I19" s="81" t="s">
-        <v>291</v>
-      </c>
-      <c r="J19" s="81" t="s">
-        <v>291</v>
-      </c>
-      <c r="K19" s="81" t="s">
-        <v>291</v>
-      </c>
-      <c r="L19" s="81" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="133.19999999999999" customHeight="1">
-      <c r="A20" s="75">
-        <v>18</v>
-      </c>
-      <c r="B20" s="82" t="s">
-        <v>804</v>
-      </c>
-      <c r="C20" s="77" t="s">
-        <v>805</v>
-      </c>
-      <c r="D20" s="78" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="83" t="s">
-        <v>806</v>
-      </c>
-      <c r="F20" s="77" t="s">
-        <v>309</v>
-      </c>
-      <c r="G20" s="77" t="s">
-        <v>310</v>
-      </c>
-      <c r="H20" s="80" t="s">
-        <v>807</v>
-      </c>
-      <c r="I20" s="81" t="s">
-        <v>311</v>
-      </c>
-      <c r="J20" s="81" t="s">
-        <v>311</v>
-      </c>
-      <c r="K20" s="81" t="s">
-        <v>311</v>
-      </c>
-      <c r="L20" s="81" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="62.4" customHeight="1">
-      <c r="A21" s="161" t="s">
-        <v>843</v>
-      </c>
-      <c r="B21" s="161"/>
-      <c r="C21" s="161"/>
-      <c r="D21" s="161"/>
-      <c r="E21" s="161"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="161"/>
-      <c r="H21" s="161"/>
-      <c r="I21" s="161"/>
-      <c r="J21" s="161"/>
-      <c r="K21" s="161"/>
-      <c r="L21" s="90"/>
-    </row>
-    <row r="22" spans="1:12" ht="14.4">
-      <c r="A22" s="162" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="162" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" s="162" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="162" t="s">
-        <v>808</v>
-      </c>
-      <c r="F22" s="162" t="s">
-        <v>39</v>
-      </c>
-      <c r="G22" s="162" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="163" t="s">
+      <c r="B28" s="91"/>
+      <c r="C28" s="92" t="s">
+        <v>831</v>
+      </c>
+      <c r="D28" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="157" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="158"/>
-      <c r="K22" s="158"/>
-      <c r="L22" s="92" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="41.4">
-      <c r="A23" s="156"/>
-      <c r="B23" s="91"/>
-      <c r="C23" s="156"/>
-      <c r="D23" s="156"/>
-      <c r="E23" s="156"/>
-      <c r="F23" s="156"/>
-      <c r="G23" s="156"/>
-      <c r="H23" s="164"/>
-      <c r="I23" s="93" t="s">
-        <v>46</v>
-      </c>
-      <c r="J23" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="K23" s="93" t="s">
-        <v>48</v>
-      </c>
-      <c r="L23" s="93" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="178.2" customHeight="1">
-      <c r="A24" s="94">
-        <v>1</v>
-      </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="95" t="s">
-        <v>809</v>
-      </c>
-      <c r="D24" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="E24" s="95" t="s">
-        <v>810</v>
-      </c>
-      <c r="F24" s="94" t="s">
-        <v>811</v>
-      </c>
-      <c r="G24" s="95" t="s">
-        <v>812</v>
-      </c>
-      <c r="H24" s="95" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" s="96" t="s">
-        <v>813</v>
-      </c>
-      <c r="J24" s="96" t="s">
-        <v>813</v>
-      </c>
-      <c r="K24" s="96" t="s">
-        <v>813</v>
-      </c>
-      <c r="L24" s="96" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="115.8" customHeight="1">
-      <c r="A25" s="94">
-        <v>2</v>
-      </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="97" t="s">
-        <v>814</v>
-      </c>
-      <c r="D25" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="95" t="s">
-        <v>815</v>
-      </c>
-      <c r="F25" s="95" t="s">
-        <v>816</v>
-      </c>
-      <c r="G25" s="95" t="s">
-        <v>817</v>
-      </c>
-      <c r="H25" s="95" t="s">
-        <v>818</v>
-      </c>
-      <c r="I25" s="96" t="s">
-        <v>819</v>
-      </c>
-      <c r="J25" s="96" t="s">
-        <v>819</v>
-      </c>
-      <c r="K25" s="96" t="s">
-        <v>819</v>
-      </c>
-      <c r="L25" s="96" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="118.2" customHeight="1">
-      <c r="A26" s="94">
-        <v>3</v>
-      </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="95" t="s">
-        <v>820</v>
-      </c>
-      <c r="D26" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="E26" s="98" t="s">
-        <v>821</v>
-      </c>
-      <c r="F26" s="95" t="s">
-        <v>822</v>
-      </c>
-      <c r="G26" s="95" t="s">
-        <v>823</v>
-      </c>
-      <c r="H26" s="95" t="s">
-        <v>824</v>
-      </c>
-      <c r="I26" s="96" t="s">
-        <v>825</v>
-      </c>
-      <c r="J26" s="96" t="s">
-        <v>825</v>
-      </c>
-      <c r="K26" s="96" t="s">
-        <v>825</v>
-      </c>
-      <c r="L26" s="96" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="109.2" customHeight="1">
-      <c r="A27" s="94">
-        <v>4</v>
-      </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="95" t="s">
-        <v>826</v>
-      </c>
-      <c r="D27" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="95" t="s">
-        <v>827</v>
-      </c>
-      <c r="F27" s="97" t="s">
-        <v>828</v>
-      </c>
-      <c r="G27" s="95" t="s">
-        <v>829</v>
-      </c>
-      <c r="H27" s="95" t="s">
-        <v>830</v>
-      </c>
-      <c r="I27" s="96" t="s">
-        <v>831</v>
-      </c>
-      <c r="J27" s="96" t="s">
-        <v>831</v>
-      </c>
-      <c r="K27" s="96" t="s">
-        <v>831</v>
-      </c>
-      <c r="L27" s="96" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="115.8" customHeight="1">
-      <c r="A28" s="94">
-        <v>5</v>
-      </c>
-      <c r="B28" s="94"/>
-      <c r="C28" s="95" t="s">
+      <c r="E28" s="92" t="s">
         <v>832</v>
       </c>
-      <c r="D28" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="E28" s="95" t="s">
+      <c r="F28" s="94" t="s">
+        <v>325</v>
+      </c>
+      <c r="G28" s="92" t="s">
+        <v>326</v>
+      </c>
+      <c r="H28" s="92" t="s">
         <v>833</v>
       </c>
-      <c r="F28" s="97" t="s">
-        <v>325</v>
-      </c>
-      <c r="G28" s="95" t="s">
-        <v>326</v>
-      </c>
-      <c r="H28" s="95" t="s">
+      <c r="I28" s="93" t="s">
         <v>834</v>
       </c>
-      <c r="I28" s="96" t="s">
-        <v>835</v>
-      </c>
-      <c r="J28" s="96" t="s">
-        <v>835</v>
-      </c>
-      <c r="K28" s="96" t="s">
-        <v>835</v>
-      </c>
-      <c r="L28" s="96" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15.6">
-      <c r="A29" s="94"/>
-      <c r="B29" s="94"/>
-      <c r="C29" s="94"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="97"/>
-      <c r="G29" s="95"/>
-      <c r="H29" s="95"/>
-      <c r="I29" s="96"/>
-      <c r="J29" s="96"/>
-      <c r="K29" s="96"/>
-      <c r="L29" s="96"/>
-    </row>
-    <row r="30" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="31" spans="1:12" ht="15.75" customHeight="1"/>
-    <row r="32" spans="1:12" ht="15.75" customHeight="1"/>
+      <c r="J28" s="93" t="s">
+        <v>834</v>
+      </c>
+      <c r="K28" s="93" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15.6">
+      <c r="A29" s="91"/>
+      <c r="B29" s="91"/>
+      <c r="C29" s="91"/>
+      <c r="D29" s="92"/>
+      <c r="E29" s="96"/>
+      <c r="F29" s="94"/>
+      <c r="G29" s="92"/>
+      <c r="H29" s="92"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:11" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:11" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -22926,9 +25724,6 @@
     <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:K1"/>
@@ -22943,6 +25738,9 @@
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Minor">
@@ -23010,286 +25808,286 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="115" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" style="115" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" style="115" customWidth="1"/>
-    <col min="4" max="4" width="45.77734375" style="115" customWidth="1"/>
-    <col min="5" max="5" width="49.88671875" style="115" customWidth="1"/>
-    <col min="6" max="6" width="19" style="115" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" style="115" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="115"/>
+    <col min="1" max="1" width="15.6640625" style="112" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" style="112" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" style="112" customWidth="1"/>
+    <col min="4" max="4" width="45.77734375" style="112" customWidth="1"/>
+    <col min="5" max="5" width="49.88671875" style="112" customWidth="1"/>
+    <col min="6" max="6" width="19" style="112" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" style="112" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="112"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="115" t="s">
         <v>670</v>
       </c>
-      <c r="B1" s="119" t="s">
+      <c r="B1" s="116" t="s">
         <v>671</v>
       </c>
-      <c r="C1" s="119" t="s">
+      <c r="C1" s="116" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="119" t="s">
+      <c r="D1" s="116" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="119" t="s">
+      <c r="E1" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="119" t="s">
+      <c r="F1" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="119" t="s">
+      <c r="G1" s="116" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="288">
-      <c r="A2" s="117" t="s">
+      <c r="A2" s="114" t="s">
         <v>672</v>
       </c>
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="113" t="s">
         <v>673</v>
       </c>
-      <c r="C2" s="116" t="s">
+      <c r="C2" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="116" t="s">
+      <c r="D2" s="113" t="s">
         <v>674</v>
       </c>
-      <c r="E2" s="116" t="s">
-        <v>869</v>
-      </c>
-      <c r="F2" s="116" t="s">
+      <c r="E2" s="113" t="s">
+        <v>868</v>
+      </c>
+      <c r="F2" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="116" t="s">
+      <c r="G2" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="408.6" customHeight="1">
-      <c r="A3" s="117" t="s">
+      <c r="A3" s="114" t="s">
         <v>676</v>
       </c>
-      <c r="B3" s="116" t="s">
+      <c r="B3" s="113" t="s">
         <v>677</v>
       </c>
-      <c r="C3" s="116" t="s">
+      <c r="C3" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="116" t="s">
+      <c r="D3" s="113" t="s">
         <v>678</v>
       </c>
-      <c r="E3" s="116" t="s">
-        <v>868</v>
-      </c>
-      <c r="F3" s="116" t="s">
+      <c r="E3" s="113" t="s">
+        <v>867</v>
+      </c>
+      <c r="F3" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="116" t="s">
+      <c r="G3" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="360">
-      <c r="A4" s="117" t="s">
+      <c r="A4" s="114" t="s">
         <v>679</v>
       </c>
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="113" t="s">
         <v>680</v>
       </c>
-      <c r="C4" s="116" t="s">
+      <c r="C4" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="D4" s="113" t="s">
         <v>681</v>
       </c>
-      <c r="E4" s="116" t="s">
-        <v>867</v>
-      </c>
-      <c r="F4" s="116" t="s">
+      <c r="E4" s="113" t="s">
+        <v>866</v>
+      </c>
+      <c r="F4" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="116" t="s">
+      <c r="G4" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="345.6">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="114" t="s">
         <v>682</v>
       </c>
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="113" t="s">
         <v>683</v>
       </c>
-      <c r="C5" s="116" t="s">
+      <c r="C5" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="116" t="s">
+      <c r="D5" s="113" t="s">
         <v>684</v>
       </c>
-      <c r="E5" s="116" t="s">
-        <v>866</v>
-      </c>
-      <c r="F5" s="116" t="s">
+      <c r="E5" s="113" t="s">
+        <v>865</v>
+      </c>
+      <c r="F5" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="116" t="s">
+      <c r="G5" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="325.2" customHeight="1">
-      <c r="A6" s="117" t="s">
+      <c r="A6" s="114" t="s">
         <v>685</v>
       </c>
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="113" t="s">
         <v>686</v>
       </c>
-      <c r="C6" s="116" t="s">
+      <c r="C6" s="113" t="s">
         <v>687</v>
       </c>
-      <c r="D6" s="116" t="s">
+      <c r="D6" s="113" t="s">
         <v>688</v>
       </c>
-      <c r="E6" s="116" t="s">
-        <v>865</v>
-      </c>
-      <c r="F6" s="116" t="s">
+      <c r="E6" s="113" t="s">
+        <v>864</v>
+      </c>
+      <c r="F6" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="116" t="s">
+      <c r="G6" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="348.6" customHeight="1">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="114" t="s">
         <v>689</v>
       </c>
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="113" t="s">
         <v>690</v>
       </c>
-      <c r="C7" s="116" t="s">
+      <c r="C7" s="113" t="s">
         <v>687</v>
       </c>
-      <c r="D7" s="116" t="s">
+      <c r="D7" s="113" t="s">
         <v>691</v>
       </c>
-      <c r="E7" s="116" t="s">
-        <v>864</v>
-      </c>
-      <c r="F7" s="116" t="s">
+      <c r="E7" s="113" t="s">
+        <v>863</v>
+      </c>
+      <c r="F7" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="116" t="s">
+      <c r="G7" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="316.8">
-      <c r="A8" s="117" t="s">
+      <c r="A8" s="114" t="s">
         <v>692</v>
       </c>
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="113" t="s">
         <v>693</v>
       </c>
-      <c r="C8" s="116" t="s">
+      <c r="C8" s="113" t="s">
         <v>694</v>
       </c>
-      <c r="D8" s="116" t="s">
+      <c r="D8" s="113" t="s">
         <v>695</v>
       </c>
-      <c r="E8" s="116" t="s">
-        <v>863</v>
-      </c>
-      <c r="F8" s="116" t="s">
+      <c r="E8" s="113" t="s">
+        <v>862</v>
+      </c>
+      <c r="F8" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="116" t="s">
+      <c r="G8" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="405" customHeight="1">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="114" t="s">
         <v>696</v>
       </c>
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="113" t="s">
         <v>697</v>
       </c>
-      <c r="C9" s="116" t="s">
+      <c r="C9" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="116" t="s">
-        <v>862</v>
-      </c>
-      <c r="E9" s="116" t="s">
+      <c r="D9" s="113" t="s">
         <v>861</v>
       </c>
-      <c r="F9" s="116" t="s">
+      <c r="E9" s="113" t="s">
+        <v>860</v>
+      </c>
+      <c r="F9" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="116" t="s">
+      <c r="G9" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="408.6" customHeight="1">
-      <c r="A10" s="117" t="s">
+      <c r="A10" s="114" t="s">
         <v>698</v>
       </c>
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="113" t="s">
         <v>699</v>
       </c>
-      <c r="C10" s="116" t="s">
+      <c r="C10" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="116" t="s">
+      <c r="D10" s="113" t="s">
         <v>700</v>
       </c>
-      <c r="E10" s="116" t="s">
-        <v>860</v>
-      </c>
-      <c r="F10" s="116" t="s">
+      <c r="E10" s="113" t="s">
+        <v>859</v>
+      </c>
+      <c r="F10" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="116" t="s">
+      <c r="G10" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="403.2">
-      <c r="A11" s="117" t="s">
+      <c r="A11" s="114" t="s">
         <v>701</v>
       </c>
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="113" t="s">
         <v>702</v>
       </c>
-      <c r="C11" s="116" t="s">
+      <c r="C11" s="113" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="116" t="s">
+      <c r="D11" s="113" t="s">
         <v>703</v>
       </c>
-      <c r="E11" s="116" t="s">
-        <v>859</v>
-      </c>
-      <c r="F11" s="116" t="s">
+      <c r="E11" s="113" t="s">
+        <v>858</v>
+      </c>
+      <c r="F11" s="113" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="116" t="s">
+      <c r="G11" s="113" t="s">
         <v>675</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.4">
-      <c r="A12" s="117"/>
-      <c r="B12" s="116"/>
-      <c r="C12" s="116"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="116"/>
-      <c r="F12" s="116"/>
-      <c r="G12" s="116"/>
+      <c r="A12" s="114"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
     </row>
     <row r="13" spans="1:7" ht="14.4">
-      <c r="A13" s="117"/>
-      <c r="B13" s="116"/>
-      <c r="C13" s="116"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="116"/>
-      <c r="F13" s="116"/>
-      <c r="G13" s="116"/>
+      <c r="A13" s="114"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23314,125 +26112,125 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="98" t="s">
+        <v>844</v>
+      </c>
+      <c r="B1" s="98" t="s">
         <v>845</v>
-      </c>
-      <c r="B1" s="101" t="s">
-        <v>846</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="31" t="s">
+        <v>847</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>856</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="E1" s="31" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="28.2" customHeight="1">
+      <c r="A2" s="108" t="s">
+        <v>850</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>836</v>
+      </c>
+      <c r="C2" s="111" t="s">
+        <v>846</v>
+      </c>
+      <c r="D2" s="109" t="s">
+        <v>837</v>
+      </c>
+      <c r="E2" s="109" t="s">
+        <v>838</v>
+      </c>
+      <c r="F2" s="110" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="103"/>
+      <c r="B3" s="101"/>
+    </row>
+    <row r="4" spans="1:6" ht="27.6" customHeight="1">
+      <c r="A4" s="104" t="s">
+        <v>851</v>
+      </c>
+      <c r="B4" s="101" t="s">
+        <v>836</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>846</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>839</v>
+      </c>
+      <c r="E4" s="109" t="s">
+        <v>852</v>
+      </c>
+      <c r="F4" s="110" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="102"/>
+    </row>
+    <row r="6" spans="1:6" ht="27.6" customHeight="1">
+      <c r="A6" s="105" t="s">
+        <v>853</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>836</v>
+      </c>
+      <c r="C6" s="111" t="s">
+        <v>854</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>840</v>
+      </c>
+      <c r="E6" s="109" t="s">
+        <v>855</v>
+      </c>
+      <c r="F6" s="110" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="106"/>
+      <c r="B7" s="98"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="107"/>
+      <c r="B8" s="99"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="164" t="s">
         <v>857</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="28.2" customHeight="1">
-      <c r="A2" s="111" t="s">
-        <v>851</v>
-      </c>
-      <c r="B2" s="104" t="s">
-        <v>837</v>
-      </c>
-      <c r="C2" s="114" t="s">
-        <v>847</v>
-      </c>
-      <c r="D2" s="112" t="s">
-        <v>838</v>
-      </c>
-      <c r="E2" s="112" t="s">
-        <v>839</v>
-      </c>
-      <c r="F2" s="113" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="106"/>
-      <c r="B3" s="104"/>
-    </row>
-    <row r="4" spans="1:6" ht="27.6" customHeight="1">
-      <c r="A4" s="107" t="s">
-        <v>852</v>
-      </c>
-      <c r="B4" s="104" t="s">
-        <v>837</v>
-      </c>
-      <c r="C4" s="114" t="s">
-        <v>847</v>
-      </c>
-      <c r="D4" s="112" t="s">
-        <v>840</v>
-      </c>
-      <c r="E4" s="112" t="s">
-        <v>853</v>
-      </c>
-      <c r="F4" s="113" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="105"/>
-    </row>
-    <row r="6" spans="1:6" ht="27.6" customHeight="1">
-      <c r="A6" s="108" t="s">
-        <v>854</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>837</v>
-      </c>
-      <c r="C6" s="114" t="s">
-        <v>855</v>
-      </c>
-      <c r="D6" s="112" t="s">
-        <v>841</v>
-      </c>
-      <c r="E6" s="112" t="s">
-        <v>856</v>
-      </c>
-      <c r="F6" s="113" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="109"/>
-      <c r="B7" s="101"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="110"/>
-      <c r="B8" s="102"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="167" t="s">
-        <v>858</v>
-      </c>
-      <c r="B11" s="168"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="168"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="168"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="165"/>
+      <c r="E11" s="165"/>
+      <c r="F11" s="165"/>
     </row>
     <row r="12" spans="1:6" ht="60.6" customHeight="1">
-      <c r="A12" s="168"/>
-      <c r="B12" s="168"/>
-      <c r="C12" s="168"/>
-      <c r="D12" s="168"/>
-      <c r="E12" s="168"/>
-      <c r="F12" s="168"/>
+      <c r="A12" s="165"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="165"/>
+      <c r="E12" s="165"/>
+      <c r="F12" s="165"/>
     </row>
     <row r="13" spans="1:6" ht="21" customHeight="1">
-      <c r="A13" s="168"/>
-      <c r="B13" s="168"/>
-      <c r="C13" s="168"/>
-      <c r="D13" s="168"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="168"/>
+      <c r="A13" s="165"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="165"/>
+      <c r="E13" s="165"/>
+      <c r="F13" s="165"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="31"/>
@@ -23480,99 +26278,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="101" t="s">
+      <c r="A1" s="98" t="s">
+        <v>844</v>
+      </c>
+      <c r="B1" s="98" t="s">
         <v>845</v>
-      </c>
-      <c r="B1" s="101" t="s">
-        <v>846</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="31" t="s">
+        <v>847</v>
+      </c>
+      <c r="E1" s="31" t="s">
+        <v>856</v>
+      </c>
+      <c r="F1" s="31" t="s">
         <v>848</v>
       </c>
-      <c r="E1" s="31" t="s">
-        <v>857</v>
-      </c>
-      <c r="F1" s="31" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="38.4" customHeight="1">
+      <c r="A2" s="108">
+        <v>100</v>
+      </c>
+      <c r="B2" s="101" t="s">
+        <v>836</v>
+      </c>
+      <c r="C2" s="111" t="s">
+        <v>846</v>
+      </c>
+      <c r="D2" s="109" t="s">
+        <v>837</v>
+      </c>
+      <c r="E2" s="109">
+        <v>1450</v>
+      </c>
+      <c r="F2" s="110" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="38.4" customHeight="1">
-      <c r="A2" s="111">
-        <v>100</v>
-      </c>
-      <c r="B2" s="104" t="s">
-        <v>837</v>
-      </c>
-      <c r="C2" s="114" t="s">
-        <v>847</v>
-      </c>
-      <c r="D2" s="112" t="s">
-        <v>838</v>
-      </c>
-      <c r="E2" s="112">
-        <v>1450</v>
-      </c>
-      <c r="F2" s="113" t="s">
-        <v>850</v>
-      </c>
-    </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="106"/>
-      <c r="B3" s="104"/>
+      <c r="A3" s="103"/>
+      <c r="B3" s="101"/>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1">
-      <c r="A4" s="107">
+      <c r="A4" s="104">
         <v>500</v>
       </c>
-      <c r="B4" s="104" t="s">
-        <v>837</v>
-      </c>
-      <c r="C4" s="114" t="s">
-        <v>847</v>
-      </c>
-      <c r="D4" s="112" t="s">
+      <c r="B4" s="101" t="s">
+        <v>836</v>
+      </c>
+      <c r="C4" s="111" t="s">
+        <v>846</v>
+      </c>
+      <c r="D4" s="109" t="s">
+        <v>839</v>
+      </c>
+      <c r="E4" s="109">
+        <v>13500</v>
+      </c>
+      <c r="F4" s="110" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="102"/>
+    </row>
+    <row r="6" spans="1:6" ht="26.4" customHeight="1">
+      <c r="A6" s="105">
+        <v>1000</v>
+      </c>
+      <c r="B6" s="100" t="s">
+        <v>836</v>
+      </c>
+      <c r="C6" s="111" t="s">
+        <v>854</v>
+      </c>
+      <c r="D6" s="109" t="s">
         <v>840</v>
       </c>
-      <c r="E4" s="112">
-        <v>13500</v>
-      </c>
-      <c r="F4" s="113" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="105"/>
-    </row>
-    <row r="6" spans="1:6" ht="26.4" customHeight="1">
-      <c r="A6" s="108">
-        <v>1000</v>
-      </c>
-      <c r="B6" s="103" t="s">
-        <v>837</v>
-      </c>
-      <c r="C6" s="114" t="s">
-        <v>855</v>
-      </c>
-      <c r="D6" s="112" t="s">
-        <v>841</v>
-      </c>
-      <c r="E6" s="112">
+      <c r="E6" s="109">
         <v>22500</v>
       </c>
-      <c r="F6" s="113" t="s">
-        <v>850</v>
+      <c r="F6" s="110" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="109"/>
-      <c r="B7" s="101"/>
+      <c r="A7" s="106"/>
+      <c r="B7" s="98"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="110"/>
-      <c r="B8" s="102"/>
+      <c r="A8" s="107"/>
+      <c r="B8" s="99"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:F8">
@@ -23593,407 +26391,407 @@
   <dimension ref="A1:AS14"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="64.5546875" style="120" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="120" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="120" customWidth="1"/>
-    <col min="4" max="6" width="8.5546875" style="120" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" style="120" customWidth="1"/>
-    <col min="8" max="8" width="8.5546875" style="120" customWidth="1"/>
-    <col min="9" max="9" width="9" style="120" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="120" customWidth="1"/>
-    <col min="11" max="11" width="8.44140625" style="120" customWidth="1"/>
-    <col min="12" max="12" width="8.5546875" style="120" customWidth="1"/>
-    <col min="13" max="13" width="8.88671875" style="120" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" style="120" customWidth="1"/>
-    <col min="15" max="15" width="8.44140625" style="120" customWidth="1"/>
-    <col min="16" max="17" width="8.77734375" style="120" customWidth="1"/>
-    <col min="18" max="18" width="9" style="120" customWidth="1"/>
-    <col min="19" max="19" width="8.5546875" style="120" customWidth="1"/>
-    <col min="20" max="20" width="8.6640625" style="120" customWidth="1"/>
-    <col min="21" max="21" width="9.33203125" style="120" customWidth="1"/>
-    <col min="22" max="22" width="8.5546875" style="120" customWidth="1"/>
-    <col min="23" max="23" width="8.88671875" style="120" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="120"/>
+    <col min="1" max="1" width="64.5546875" style="117" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="117" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="117" customWidth="1"/>
+    <col min="4" max="6" width="8.5546875" style="117" customWidth="1"/>
+    <col min="7" max="7" width="8.77734375" style="117" customWidth="1"/>
+    <col min="8" max="8" width="8.5546875" style="117" customWidth="1"/>
+    <col min="9" max="9" width="9" style="117" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="117" customWidth="1"/>
+    <col min="11" max="11" width="8.44140625" style="117" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" style="117" customWidth="1"/>
+    <col min="13" max="13" width="8.88671875" style="117" customWidth="1"/>
+    <col min="14" max="14" width="8.6640625" style="117" customWidth="1"/>
+    <col min="15" max="15" width="8.44140625" style="117" customWidth="1"/>
+    <col min="16" max="17" width="8.77734375" style="117" customWidth="1"/>
+    <col min="18" max="18" width="9" style="117" customWidth="1"/>
+    <col min="19" max="19" width="8.5546875" style="117" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="117" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" style="117" customWidth="1"/>
+    <col min="22" max="22" width="8.5546875" style="117" customWidth="1"/>
+    <col min="23" max="23" width="8.88671875" style="117" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="117"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45">
-      <c r="A1" s="127"/>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="127"/>
-      <c r="Q1" s="127"/>
-      <c r="R1" s="127"/>
-      <c r="S1" s="127"/>
-      <c r="T1" s="127"/>
-      <c r="U1" s="127"/>
-      <c r="V1" s="127"/>
-      <c r="W1" s="127"/>
-      <c r="X1" s="127"/>
-      <c r="Y1" s="127"/>
-      <c r="Z1" s="127"/>
-      <c r="AA1" s="127"/>
-      <c r="AB1" s="127"/>
-      <c r="AC1" s="127"/>
-      <c r="AD1" s="127"/>
-      <c r="AE1" s="127"/>
-      <c r="AF1" s="127"/>
-      <c r="AG1" s="127"/>
-      <c r="AH1" s="127"/>
-      <c r="AI1" s="127"/>
-      <c r="AJ1" s="127"/>
-      <c r="AK1" s="127"/>
-      <c r="AL1" s="127"/>
-      <c r="AM1" s="127"/>
-      <c r="AN1" s="127"/>
-      <c r="AO1" s="127"/>
-      <c r="AP1" s="127"/>
-      <c r="AQ1" s="127"/>
-      <c r="AR1" s="127"/>
-      <c r="AS1" s="127"/>
+      <c r="A1" s="124"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
+      <c r="M1" s="124"/>
+      <c r="N1" s="124"/>
+      <c r="O1" s="124"/>
+      <c r="P1" s="124"/>
+      <c r="Q1" s="124"/>
+      <c r="R1" s="124"/>
+      <c r="S1" s="124"/>
+      <c r="T1" s="124"/>
+      <c r="U1" s="124"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="124"/>
+      <c r="X1" s="124"/>
+      <c r="Y1" s="124"/>
+      <c r="Z1" s="124"/>
+      <c r="AA1" s="124"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="124"/>
+      <c r="AD1" s="124"/>
+      <c r="AE1" s="124"/>
+      <c r="AF1" s="124"/>
+      <c r="AG1" s="124"/>
+      <c r="AH1" s="124"/>
+      <c r="AI1" s="124"/>
+      <c r="AJ1" s="124"/>
+      <c r="AK1" s="124"/>
+      <c r="AL1" s="124"/>
+      <c r="AM1" s="124"/>
+      <c r="AN1" s="124"/>
+      <c r="AO1" s="124"/>
+      <c r="AP1" s="124"/>
+      <c r="AQ1" s="124"/>
+      <c r="AR1" s="124"/>
+      <c r="AS1" s="124"/>
     </row>
     <row r="2" spans="1:45" ht="17.399999999999999">
-      <c r="A2" s="127"/>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="128"/>
-      <c r="I2" s="128"/>
-      <c r="J2" s="128"/>
-      <c r="K2" s="128"/>
-      <c r="L2" s="128"/>
-      <c r="M2" s="128"/>
-      <c r="N2" s="128"/>
-      <c r="O2" s="128"/>
-      <c r="P2" s="128"/>
-      <c r="Q2" s="127"/>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="127"/>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="127"/>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="128"/>
-      <c r="AF2" s="128"/>
-      <c r="AG2" s="128"/>
-      <c r="AH2" s="128"/>
-      <c r="AI2" s="128"/>
-      <c r="AJ2" s="128"/>
-      <c r="AK2" s="128"/>
-      <c r="AL2" s="128"/>
-      <c r="AM2" s="128"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="127"/>
+      <c r="A2" s="124"/>
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
+      <c r="M2" s="125"/>
+      <c r="N2" s="125"/>
+      <c r="O2" s="125"/>
+      <c r="P2" s="125"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
+      <c r="T2" s="124"/>
+      <c r="U2" s="124"/>
+      <c r="V2" s="124"/>
+      <c r="W2" s="124"/>
+      <c r="X2" s="124"/>
+      <c r="Y2" s="124"/>
+      <c r="Z2" s="124"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="124"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="125"/>
+      <c r="AF2" s="125"/>
+      <c r="AG2" s="125"/>
+      <c r="AH2" s="125"/>
+      <c r="AI2" s="125"/>
+      <c r="AJ2" s="125"/>
+      <c r="AK2" s="125"/>
+      <c r="AL2" s="125"/>
+      <c r="AM2" s="125"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="124"/>
+      <c r="AP2" s="124"/>
+      <c r="AQ2" s="124"/>
+      <c r="AR2" s="124"/>
+      <c r="AS2" s="124"/>
     </row>
     <row r="3" spans="1:45" ht="17.399999999999999">
-      <c r="A3" s="127"/>
-      <c r="B3" s="127"/>
-      <c r="C3" s="127"/>
-      <c r="D3" s="127"/>
-      <c r="E3" s="127"/>
-      <c r="F3" s="127"/>
-      <c r="G3" s="127"/>
-      <c r="H3" s="128"/>
-      <c r="I3" s="128"/>
-      <c r="J3" s="128"/>
-      <c r="K3" s="128"/>
-      <c r="L3" s="128"/>
-      <c r="M3" s="128"/>
-      <c r="N3" s="128"/>
-      <c r="O3" s="128"/>
-      <c r="P3" s="128"/>
-      <c r="Q3" s="127"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="127"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="127"/>
-      <c r="V3" s="127"/>
-      <c r="W3" s="127"/>
-      <c r="X3" s="127"/>
-      <c r="Y3" s="127"/>
-      <c r="Z3" s="127"/>
-      <c r="AA3" s="127"/>
-      <c r="AB3" s="127"/>
-      <c r="AC3" s="127"/>
-      <c r="AD3" s="127"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="128"/>
-      <c r="AI3" s="128"/>
-      <c r="AJ3" s="128"/>
-      <c r="AK3" s="128"/>
-      <c r="AL3" s="128"/>
-      <c r="AM3" s="128"/>
-      <c r="AN3" s="127"/>
-      <c r="AO3" s="127"/>
-      <c r="AP3" s="127"/>
-      <c r="AQ3" s="127"/>
-      <c r="AR3" s="127"/>
-      <c r="AS3" s="127"/>
+      <c r="A3" s="124"/>
+      <c r="B3" s="124"/>
+      <c r="C3" s="124"/>
+      <c r="D3" s="124"/>
+      <c r="E3" s="124"/>
+      <c r="F3" s="124"/>
+      <c r="G3" s="124"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="125"/>
+      <c r="J3" s="125"/>
+      <c r="K3" s="125"/>
+      <c r="L3" s="125"/>
+      <c r="M3" s="125"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="124"/>
+      <c r="S3" s="124"/>
+      <c r="T3" s="124"/>
+      <c r="U3" s="124"/>
+      <c r="V3" s="124"/>
+      <c r="W3" s="124"/>
+      <c r="X3" s="124"/>
+      <c r="Y3" s="124"/>
+      <c r="Z3" s="124"/>
+      <c r="AA3" s="124"/>
+      <c r="AB3" s="124"/>
+      <c r="AC3" s="124"/>
+      <c r="AD3" s="124"/>
+      <c r="AE3" s="125"/>
+      <c r="AF3" s="125"/>
+      <c r="AG3" s="125"/>
+      <c r="AH3" s="125"/>
+      <c r="AI3" s="125"/>
+      <c r="AJ3" s="125"/>
+      <c r="AK3" s="125"/>
+      <c r="AL3" s="125"/>
+      <c r="AM3" s="125"/>
+      <c r="AN3" s="124"/>
+      <c r="AO3" s="124"/>
+      <c r="AP3" s="124"/>
+      <c r="AQ3" s="124"/>
+      <c r="AR3" s="124"/>
+      <c r="AS3" s="124"/>
     </row>
     <row r="4" spans="1:45" ht="24.6">
-      <c r="A4" s="127"/>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="129" t="s">
+      <c r="A4" s="124"/>
+      <c r="B4" s="124"/>
+      <c r="C4" s="124"/>
+      <c r="D4" s="124"/>
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="126" t="s">
+        <v>869</v>
+      </c>
+      <c r="I4" s="125"/>
+      <c r="J4" s="125"/>
+      <c r="K4" s="125"/>
+      <c r="L4" s="125"/>
+      <c r="M4" s="125"/>
+      <c r="N4" s="125"/>
+      <c r="O4" s="125"/>
+      <c r="P4" s="125"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
+      <c r="S4" s="124"/>
+      <c r="T4" s="124"/>
+      <c r="U4" s="124"/>
+      <c r="V4" s="124"/>
+      <c r="W4" s="124"/>
+      <c r="X4" s="124"/>
+      <c r="Y4" s="124"/>
+      <c r="Z4" s="124"/>
+      <c r="AA4" s="124"/>
+      <c r="AB4" s="124"/>
+      <c r="AC4" s="124"/>
+      <c r="AD4" s="124"/>
+      <c r="AE4" s="126" t="s">
+        <v>869</v>
+      </c>
+      <c r="AF4" s="125"/>
+      <c r="AG4" s="125"/>
+      <c r="AH4" s="125"/>
+      <c r="AI4" s="125"/>
+      <c r="AJ4" s="125"/>
+      <c r="AK4" s="125"/>
+      <c r="AL4" s="125"/>
+      <c r="AM4" s="125"/>
+      <c r="AN4" s="124"/>
+      <c r="AO4" s="124"/>
+      <c r="AP4" s="124"/>
+      <c r="AQ4" s="124"/>
+      <c r="AR4" s="124"/>
+      <c r="AS4" s="124"/>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="A5" s="123" t="s">
         <v>870</v>
       </c>
-      <c r="I4" s="128"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="128"/>
-      <c r="L4" s="128"/>
-      <c r="M4" s="128"/>
-      <c r="N4" s="128"/>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="127"/>
-      <c r="R4" s="127"/>
-      <c r="S4" s="127"/>
-      <c r="T4" s="127"/>
-      <c r="U4" s="127"/>
-      <c r="V4" s="127"/>
-      <c r="W4" s="127"/>
-      <c r="X4" s="127"/>
-      <c r="Y4" s="127"/>
-      <c r="Z4" s="127"/>
-      <c r="AA4" s="127"/>
-      <c r="AB4" s="127"/>
-      <c r="AC4" s="127"/>
-      <c r="AD4" s="127"/>
-      <c r="AE4" s="129" t="s">
-        <v>870</v>
-      </c>
-      <c r="AF4" s="128"/>
-      <c r="AG4" s="128"/>
-      <c r="AH4" s="128"/>
-      <c r="AI4" s="128"/>
-      <c r="AJ4" s="128"/>
-      <c r="AK4" s="128"/>
-      <c r="AL4" s="128"/>
-      <c r="AM4" s="128"/>
-      <c r="AN4" s="127"/>
-      <c r="AO4" s="127"/>
-      <c r="AP4" s="127"/>
-      <c r="AQ4" s="127"/>
-      <c r="AR4" s="127"/>
-      <c r="AS4" s="127"/>
-    </row>
-    <row r="5" spans="1:45">
-      <c r="A5" s="126" t="s">
+      <c r="B5" s="122" t="s">
         <v>871</v>
       </c>
-      <c r="B5" s="125" t="s">
+      <c r="C5" s="122" t="s">
         <v>872</v>
       </c>
-      <c r="C5" s="125" t="s">
+      <c r="D5" s="122" t="s">
         <v>873</v>
       </c>
-      <c r="D5" s="125" t="s">
+      <c r="E5" s="122" t="s">
         <v>874</v>
       </c>
-      <c r="E5" s="125" t="s">
+      <c r="F5" s="122" t="s">
         <v>875</v>
       </c>
-      <c r="F5" s="125" t="s">
+      <c r="G5" s="122" t="s">
         <v>876</v>
       </c>
-      <c r="G5" s="125" t="s">
+      <c r="H5" s="122" t="s">
         <v>877</v>
       </c>
-      <c r="H5" s="125" t="s">
+      <c r="I5" s="122" t="s">
         <v>878</v>
       </c>
-      <c r="I5" s="125" t="s">
+      <c r="J5" s="122" t="s">
         <v>879</v>
       </c>
-      <c r="J5" s="125" t="s">
+      <c r="K5" s="122" t="s">
         <v>880</v>
       </c>
-      <c r="K5" s="125" t="s">
+      <c r="L5" s="122" t="s">
         <v>881</v>
       </c>
-      <c r="L5" s="125" t="s">
+      <c r="M5" s="122" t="s">
         <v>882</v>
       </c>
-      <c r="M5" s="125" t="s">
+      <c r="N5" s="122" t="s">
         <v>883</v>
       </c>
-      <c r="N5" s="125" t="s">
+      <c r="O5" s="122" t="s">
         <v>884</v>
       </c>
-      <c r="O5" s="125" t="s">
+      <c r="P5" s="122" t="s">
         <v>885</v>
       </c>
-      <c r="P5" s="125" t="s">
+      <c r="Q5" s="122" t="s">
         <v>886</v>
       </c>
-      <c r="Q5" s="125" t="s">
+      <c r="R5" s="122" t="s">
         <v>887</v>
       </c>
-      <c r="R5" s="125" t="s">
+      <c r="S5" s="122" t="s">
         <v>888</v>
       </c>
-      <c r="S5" s="125" t="s">
+      <c r="T5" s="122" t="s">
         <v>889</v>
       </c>
-      <c r="T5" s="125" t="s">
+      <c r="U5" s="122" t="s">
         <v>890</v>
       </c>
-      <c r="U5" s="125" t="s">
+      <c r="V5" s="122" t="s">
         <v>891</v>
       </c>
-      <c r="V5" s="125" t="s">
+      <c r="W5" s="122" t="s">
         <v>892</v>
       </c>
-      <c r="W5" s="125" t="s">
+      <c r="X5" s="122" t="s">
         <v>893</v>
       </c>
-      <c r="X5" s="125" t="s">
+      <c r="Y5" s="122" t="s">
         <v>894</v>
       </c>
-      <c r="Y5" s="125" t="s">
+      <c r="Z5" s="122" t="s">
         <v>895</v>
       </c>
-      <c r="Z5" s="125" t="s">
+      <c r="AA5" s="122" t="s">
         <v>896</v>
       </c>
-      <c r="AA5" s="125" t="s">
+      <c r="AB5" s="122" t="s">
         <v>897</v>
       </c>
-      <c r="AB5" s="125" t="s">
+      <c r="AC5" s="122" t="s">
         <v>898</v>
       </c>
-      <c r="AC5" s="125" t="s">
+      <c r="AD5" s="122" t="s">
         <v>899</v>
       </c>
-      <c r="AD5" s="125" t="s">
+      <c r="AE5" s="122" t="s">
         <v>900</v>
       </c>
-      <c r="AE5" s="125" t="s">
+      <c r="AF5" s="122" t="s">
         <v>901</v>
       </c>
-      <c r="AF5" s="125" t="s">
+      <c r="AG5" s="122"/>
+      <c r="AH5" s="122"/>
+      <c r="AI5" s="122"/>
+      <c r="AJ5" s="122"/>
+      <c r="AK5" s="122"/>
+      <c r="AL5" s="122"/>
+      <c r="AM5" s="122"/>
+      <c r="AN5" s="122"/>
+      <c r="AO5" s="122"/>
+      <c r="AP5" s="122"/>
+      <c r="AQ5" s="122"/>
+      <c r="AR5" s="122"/>
+      <c r="AS5" s="122"/>
+    </row>
+    <row r="6" spans="1:45" ht="15">
+      <c r="A6" s="121" t="s">
         <v>902</v>
       </c>
-      <c r="AG5" s="125"/>
-      <c r="AH5" s="125"/>
-      <c r="AI5" s="125"/>
-      <c r="AJ5" s="125"/>
-      <c r="AK5" s="125"/>
-      <c r="AL5" s="125"/>
-      <c r="AM5" s="125"/>
-      <c r="AN5" s="125"/>
-      <c r="AO5" s="125"/>
-      <c r="AP5" s="125"/>
-      <c r="AQ5" s="125"/>
-      <c r="AR5" s="125"/>
-      <c r="AS5" s="125"/>
-    </row>
-    <row r="6" spans="1:45" ht="15">
-      <c r="A6" s="124" t="s">
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+    </row>
+    <row r="7" spans="1:45" ht="30">
+      <c r="A7" s="119" t="s">
         <v>903</v>
       </c>
-      <c r="B6" s="121"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="121"/>
-      <c r="E6" s="121"/>
-    </row>
-    <row r="7" spans="1:45" ht="30">
-      <c r="A7" s="122" t="s">
+      <c r="F7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+    </row>
+    <row r="8" spans="1:45" ht="15">
+      <c r="A8" s="120" t="s">
         <v>904</v>
       </c>
-      <c r="F7" s="121"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="121"/>
-      <c r="I7" s="121"/>
-    </row>
-    <row r="8" spans="1:45" ht="15">
-      <c r="A8" s="123" t="s">
+      <c r="J8" s="118"/>
+      <c r="K8" s="118"/>
+      <c r="L8" s="118"/>
+      <c r="M8" s="118"/>
+    </row>
+    <row r="9" spans="1:45" ht="30">
+      <c r="A9" s="120" t="s">
         <v>905</v>
       </c>
-      <c r="J8" s="121"/>
-      <c r="K8" s="121"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="121"/>
-    </row>
-    <row r="9" spans="1:45" ht="30">
-      <c r="A9" s="123" t="s">
+      <c r="N9" s="118"/>
+      <c r="O9" s="118"/>
+      <c r="P9" s="118"/>
+      <c r="Q9" s="118"/>
+    </row>
+    <row r="10" spans="1:45" ht="30">
+      <c r="A10" s="120" t="s">
         <v>906</v>
       </c>
-      <c r="N9" s="121"/>
-      <c r="O9" s="121"/>
-      <c r="P9" s="121"/>
-      <c r="Q9" s="121"/>
-    </row>
-    <row r="10" spans="1:45" ht="30">
-      <c r="A10" s="123" t="s">
+      <c r="R10" s="118"/>
+      <c r="S10" s="118"/>
+      <c r="T10" s="118"/>
+      <c r="U10" s="118"/>
+      <c r="V10" s="118"/>
+      <c r="W10" s="118"/>
+    </row>
+    <row r="11" spans="1:45" ht="30">
+      <c r="A11" s="120" t="s">
         <v>907</v>
       </c>
-      <c r="R10" s="121"/>
-      <c r="S10" s="121"/>
-      <c r="T10" s="121"/>
-      <c r="U10" s="121"/>
-      <c r="V10" s="121"/>
-      <c r="W10" s="121"/>
-    </row>
-    <row r="11" spans="1:45" ht="30">
-      <c r="A11" s="123" t="s">
+      <c r="X11" s="118"/>
+    </row>
+    <row r="12" spans="1:45" ht="30">
+      <c r="A12" s="120" t="s">
         <v>908</v>
       </c>
-      <c r="X11" s="121"/>
-    </row>
-    <row r="12" spans="1:45" ht="30">
-      <c r="A12" s="123" t="s">
+      <c r="Y12" s="118"/>
+      <c r="Z12" s="118"/>
+    </row>
+    <row r="13" spans="1:45" ht="30">
+      <c r="A13" s="119" t="s">
         <v>909</v>
       </c>
-      <c r="Y12" s="121"/>
-      <c r="Z12" s="121"/>
-    </row>
-    <row r="13" spans="1:45" ht="30">
-      <c r="A13" s="122" t="s">
+      <c r="AA13" s="118"/>
+      <c r="AB13" s="118"/>
+    </row>
+    <row r="14" spans="1:45" ht="30">
+      <c r="A14" s="119" t="s">
         <v>910</v>
       </c>
-      <c r="AA13" s="121"/>
-      <c r="AB13" s="121"/>
-    </row>
-    <row r="14" spans="1:45" ht="30">
-      <c r="A14" s="122" t="s">
-        <v>911</v>
-      </c>
-      <c r="AC14" s="121"/>
-      <c r="AD14" s="121"/>
-      <c r="AE14" s="121"/>
-      <c r="AF14" s="121"/>
+      <c r="AC14" s="118"/>
+      <c r="AD14" s="118"/>
+      <c r="AE14" s="118"/>
+      <c r="AF14" s="118"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
+++ b/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hidden\Desktop\Финальный проект_АКАДЕМИЯ ТОП\Мой_ДИПЛОМНЫЙ_ПРОЕКТ\Свод(чек-лист+тест-кейс+баг-репор+автоматизация)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B96163-0C06-4F6A-9DB3-EBD7ADF29799}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D64D26-D236-4C38-8440-38F1336B433B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -4314,26 +4314,10 @@
     <xf numFmtId="0" fontId="55" fillId="27" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="50" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="51" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4341,8 +4325,33 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4353,32 +4362,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="19" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4395,6 +4389,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="49" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5067,6 +5067,799 @@
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Результаты тестирования веб-ресурса</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-F47D-44E6-9836-2D3021009484}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000002-F47D-44E6-9836-2D3021009484}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:pattFill prst="pct75">
+                <a:fgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="50000"/>
+                      <a:lumOff val="50000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Тест-кейсы'!$B$92:$B$93</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>PASSED</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>FAILED</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Тест-кейсы'!$C$92:$C$93</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F47D-44E6-9836-2D3021009484}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="39000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Зависимость времени ответа (Response Time) от количества пользователей</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU" sz="1400"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Диаграмма!$A$2:$A$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D625-4F29-8C7F-473EF9E3071A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="inEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="50000"/>
+                          <a:lumOff val="50000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Диаграмма!$E$2:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>22500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D625-4F29-8C7F-473EF9E3071A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="65"/>
+        <c:axId val="615727183"/>
+        <c:axId val="507085823"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="615727183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="75000"/>
+                <a:lumOff val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="dk1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="507085823"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="507085823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="95000"/>
+                      <a:lumOff val="5000"/>
+                      <a:alpha val="42000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="75000"/>
+                      <a:alpha val="36000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="615727183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="39000">
+          <a:schemeClr val="lt1"/>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="lt1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="25000"/>
+          <a:lumOff val="75000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -7042,11 +7835,11 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -7055,8 +7848,8 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
-              <a:t>Результаты тестирования веб-ресурса</a:t>
+              <a:rPr lang="ru-RU" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Распределение дефектов по уровню критичности</a:t>
             </a:r>
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
@@ -7075,11 +7868,11 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -7092,9 +7885,48 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
+    <c:view3D>
+      <c:rotX val="30"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
-      <c:pieChart>
+      <c:pie3DChart>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -7104,22 +7936,25 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="00B050"/>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="75000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
                 </a:outerShdw>
               </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000001-F47D-44E6-9836-2D3021009484}"/>
+                <c16:uniqueId val="{00000001-F5FE-4850-BE28-3F71864D84A9}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -7128,51 +7963,86 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF0000"/>
+                <a:srgbClr val="FFFF00"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
               </a:ln>
               <a:effectLst>
-                <a:outerShdw blurRad="254000" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="20000"/>
-                  </a:prstClr>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
                 </a:outerShdw>
               </a:effectLst>
+              <a:sp3d/>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-F47D-44E6-9836-2D3021009484}"/>
+                <c16:uniqueId val="{00000003-F5FE-4850-BE28-3F71864D84A9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="00B050"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-F5FE-4850-BE28-3F71864D84A9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                  <a:srgbClr val="000000">
+                    <a:alpha val="63000"/>
+                  </a:srgbClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:sp3d/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-F5FE-4850-BE28-3F71864D84A9}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
-              <a:pattFill prst="pct75">
-                <a:fgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:fgClr>
-                <a:bgClr>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:bgClr>
-              </a:pattFill>
+              <a:noFill/>
               <a:ln>
                 <a:noFill/>
               </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="50800" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
-                  <a:prstClr val="black">
-                    <a:alpha val="40000"/>
-                  </a:prstClr>
-                </a:outerShdw>
-              </a:effectLst>
+              <a:effectLst/>
             </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
@@ -7181,9 +8051,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -7203,13 +8076,14 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="9525">
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
                   <a:solidFill>
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="50000"/>
-                      <a:lumOff val="50000"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
                     </a:schemeClr>
                   </a:solidFill>
+                  <a:round/>
                 </a:ln>
                 <a:effectLst/>
               </c:spPr>
@@ -7220,36 +8094,48 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Тест-кейсы'!$B$92:$B$93</c:f>
+              <c:f>'Чек-лист'!$B$256:$B$259</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>PASSED</c:v>
+                  <c:v>Major (Значительный)</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>FAILED</c:v>
+                  <c:v>Medium (Средний)</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Minor (Низкий)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Advice (Рекомендации)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Тест-кейсы'!$C$92:$C$93</c:f>
+              <c:f>'Чек-лист'!$C$256:$C$259</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>75</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21</c:v>
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F47D-44E6-9836-2D3021009484}"/>
+              <c16:uniqueId val="{00000008-F5FE-4850-BE28-3F71864D84A9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7263,8 +8149,7 @@
           <c:showBubbleSize val="0"/>
           <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
+      </c:pie3DChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -7274,15 +8159,10 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -7295,9 +8175,9 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -7321,30 +8201,14 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -7383,89 +8247,113 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ru-RU" sz="1400" b="1" i="0" u="none" strike="noStrike" baseline="0"/>
-              <a:t>Зависимость времени ответа (Response Time) от количества пользователей</a:t>
-            </a:r>
-            <a:endParaRPr lang="ru-RU" sz="1400"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
+    <c:autoTitleDeleted val="1"/>
+    <c:view3D>
+      <c:rotX val="50"/>
+      <c:rotY val="0"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+      <c:perspective val="60"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
       <c:spPr>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
+        <a:sp3d/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pie3DChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-75F0-4B4C-BE3E-4B3AB133B788}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:explosion val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="20000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:scene3d>
+                <a:camera prst="orthographicFront"/>
+                <a:lightRig rig="threePt" dir="t"/>
+              </a:scene3d>
+              <a:sp3d prstMaterial="matte"/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-75F0-4B4C-BE3E-4B3AB133B788}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
           <c:dLbls>
             <c:spPr>
               <a:noFill/>
@@ -7495,257 +8383,76 @@
             </c:txPr>
             <c:dLblPos val="inEnd"/>
             <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
+            <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
+            <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="dk1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
             <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
             </c:extLst>
           </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Чек-лист'!$B$289:$B$290</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Passed</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Failed</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Диаграмма!$A$2:$A$6</c:f>
+              <c:f>'Чек-лист'!$C$289:$C$290</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>100</c:v>
+                  <c:v>124</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1000</c:v>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D625-4F29-8C7F-473EF9E3071A}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="lt1"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="ru-RU"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>Диаграмма!$E$2:$E$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
-                <c:pt idx="0">
-                  <c:v>1450</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>13500</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>22500</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D625-4F29-8C7F-473EF9E3071A}"/>
+              <c16:uniqueId val="{00000004-75F0-4B4C-BE3E-4B3AB133B788}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="inEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
+          <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="65"/>
-        <c:axId val="615727183"/>
-        <c:axId val="507085823"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="615727183"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="ru-RU"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="507085823"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="507085823"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="95000"/>
-                      <a:lumOff val="5000"/>
-                      <a:alpha val="42000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="75000"/>
-                      <a:alpha val="36000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="615727183"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+      </c:pie3DChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -7766,30 +8473,21 @@
     </c:extLst>
   </c:chart>
   <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
+    <a:pattFill prst="dkDnDiag">
+      <a:fgClr>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:fgClr>
+      <a:bgClr>
+        <a:schemeClr val="lt1"/>
+      </a:bgClr>
+    </a:pattFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:round/>
@@ -7972,6 +8670,86 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
   <a:schemeClr val="accent6"/>
   <a:schemeClr val="accent5"/>
@@ -8008,7 +8786,7 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10120,6 +10898,1039 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="345">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx2"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="261">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="dkDnDiag">
+        <a:fgClr>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="317500" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="25000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:effectLst>
+        <a:outerShdw blurRad="88900" sx="102000" sy="102000" algn="ctr" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="20000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+      <a:scene3d>
+        <a:camera prst="orthographicFront"/>
+        <a:lightRig rig="threePt" dir="t"/>
+      </a:scene3d>
+      <a:sp3d prstMaterial="matte"/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:alpha val="78000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="253">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10720,7 +12531,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11548,6 +13359,82 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>323</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>10885</xdr:colOff>
+      <xdr:row>346</xdr:row>
+      <xdr:rowOff>43543</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Диаграмма 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31A98960-425E-4602-9494-40C15BF6C514}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>350</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>21772</xdr:colOff>
+      <xdr:row>370</xdr:row>
+      <xdr:rowOff>87086</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Диаграмма 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{342354C5-4A17-45E2-A30D-7C29F2EF4EFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11977,27 +13864,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8">
-      <c r="A1" s="137" t="s">
+      <c r="A1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="131" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="131" t="s">
+      <c r="C1" s="132"/>
+      <c r="D1" s="136" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="132"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="134" t="s">
+      <c r="E1" s="137"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="138" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="127" t="s">
+      <c r="H1" s="134" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="55.2">
-      <c r="A2" s="138"/>
+      <c r="A2" s="130"/>
       <c r="B2" s="23" t="s">
         <v>5</v>
       </c>
@@ -12013,11 +13900,11 @@
       <c r="F2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="135"/>
-      <c r="H2" s="128"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="135"/>
     </row>
     <row r="3" spans="1:25" ht="13.8">
-      <c r="A3" s="129" t="s">
+      <c r="A3" s="133" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -12039,7 +13926,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:25" ht="13.8">
-      <c r="A4" s="130"/>
+      <c r="A4" s="128"/>
       <c r="B4" s="13" t="s">
         <v>53</v>
       </c>
@@ -12059,7 +13946,7 @@
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:25" ht="13.8">
-      <c r="A5" s="130"/>
+      <c r="A5" s="128"/>
       <c r="B5" s="13" t="s">
         <v>55</v>
       </c>
@@ -12079,7 +13966,7 @@
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:25" ht="27.6">
-      <c r="A6" s="130"/>
+      <c r="A6" s="128"/>
       <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
@@ -12099,7 +13986,7 @@
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:25" ht="27.6">
-      <c r="A7" s="130"/>
+      <c r="A7" s="128"/>
       <c r="B7" s="13" t="s">
         <v>58</v>
       </c>
@@ -12119,7 +14006,7 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:25" ht="41.4">
-      <c r="A8" s="130"/>
+      <c r="A8" s="128"/>
       <c r="B8" s="27" t="s">
         <v>60</v>
       </c>
@@ -12139,7 +14026,7 @@
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:25" ht="55.2">
-      <c r="A9" s="130"/>
+      <c r="A9" s="128"/>
       <c r="B9" s="13" t="s">
         <v>61</v>
       </c>
@@ -12159,7 +14046,7 @@
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:25" ht="69">
-      <c r="A10" s="130"/>
+      <c r="A10" s="128"/>
       <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
@@ -12179,7 +14066,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:25" ht="55.2">
-      <c r="A11" s="130"/>
+      <c r="A11" s="128"/>
       <c r="B11" s="13" t="s">
         <v>66</v>
       </c>
@@ -12216,7 +14103,7 @@
       <c r="Y11" s="2"/>
     </row>
     <row r="12" spans="1:25" ht="55.2">
-      <c r="A12" s="130"/>
+      <c r="A12" s="128"/>
       <c r="B12" s="13" t="s">
         <v>67</v>
       </c>
@@ -12253,7 +14140,7 @@
       <c r="Y12" s="2"/>
     </row>
     <row r="13" spans="1:25" ht="16.8" customHeight="1">
-      <c r="A13" s="129" t="s">
+      <c r="A13" s="133" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -12292,7 +14179,7 @@
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="1:25" ht="30" customHeight="1">
-      <c r="A14" s="130"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="27" t="s">
         <v>71</v>
       </c>
@@ -12329,7 +14216,7 @@
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="27.6">
-      <c r="A15" s="130"/>
+      <c r="A15" s="128"/>
       <c r="B15" s="27" t="s">
         <v>424</v>
       </c>
@@ -12366,7 +14253,7 @@
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="27.6">
-      <c r="A16" s="130"/>
+      <c r="A16" s="128"/>
       <c r="B16" s="27" t="s">
         <v>426</v>
       </c>
@@ -12386,7 +14273,7 @@
       <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="41.4">
-      <c r="A17" s="130"/>
+      <c r="A17" s="128"/>
       <c r="B17" s="27" t="s">
         <v>73</v>
       </c>
@@ -12406,7 +14293,7 @@
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="41.4">
-      <c r="A18" s="130"/>
+      <c r="A18" s="128"/>
       <c r="B18" s="27" t="s">
         <v>76</v>
       </c>
@@ -12426,7 +14313,7 @@
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="27.6">
-      <c r="A19" s="130"/>
+      <c r="A19" s="128"/>
       <c r="B19" s="27" t="s">
         <v>79</v>
       </c>
@@ -12446,7 +14333,7 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="55.2">
-      <c r="A20" s="130"/>
+      <c r="A20" s="128"/>
       <c r="B20" s="27" t="s">
         <v>81</v>
       </c>
@@ -12466,7 +14353,7 @@
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="92.4">
-      <c r="A21" s="130"/>
+      <c r="A21" s="128"/>
       <c r="B21" s="27" t="s">
         <v>82</v>
       </c>
@@ -12490,7 +14377,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6">
-      <c r="A22" s="129" t="s">
+      <c r="A22" s="133" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="27" t="s">
@@ -12512,7 +14399,7 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="27.6">
-      <c r="A23" s="130"/>
+      <c r="A23" s="128"/>
       <c r="B23" s="13" t="s">
         <v>179</v>
       </c>
@@ -12532,7 +14419,7 @@
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="27.6">
-      <c r="A24" s="130"/>
+      <c r="A24" s="128"/>
       <c r="B24" s="13" t="s">
         <v>182</v>
       </c>
@@ -12552,7 +14439,7 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="41.4">
-      <c r="A25" s="130"/>
+      <c r="A25" s="128"/>
       <c r="B25" s="13" t="s">
         <v>180</v>
       </c>
@@ -12576,7 +14463,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="52.8">
-      <c r="A26" s="130"/>
+      <c r="A26" s="128"/>
       <c r="B26" s="13" t="s">
         <v>186</v>
       </c>
@@ -12600,7 +14487,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="41.4">
-      <c r="A27" s="130"/>
+      <c r="A27" s="128"/>
       <c r="B27" s="13" t="s">
         <v>190</v>
       </c>
@@ -12620,7 +14507,7 @@
       <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="41.4">
-      <c r="A28" s="130"/>
+      <c r="A28" s="128"/>
       <c r="B28" s="13" t="s">
         <v>192</v>
       </c>
@@ -12640,7 +14527,7 @@
       <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="27.6">
-      <c r="A29" s="130"/>
+      <c r="A29" s="128"/>
       <c r="B29" s="13" t="s">
         <v>194</v>
       </c>
@@ -12660,7 +14547,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="27.6">
-      <c r="A30" s="130"/>
+      <c r="A30" s="128"/>
       <c r="B30" s="13" t="s">
         <v>196</v>
       </c>
@@ -12680,7 +14567,7 @@
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="27.6">
-      <c r="A31" s="130"/>
+      <c r="A31" s="128"/>
       <c r="B31" s="13" t="s">
         <v>200</v>
       </c>
@@ -12700,7 +14587,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="52.8">
-      <c r="A32" s="130"/>
+      <c r="A32" s="128"/>
       <c r="B32" s="13" t="s">
         <v>280</v>
       </c>
@@ -12724,7 +14611,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="55.2">
-      <c r="A33" s="130"/>
+      <c r="A33" s="128"/>
       <c r="B33" s="13" t="s">
         <v>202</v>
       </c>
@@ -12744,7 +14631,7 @@
       <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="41.4">
-      <c r="A34" s="130"/>
+      <c r="A34" s="128"/>
       <c r="B34" s="13" t="s">
         <v>204</v>
       </c>
@@ -12768,7 +14655,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="27.6">
-      <c r="A35" s="129" t="s">
+      <c r="A35" s="133" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -12790,7 +14677,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="13.8">
-      <c r="A36" s="130"/>
+      <c r="A36" s="128"/>
       <c r="B36" s="13" t="s">
         <v>87</v>
       </c>
@@ -12810,7 +14697,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="79.2">
-      <c r="A37" s="130"/>
+      <c r="A37" s="128"/>
       <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
@@ -12834,7 +14721,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="76.2" customHeight="1">
-      <c r="A38" s="130"/>
+      <c r="A38" s="128"/>
       <c r="B38" s="13" t="s">
         <v>276</v>
       </c>
@@ -12858,7 +14745,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="55.2">
-      <c r="A39" s="130"/>
+      <c r="A39" s="128"/>
       <c r="B39" s="13" t="s">
         <v>95</v>
       </c>
@@ -12878,7 +14765,7 @@
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="69">
-      <c r="A40" s="130"/>
+      <c r="A40" s="128"/>
       <c r="B40" s="13" t="s">
         <v>97</v>
       </c>
@@ -12898,7 +14785,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="79.2">
-      <c r="A41" s="130"/>
+      <c r="A41" s="128"/>
       <c r="B41" s="13" t="s">
         <v>99</v>
       </c>
@@ -12922,7 +14809,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="69">
-      <c r="A42" s="130"/>
+      <c r="A42" s="128"/>
       <c r="B42" s="13" t="s">
         <v>104</v>
       </c>
@@ -12942,7 +14829,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="92.4">
-      <c r="A43" s="130"/>
+      <c r="A43" s="128"/>
       <c r="B43" s="13" t="s">
         <v>105</v>
       </c>
@@ -12966,7 +14853,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="27.6">
-      <c r="A44" s="130"/>
+      <c r="A44" s="128"/>
       <c r="B44" s="13" t="s">
         <v>109</v>
       </c>
@@ -12986,7 +14873,7 @@
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="27.6">
-      <c r="A45" s="130"/>
+      <c r="A45" s="128"/>
       <c r="B45" s="13" t="s">
         <v>112</v>
       </c>
@@ -13006,7 +14893,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="27.6">
-      <c r="A46" s="129" t="s">
+      <c r="A46" s="133" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -13028,7 +14915,7 @@
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="27.6">
-      <c r="A47" s="130"/>
+      <c r="A47" s="128"/>
       <c r="B47" s="13" t="s">
         <v>115</v>
       </c>
@@ -13048,7 +14935,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="66">
-      <c r="A48" s="130"/>
+      <c r="A48" s="128"/>
       <c r="B48" s="13" t="s">
         <v>273</v>
       </c>
@@ -13072,7 +14959,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="27.6">
-      <c r="A49" s="130"/>
+      <c r="A49" s="128"/>
       <c r="B49" s="13" t="s">
         <v>117</v>
       </c>
@@ -13092,7 +14979,7 @@
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" ht="27.6">
-      <c r="A50" s="130"/>
+      <c r="A50" s="128"/>
       <c r="B50" s="13" t="s">
         <v>119</v>
       </c>
@@ -13112,7 +14999,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" ht="27.6">
-      <c r="A51" s="130"/>
+      <c r="A51" s="128"/>
       <c r="B51" s="13" t="s">
         <v>121</v>
       </c>
@@ -13132,7 +15019,7 @@
       <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" ht="27.6">
-      <c r="A52" s="130"/>
+      <c r="A52" s="128"/>
       <c r="B52" s="13" t="s">
         <v>123</v>
       </c>
@@ -13152,7 +15039,7 @@
       <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="27.6">
-      <c r="A53" s="130"/>
+      <c r="A53" s="128"/>
       <c r="B53" s="13" t="s">
         <v>125</v>
       </c>
@@ -13172,7 +15059,7 @@
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" ht="27.6">
-      <c r="A54" s="130"/>
+      <c r="A54" s="128"/>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
@@ -13192,7 +15079,7 @@
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" ht="41.4">
-      <c r="A55" s="130"/>
+      <c r="A55" s="128"/>
       <c r="B55" s="13" t="s">
         <v>129</v>
       </c>
@@ -13212,7 +15099,7 @@
       <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" ht="27.6">
-      <c r="A56" s="130"/>
+      <c r="A56" s="128"/>
       <c r="B56" s="13" t="s">
         <v>130</v>
       </c>
@@ -13232,7 +15119,7 @@
       <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" ht="27.6">
-      <c r="A57" s="130"/>
+      <c r="A57" s="128"/>
       <c r="B57" s="13" t="s">
         <v>132</v>
       </c>
@@ -13252,7 +15139,7 @@
       <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8" ht="27.6">
-      <c r="A58" s="130"/>
+      <c r="A58" s="128"/>
       <c r="B58" s="13" t="s">
         <v>134</v>
       </c>
@@ -13272,7 +15159,7 @@
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8" ht="41.4">
-      <c r="A59" s="130"/>
+      <c r="A59" s="128"/>
       <c r="B59" s="13" t="s">
         <v>136</v>
       </c>
@@ -13292,7 +15179,7 @@
       <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" ht="41.4">
-      <c r="A60" s="130"/>
+      <c r="A60" s="128"/>
       <c r="B60" s="13" t="s">
         <v>137</v>
       </c>
@@ -13312,7 +15199,7 @@
       <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A61" s="130"/>
+      <c r="A61" s="128"/>
       <c r="B61" s="13" t="s">
         <v>138</v>
       </c>
@@ -13332,7 +15219,7 @@
       <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8" ht="27.6">
-      <c r="A62" s="130"/>
+      <c r="A62" s="128"/>
       <c r="B62" s="13" t="s">
         <v>140</v>
       </c>
@@ -13352,7 +15239,7 @@
       <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8" ht="27.6">
-      <c r="A63" s="130"/>
+      <c r="A63" s="128"/>
       <c r="B63" s="13" t="s">
         <v>142</v>
       </c>
@@ -13372,7 +15259,7 @@
       <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8" ht="27.6">
-      <c r="A64" s="130"/>
+      <c r="A64" s="128"/>
       <c r="B64" s="13" t="s">
         <v>144</v>
       </c>
@@ -13392,7 +15279,7 @@
       <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:14" ht="52.2" customHeight="1">
-      <c r="A65" s="130"/>
+      <c r="A65" s="128"/>
       <c r="B65" s="13" t="s">
         <v>282</v>
       </c>
@@ -13416,7 +15303,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="41.4">
-      <c r="A66" s="130"/>
+      <c r="A66" s="128"/>
       <c r="B66" s="13" t="s">
         <v>147</v>
       </c>
@@ -13436,7 +15323,7 @@
       <c r="H66" s="16"/>
     </row>
     <row r="67" spans="1:14" ht="27.6">
-      <c r="A67" s="130"/>
+      <c r="A67" s="128"/>
       <c r="B67" s="13" t="s">
         <v>151</v>
       </c>
@@ -13456,7 +15343,7 @@
       <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:14" ht="27.6">
-      <c r="A68" s="130"/>
+      <c r="A68" s="128"/>
       <c r="B68" s="13" t="s">
         <v>149</v>
       </c>
@@ -13476,7 +15363,7 @@
       <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:14" ht="55.2">
-      <c r="A69" s="129" t="s">
+      <c r="A69" s="133" t="s">
         <v>208</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -13498,7 +15385,7 @@
       <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:14" ht="42" customHeight="1">
-      <c r="A70" s="130"/>
+      <c r="A70" s="128"/>
       <c r="B70" s="21" t="s">
         <v>211</v>
       </c>
@@ -13523,7 +15410,7 @@
       <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A71" s="130"/>
+      <c r="A71" s="128"/>
       <c r="B71" s="21" t="s">
         <v>213</v>
       </c>
@@ -13548,7 +15435,7 @@
       <c r="N71" s="4"/>
     </row>
     <row r="72" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A72" s="130"/>
+      <c r="A72" s="128"/>
       <c r="B72" s="21" t="s">
         <v>215</v>
       </c>
@@ -13573,7 +15460,7 @@
       <c r="N72" s="4"/>
     </row>
     <row r="73" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A73" s="130"/>
+      <c r="A73" s="128"/>
       <c r="B73" s="21" t="s">
         <v>217</v>
       </c>
@@ -13598,7 +15485,7 @@
       <c r="N73" s="4"/>
     </row>
     <row r="74" spans="1:14" ht="63.6" customHeight="1">
-      <c r="A74" s="130"/>
+      <c r="A74" s="128"/>
       <c r="B74" s="21" t="s">
         <v>219</v>
       </c>
@@ -13623,7 +15510,7 @@
       <c r="N74" s="4"/>
     </row>
     <row r="75" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A75" s="130"/>
+      <c r="A75" s="128"/>
       <c r="B75" s="21" t="s">
         <v>221</v>
       </c>
@@ -13648,7 +15535,7 @@
       <c r="N75" s="4"/>
     </row>
     <row r="76" spans="1:14" ht="54.6" customHeight="1">
-      <c r="A76" s="130"/>
+      <c r="A76" s="128"/>
       <c r="B76" s="21" t="s">
         <v>223</v>
       </c>
@@ -13673,7 +15560,7 @@
       <c r="N76" s="4"/>
     </row>
     <row r="77" spans="1:14" ht="42" customHeight="1">
-      <c r="A77" s="130"/>
+      <c r="A77" s="128"/>
       <c r="B77" s="21" t="s">
         <v>225</v>
       </c>
@@ -13698,7 +15585,7 @@
       <c r="N77" s="4"/>
     </row>
     <row r="78" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A78" s="130"/>
+      <c r="A78" s="128"/>
       <c r="B78" s="21" t="s">
         <v>227</v>
       </c>
@@ -13723,7 +15610,7 @@
       <c r="N78" s="4"/>
     </row>
     <row r="79" spans="1:14" ht="42.6" customHeight="1">
-      <c r="A79" s="130"/>
+      <c r="A79" s="128"/>
       <c r="B79" s="21" t="s">
         <v>229</v>
       </c>
@@ -13748,7 +15635,7 @@
       <c r="N79" s="4"/>
     </row>
     <row r="80" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A80" s="130"/>
+      <c r="A80" s="128"/>
       <c r="B80" s="21" t="s">
         <v>231</v>
       </c>
@@ -13773,7 +15660,7 @@
       <c r="N80" s="4"/>
     </row>
     <row r="81" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A81" s="130"/>
+      <c r="A81" s="128"/>
       <c r="B81" s="21" t="s">
         <v>233</v>
       </c>
@@ -13798,7 +15685,7 @@
       <c r="N81" s="4"/>
     </row>
     <row r="82" spans="1:14" ht="42" customHeight="1">
-      <c r="A82" s="130"/>
+      <c r="A82" s="128"/>
       <c r="B82" s="21" t="s">
         <v>235</v>
       </c>
@@ -13827,7 +15714,7 @@
       <c r="N82" s="4"/>
     </row>
     <row r="83" spans="1:14" ht="42" customHeight="1">
-      <c r="A83" s="130"/>
+      <c r="A83" s="128"/>
       <c r="B83" s="21" t="s">
         <v>239</v>
       </c>
@@ -13856,7 +15743,7 @@
       <c r="N83" s="4"/>
     </row>
     <row r="84" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A84" s="130"/>
+      <c r="A84" s="128"/>
       <c r="B84" s="21" t="s">
         <v>243</v>
       </c>
@@ -13885,7 +15772,7 @@
       <c r="N84" s="4"/>
     </row>
     <row r="85" spans="1:14" ht="70.2" customHeight="1">
-      <c r="A85" s="130"/>
+      <c r="A85" s="128"/>
       <c r="B85" s="21" t="s">
         <v>245</v>
       </c>
@@ -13914,7 +15801,7 @@
       <c r="N85" s="4"/>
     </row>
     <row r="86" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A86" s="130"/>
+      <c r="A86" s="128"/>
       <c r="B86" s="21" t="s">
         <v>252</v>
       </c>
@@ -13943,7 +15830,7 @@
       <c r="N86" s="4"/>
     </row>
     <row r="87" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A87" s="130"/>
+      <c r="A87" s="128"/>
       <c r="B87" s="21" t="s">
         <v>255</v>
       </c>
@@ -13972,7 +15859,7 @@
       <c r="N87" s="4"/>
     </row>
     <row r="88" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A88" s="130"/>
+      <c r="A88" s="128"/>
       <c r="B88" s="21" t="s">
         <v>258</v>
       </c>
@@ -13997,7 +15884,7 @@
       <c r="N88" s="4"/>
     </row>
     <row r="89" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A89" s="130"/>
+      <c r="A89" s="128"/>
       <c r="B89" s="21" t="s">
         <v>260</v>
       </c>
@@ -14026,7 +15913,7 @@
       <c r="N89" s="4"/>
     </row>
     <row r="90" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A90" s="130"/>
+      <c r="A90" s="128"/>
       <c r="B90" s="21" t="s">
         <v>265</v>
       </c>
@@ -14051,7 +15938,7 @@
       <c r="N90" s="4"/>
     </row>
     <row r="91" spans="1:14" ht="56.4" customHeight="1">
-      <c r="A91" s="130"/>
+      <c r="A91" s="128"/>
       <c r="B91" s="21" t="s">
         <v>269</v>
       </c>
@@ -14080,7 +15967,7 @@
       <c r="N91" s="4"/>
     </row>
     <row r="92" spans="1:14" ht="42" customHeight="1">
-      <c r="A92" s="129" t="s">
+      <c r="A92" s="133" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="27" t="s">
@@ -14107,7 +15994,7 @@
       <c r="N92" s="4"/>
     </row>
     <row r="93" spans="1:14" s="63" customFormat="1" ht="27.6">
-      <c r="A93" s="130"/>
+      <c r="A93" s="128"/>
       <c r="B93" s="27" t="s">
         <v>160</v>
       </c>
@@ -14129,7 +16016,7 @@
       <c r="K93" s="64"/>
     </row>
     <row r="94" spans="1:14" ht="61.2" customHeight="1">
-      <c r="A94" s="130"/>
+      <c r="A94" s="128"/>
       <c r="B94" s="27" t="s">
         <v>586</v>
       </c>
@@ -14154,7 +16041,7 @@
       <c r="N94" s="2"/>
     </row>
     <row r="95" spans="1:14" ht="27.6">
-      <c r="A95" s="130"/>
+      <c r="A95" s="128"/>
       <c r="B95" s="27" t="s">
         <v>161</v>
       </c>
@@ -14179,7 +16066,7 @@
       <c r="N95" s="2"/>
     </row>
     <row r="96" spans="1:14" ht="27.6">
-      <c r="A96" s="130"/>
+      <c r="A96" s="128"/>
       <c r="B96" s="21" t="s">
         <v>155</v>
       </c>
@@ -14204,7 +16091,7 @@
       <c r="N96" s="2"/>
     </row>
     <row r="97" spans="1:14" ht="41.4">
-      <c r="A97" s="130"/>
+      <c r="A97" s="128"/>
       <c r="B97" s="21" t="s">
         <v>156</v>
       </c>
@@ -14229,7 +16116,7 @@
       <c r="N97" s="2"/>
     </row>
     <row r="98" spans="1:14" ht="41.4">
-      <c r="A98" s="130"/>
+      <c r="A98" s="128"/>
       <c r="B98" s="21" t="s">
         <v>158</v>
       </c>
@@ -14254,7 +16141,7 @@
       <c r="N98" s="2"/>
     </row>
     <row r="99" spans="1:14" ht="41.4">
-      <c r="A99" s="130"/>
+      <c r="A99" s="128"/>
       <c r="B99" s="27" t="s">
         <v>162</v>
       </c>
@@ -14279,7 +16166,7 @@
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" ht="41.4">
-      <c r="A100" s="130"/>
+      <c r="A100" s="128"/>
       <c r="B100" s="27" t="s">
         <v>164</v>
       </c>
@@ -14304,7 +16191,7 @@
       <c r="N100" s="2"/>
     </row>
     <row r="101" spans="1:14" ht="39" customHeight="1">
-      <c r="A101" s="130"/>
+      <c r="A101" s="128"/>
       <c r="B101" s="27" t="s">
         <v>587</v>
       </c>
@@ -14329,7 +16216,7 @@
       <c r="N101" s="2"/>
     </row>
     <row r="102" spans="1:14" ht="41.4">
-      <c r="A102" s="130"/>
+      <c r="A102" s="128"/>
       <c r="B102" s="27" t="s">
         <v>166</v>
       </c>
@@ -14354,7 +16241,7 @@
       <c r="N102" s="2"/>
     </row>
     <row r="103" spans="1:14" s="63" customFormat="1" ht="69.599999999999994" customHeight="1">
-      <c r="A103" s="130"/>
+      <c r="A103" s="128"/>
       <c r="B103" s="27" t="s">
         <v>168</v>
       </c>
@@ -14379,7 +16266,7 @@
       <c r="N103" s="65"/>
     </row>
     <row r="104" spans="1:14" ht="27.6">
-      <c r="A104" s="130"/>
+      <c r="A104" s="128"/>
       <c r="B104" s="21" t="s">
         <v>169</v>
       </c>
@@ -14404,7 +16291,7 @@
       <c r="N104" s="2"/>
     </row>
     <row r="105" spans="1:14" ht="55.2">
-      <c r="A105" s="130"/>
+      <c r="A105" s="128"/>
       <c r="B105" s="21" t="s">
         <v>171</v>
       </c>
@@ -14429,7 +16316,7 @@
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A106" s="130"/>
+      <c r="A106" s="128"/>
       <c r="B106" s="27" t="s">
         <v>600</v>
       </c>
@@ -14454,7 +16341,7 @@
       <c r="N106" s="2"/>
     </row>
     <row r="107" spans="1:14" ht="55.2">
-      <c r="A107" s="130"/>
+      <c r="A107" s="128"/>
       <c r="B107" s="21" t="s">
         <v>173</v>
       </c>
@@ -14479,7 +16366,7 @@
       <c r="N107" s="2"/>
     </row>
     <row r="108" spans="1:14" ht="69">
-      <c r="A108" s="130"/>
+      <c r="A108" s="128"/>
       <c r="B108" s="27" t="s">
         <v>175</v>
       </c>
@@ -14504,7 +16391,7 @@
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" ht="61.8" customHeight="1">
-      <c r="A109" s="136" t="s">
+      <c r="A109" s="127" t="s">
         <v>14</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -14531,7 +16418,7 @@
       <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" ht="60" customHeight="1">
-      <c r="A110" s="130"/>
+      <c r="A110" s="128"/>
       <c r="B110" s="21" t="s">
         <v>288</v>
       </c>
@@ -14560,7 +16447,7 @@
       <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" ht="63" customHeight="1">
-      <c r="A111" s="130"/>
+      <c r="A111" s="128"/>
       <c r="B111" s="21" t="s">
         <v>292</v>
       </c>
@@ -14585,7 +16472,7 @@
       <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" ht="74.400000000000006" customHeight="1">
-      <c r="A112" s="130"/>
+      <c r="A112" s="128"/>
       <c r="B112" s="21" t="s">
         <v>294</v>
       </c>
@@ -14614,7 +16501,7 @@
       <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A113" s="130"/>
+      <c r="A113" s="128"/>
       <c r="B113" s="21" t="s">
         <v>299</v>
       </c>
@@ -14639,7 +16526,7 @@
       <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" ht="41.4">
-      <c r="A114" s="130"/>
+      <c r="A114" s="128"/>
       <c r="B114" s="21" t="s">
         <v>300</v>
       </c>
@@ -14664,7 +16551,7 @@
       <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A115" s="130"/>
+      <c r="A115" s="128"/>
       <c r="B115" s="21" t="s">
         <v>302</v>
       </c>
@@ -14689,7 +16576,7 @@
       <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A116" s="130"/>
+      <c r="A116" s="128"/>
       <c r="B116" s="21" t="s">
         <v>304</v>
       </c>
@@ -14714,7 +16601,7 @@
       <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A117" s="130"/>
+      <c r="A117" s="128"/>
       <c r="B117" s="21" t="s">
         <v>306</v>
       </c>
@@ -14739,7 +16626,7 @@
       <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" ht="77.400000000000006" customHeight="1">
-      <c r="A118" s="130"/>
+      <c r="A118" s="128"/>
       <c r="B118" s="21" t="s">
         <v>308</v>
       </c>
@@ -14768,7 +16655,7 @@
       <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" ht="65.400000000000006" customHeight="1">
-      <c r="A119" s="130"/>
+      <c r="A119" s="128"/>
       <c r="B119" s="21" t="s">
         <v>312</v>
       </c>
@@ -14793,7 +16680,7 @@
       <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" ht="60.6" customHeight="1">
-      <c r="A120" s="130"/>
+      <c r="A120" s="128"/>
       <c r="B120" s="21" t="s">
         <v>314</v>
       </c>
@@ -14818,7 +16705,7 @@
       <c r="N120" s="4"/>
     </row>
     <row r="121" spans="1:14" ht="40.200000000000003" customHeight="1">
-      <c r="A121" s="130"/>
+      <c r="A121" s="128"/>
       <c r="B121" s="21" t="s">
         <v>316</v>
       </c>
@@ -14843,7 +16730,7 @@
       <c r="N121" s="4"/>
     </row>
     <row r="122" spans="1:14" ht="69">
-      <c r="A122" s="130"/>
+      <c r="A122" s="128"/>
       <c r="B122" s="21" t="s">
         <v>318</v>
       </c>
@@ -14868,7 +16755,7 @@
       <c r="N122" s="4"/>
     </row>
     <row r="123" spans="1:14" ht="60" customHeight="1">
-      <c r="A123" s="130"/>
+      <c r="A123" s="128"/>
       <c r="B123" s="21" t="s">
         <v>320</v>
       </c>
@@ -14893,7 +16780,7 @@
       <c r="N123" s="4"/>
     </row>
     <row r="124" spans="1:14" ht="69">
-      <c r="A124" s="130"/>
+      <c r="A124" s="128"/>
       <c r="B124" s="21" t="s">
         <v>322</v>
       </c>
@@ -14918,7 +16805,7 @@
       <c r="N124" s="4"/>
     </row>
     <row r="125" spans="1:14" ht="67.8" customHeight="1">
-      <c r="A125" s="130"/>
+      <c r="A125" s="128"/>
       <c r="B125" s="27" t="s">
         <v>324</v>
       </c>
@@ -17917,6 +19804,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A92:A108"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A109:A125"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -17924,12 +19817,6 @@
     <mergeCell ref="A35:A45"/>
     <mergeCell ref="A46:A68"/>
     <mergeCell ref="A69:A91"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A92:A108"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:F1048576 C2">
@@ -17983,44 +19870,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="145" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="151" t="s">
+      <c r="B1" s="145" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="151" t="s">
+      <c r="C1" s="145" t="s">
         <v>367</v>
       </c>
-      <c r="D1" s="151" t="s">
+      <c r="D1" s="145" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="151" t="s">
+      <c r="E1" s="145" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="151" t="s">
+      <c r="F1" s="145" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="151" t="s">
+      <c r="G1" s="145" t="s">
         <v>835</v>
       </c>
-      <c r="H1" s="148" t="s">
+      <c r="H1" s="140" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="149"/>
-      <c r="J1" s="150"/>
-      <c r="K1" s="140" t="s">
+      <c r="I1" s="141"/>
+      <c r="J1" s="142"/>
+      <c r="K1" s="143" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6">
-      <c r="A2" s="146"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
       <c r="H2" s="36" t="s">
         <v>21</v>
       </c>
@@ -18030,10 +19917,10 @@
       <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="146"/>
+      <c r="K2" s="144"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="144" t="s">
+      <c r="A3" s="149" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -18066,7 +19953,7 @@
       <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A4" s="145"/>
+      <c r="A4" s="150"/>
       <c r="B4" s="38" t="s">
         <v>336</v>
       </c>
@@ -18097,7 +19984,7 @@
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="145"/>
+      <c r="A5" s="150"/>
       <c r="B5" s="38" t="s">
         <v>337</v>
       </c>
@@ -18128,7 +20015,7 @@
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="145"/>
+      <c r="A6" s="150"/>
       <c r="B6" s="38" t="s">
         <v>338</v>
       </c>
@@ -18159,7 +20046,7 @@
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="145"/>
+      <c r="A7" s="150"/>
       <c r="B7" s="38" t="s">
         <v>339</v>
       </c>
@@ -18190,7 +20077,7 @@
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="145"/>
+      <c r="A8" s="150"/>
       <c r="B8" s="38" t="s">
         <v>340</v>
       </c>
@@ -18221,7 +20108,7 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="146"/>
+      <c r="A9" s="144"/>
       <c r="B9" s="38" t="s">
         <v>341</v>
       </c>
@@ -18252,7 +20139,7 @@
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="144" t="s">
+      <c r="A10" s="149" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -18285,7 +20172,7 @@
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="145"/>
+      <c r="A11" s="150"/>
       <c r="B11" s="38" t="s">
         <v>343</v>
       </c>
@@ -18316,7 +20203,7 @@
       <c r="K11" s="41"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="145"/>
+      <c r="A12" s="150"/>
       <c r="B12" s="38" t="s">
         <v>344</v>
       </c>
@@ -18347,7 +20234,7 @@
       <c r="K12" s="41"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="145"/>
+      <c r="A13" s="150"/>
       <c r="B13" s="38" t="s">
         <v>345</v>
       </c>
@@ -18378,7 +20265,7 @@
       <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="145"/>
+      <c r="A14" s="150"/>
       <c r="B14" s="38" t="s">
         <v>346</v>
       </c>
@@ -18409,7 +20296,7 @@
       <c r="K14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="145"/>
+      <c r="A15" s="150"/>
       <c r="B15" s="38" t="s">
         <v>347</v>
       </c>
@@ -18440,7 +20327,7 @@
       <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="145"/>
+      <c r="A16" s="150"/>
       <c r="B16" s="38" t="s">
         <v>348</v>
       </c>
@@ -18471,7 +20358,7 @@
       <c r="K16" s="41"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="145"/>
+      <c r="A17" s="150"/>
       <c r="B17" s="38" t="s">
         <v>349</v>
       </c>
@@ -18504,7 +20391,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="145"/>
+      <c r="A18" s="150"/>
       <c r="B18" s="38" t="s">
         <v>436</v>
       </c>
@@ -18535,7 +20422,7 @@
       <c r="K18" s="41"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="146"/>
+      <c r="A19" s="144"/>
       <c r="B19" s="38" t="s">
         <v>437</v>
       </c>
@@ -18566,7 +20453,7 @@
       <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A20" s="144" t="s">
+      <c r="A20" s="149" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -18599,7 +20486,7 @@
       <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="145"/>
+      <c r="A21" s="150"/>
       <c r="B21" s="38" t="s">
         <v>351</v>
       </c>
@@ -18630,7 +20517,7 @@
       <c r="K21" s="41"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A22" s="145"/>
+      <c r="A22" s="150"/>
       <c r="B22" s="38" t="s">
         <v>352</v>
       </c>
@@ -18663,7 +20550,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="145"/>
+      <c r="A23" s="150"/>
       <c r="B23" s="38" t="s">
         <v>353</v>
       </c>
@@ -18696,7 +20583,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A24" s="145"/>
+      <c r="A24" s="150"/>
       <c r="B24" s="38" t="s">
         <v>446</v>
       </c>
@@ -18727,7 +20614,7 @@
       <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A25" s="145"/>
+      <c r="A25" s="150"/>
       <c r="B25" s="38" t="s">
         <v>354</v>
       </c>
@@ -18758,7 +20645,7 @@
       <c r="K25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A26" s="145"/>
+      <c r="A26" s="150"/>
       <c r="B26" s="38" t="s">
         <v>355</v>
       </c>
@@ -18789,7 +20676,7 @@
       <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A27" s="145"/>
+      <c r="A27" s="150"/>
       <c r="B27" s="38" t="s">
         <v>356</v>
       </c>
@@ -18822,7 +20709,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="145"/>
+      <c r="A28" s="150"/>
       <c r="B28" s="38" t="s">
         <v>357</v>
       </c>
@@ -18855,7 +20742,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="145"/>
+      <c r="A29" s="150"/>
       <c r="B29" s="38" t="s">
         <v>389</v>
       </c>
@@ -18886,7 +20773,7 @@
       <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="145"/>
+      <c r="A30" s="150"/>
       <c r="B30" s="38" t="s">
         <v>390</v>
       </c>
@@ -18917,7 +20804,7 @@
       <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="85.8" customHeight="1">
-      <c r="A31" s="147" t="s">
+      <c r="A31" s="151" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
@@ -18950,7 +20837,7 @@
       <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="55.2">
-      <c r="A32" s="145"/>
+      <c r="A32" s="150"/>
       <c r="B32" s="38" t="s">
         <v>451</v>
       </c>
@@ -18983,7 +20870,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="82.8">
-      <c r="A33" s="145"/>
+      <c r="A33" s="150"/>
       <c r="B33" s="38" t="s">
         <v>452</v>
       </c>
@@ -19016,7 +20903,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="96.6">
-      <c r="A34" s="145"/>
+      <c r="A34" s="150"/>
       <c r="B34" s="38" t="s">
         <v>453</v>
       </c>
@@ -19047,7 +20934,7 @@
       <c r="K34" s="41"/>
     </row>
     <row r="35" spans="1:11" ht="82.8">
-      <c r="A35" s="145"/>
+      <c r="A35" s="150"/>
       <c r="B35" s="38" t="s">
         <v>454</v>
       </c>
@@ -19080,7 +20967,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="69">
-      <c r="A36" s="145"/>
+      <c r="A36" s="150"/>
       <c r="B36" s="38" t="s">
         <v>455</v>
       </c>
@@ -19111,7 +20998,7 @@
       <c r="K36" s="41"/>
     </row>
     <row r="37" spans="1:11" ht="57" customHeight="1">
-      <c r="A37" s="145"/>
+      <c r="A37" s="150"/>
       <c r="B37" s="38" t="s">
         <v>456</v>
       </c>
@@ -19144,7 +21031,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="72" customHeight="1">
-      <c r="A38" s="145"/>
+      <c r="A38" s="150"/>
       <c r="B38" s="38" t="s">
         <v>473</v>
       </c>
@@ -19175,7 +21062,7 @@
       <c r="K38" s="41"/>
     </row>
     <row r="39" spans="1:11" ht="92.4">
-      <c r="A39" s="144" t="s">
+      <c r="A39" s="149" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -19208,7 +21095,7 @@
       <c r="K39" s="41"/>
     </row>
     <row r="40" spans="1:11" ht="110.4">
-      <c r="A40" s="145"/>
+      <c r="A40" s="150"/>
       <c r="B40" s="38" t="s">
         <v>482</v>
       </c>
@@ -19239,7 +21126,7 @@
       <c r="K40" s="41"/>
     </row>
     <row r="41" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A41" s="145"/>
+      <c r="A41" s="150"/>
       <c r="B41" s="38" t="s">
         <v>483</v>
       </c>
@@ -19270,7 +21157,7 @@
       <c r="K41" s="41"/>
     </row>
     <row r="42" spans="1:11" ht="61.2" customHeight="1">
-      <c r="A42" s="145"/>
+      <c r="A42" s="150"/>
       <c r="B42" s="38" t="s">
         <v>484</v>
       </c>
@@ -19301,7 +21188,7 @@
       <c r="K42" s="41"/>
     </row>
     <row r="43" spans="1:11" ht="69" customHeight="1">
-      <c r="A43" s="145"/>
+      <c r="A43" s="150"/>
       <c r="B43" s="38" t="s">
         <v>485</v>
       </c>
@@ -19332,7 +21219,7 @@
       <c r="K43" s="41"/>
     </row>
     <row r="44" spans="1:11" ht="73.8" customHeight="1">
-      <c r="A44" s="145"/>
+      <c r="A44" s="150"/>
       <c r="B44" s="38" t="s">
         <v>486</v>
       </c>
@@ -19363,7 +21250,7 @@
       <c r="K44" s="41"/>
     </row>
     <row r="45" spans="1:11" ht="85.2" customHeight="1">
-      <c r="A45" s="145"/>
+      <c r="A45" s="150"/>
       <c r="B45" s="38" t="s">
         <v>487</v>
       </c>
@@ -19394,7 +21281,7 @@
       <c r="K45" s="41"/>
     </row>
     <row r="46" spans="1:11" ht="70.8" customHeight="1">
-      <c r="A46" s="145"/>
+      <c r="A46" s="150"/>
       <c r="B46" s="38" t="s">
         <v>488</v>
       </c>
@@ -19427,7 +21314,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="99" customHeight="1">
-      <c r="A47" s="145"/>
+      <c r="A47" s="150"/>
       <c r="B47" s="38" t="s">
         <v>510</v>
       </c>
@@ -19460,7 +21347,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="92.4" customHeight="1">
-      <c r="A48" s="145"/>
+      <c r="A48" s="150"/>
       <c r="B48" s="38" t="s">
         <v>513</v>
       </c>
@@ -19491,7 +21378,7 @@
       <c r="K48" s="41"/>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1">
-      <c r="A49" s="146"/>
+      <c r="A49" s="144"/>
       <c r="B49" s="38" t="s">
         <v>514</v>
       </c>
@@ -19522,7 +21409,7 @@
       <c r="K49" s="41"/>
     </row>
     <row r="50" spans="1:11" ht="82.8">
-      <c r="A50" s="144" t="s">
+      <c r="A50" s="149" t="s">
         <v>208</v>
       </c>
       <c r="B50" s="38" t="s">
@@ -19555,7 +21442,7 @@
       <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A51" s="145"/>
+      <c r="A51" s="150"/>
       <c r="B51" s="38" t="s">
         <v>522</v>
       </c>
@@ -19586,7 +21473,7 @@
       <c r="K51" s="41"/>
     </row>
     <row r="52" spans="1:11" ht="96.6">
-      <c r="A52" s="145"/>
+      <c r="A52" s="150"/>
       <c r="B52" s="38" t="s">
         <v>523</v>
       </c>
@@ -19617,7 +21504,7 @@
       <c r="K52" s="41"/>
     </row>
     <row r="53" spans="1:11" ht="82.2" customHeight="1">
-      <c r="A53" s="145"/>
+      <c r="A53" s="150"/>
       <c r="B53" s="38" t="s">
         <v>524</v>
       </c>
@@ -19648,7 +21535,7 @@
       <c r="K53" s="44"/>
     </row>
     <row r="54" spans="1:11" ht="82.8">
-      <c r="A54" s="145"/>
+      <c r="A54" s="150"/>
       <c r="B54" s="38" t="s">
         <v>525</v>
       </c>
@@ -19681,7 +21568,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="55.2">
-      <c r="A55" s="145"/>
+      <c r="A55" s="150"/>
       <c r="B55" s="38" t="s">
         <v>526</v>
       </c>
@@ -19714,7 +21601,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="41.4">
-      <c r="A56" s="145"/>
+      <c r="A56" s="150"/>
       <c r="B56" s="38" t="s">
         <v>527</v>
       </c>
@@ -19747,7 +21634,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="55.8">
-      <c r="A57" s="145"/>
+      <c r="A57" s="150"/>
       <c r="B57" s="38" t="s">
         <v>528</v>
       </c>
@@ -19780,7 +21667,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="82.8">
-      <c r="A58" s="145"/>
+      <c r="A58" s="150"/>
       <c r="B58" s="38" t="s">
         <v>529</v>
       </c>
@@ -19811,7 +21698,7 @@
       <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" ht="82.8">
-      <c r="A59" s="145"/>
+      <c r="A59" s="150"/>
       <c r="B59" s="38" t="s">
         <v>530</v>
       </c>
@@ -19844,7 +21731,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="55.2">
-      <c r="A60" s="145"/>
+      <c r="A60" s="150"/>
       <c r="B60" s="38" t="s">
         <v>531</v>
       </c>
@@ -19875,7 +21762,7 @@
       <c r="K60" s="41"/>
     </row>
     <row r="61" spans="1:11" ht="69">
-      <c r="A61" s="145"/>
+      <c r="A61" s="150"/>
       <c r="B61" s="38" t="s">
         <v>532</v>
       </c>
@@ -19908,7 +21795,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" ht="69.599999999999994">
-      <c r="A62" s="145"/>
+      <c r="A62" s="150"/>
       <c r="B62" s="38" t="s">
         <v>533</v>
       </c>
@@ -19939,7 +21826,7 @@
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11" ht="117.6" customHeight="1">
-      <c r="A63" s="145"/>
+      <c r="A63" s="150"/>
       <c r="B63" s="38" t="s">
         <v>534</v>
       </c>
@@ -19970,7 +21857,7 @@
       <c r="K63" s="41"/>
     </row>
     <row r="64" spans="1:11" ht="83.4">
-      <c r="A64" s="144" t="s">
+      <c r="A64" s="149" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -20003,7 +21890,7 @@
       <c r="K64" s="41"/>
     </row>
     <row r="65" spans="1:27" ht="69.599999999999994">
-      <c r="A65" s="145"/>
+      <c r="A65" s="150"/>
       <c r="B65" s="38" t="s">
         <v>574</v>
       </c>
@@ -20050,7 +21937,7 @@
       <c r="AA65" s="2"/>
     </row>
     <row r="66" spans="1:27" ht="83.4">
-      <c r="A66" s="145"/>
+      <c r="A66" s="150"/>
       <c r="B66" s="38" t="s">
         <v>575</v>
       </c>
@@ -20097,7 +21984,7 @@
       <c r="AA66" s="2"/>
     </row>
     <row r="67" spans="1:27" ht="104.4" customHeight="1">
-      <c r="A67" s="145"/>
+      <c r="A67" s="150"/>
       <c r="B67" s="38" t="s">
         <v>576</v>
       </c>
@@ -20144,7 +22031,7 @@
       <c r="AA67" s="2"/>
     </row>
     <row r="68" spans="1:27" ht="75" customHeight="1">
-      <c r="A68" s="145"/>
+      <c r="A68" s="150"/>
       <c r="B68" s="38" t="s">
         <v>577</v>
       </c>
@@ -20191,7 +22078,7 @@
       <c r="AA68" s="2"/>
     </row>
     <row r="69" spans="1:27" ht="83.4">
-      <c r="A69" s="145"/>
+      <c r="A69" s="150"/>
       <c r="B69" s="38" t="s">
         <v>578</v>
       </c>
@@ -20238,7 +22125,7 @@
       <c r="AA69" s="2"/>
     </row>
     <row r="70" spans="1:27" ht="42">
-      <c r="A70" s="145"/>
+      <c r="A70" s="150"/>
       <c r="B70" s="38" t="s">
         <v>579</v>
       </c>
@@ -20285,7 +22172,7 @@
       <c r="AA70" s="2"/>
     </row>
     <row r="71" spans="1:27" ht="78">
-      <c r="A71" s="145"/>
+      <c r="A71" s="150"/>
       <c r="B71" s="38" t="s">
         <v>580</v>
       </c>
@@ -20332,7 +22219,7 @@
       <c r="AA71" s="2"/>
     </row>
     <row r="72" spans="1:27" ht="78">
-      <c r="A72" s="145"/>
+      <c r="A72" s="150"/>
       <c r="B72" s="38" t="s">
         <v>581</v>
       </c>
@@ -20363,7 +22250,7 @@
       <c r="K72" s="41"/>
     </row>
     <row r="73" spans="1:27" ht="94.8" customHeight="1">
-      <c r="A73" s="140" t="s">
+      <c r="A73" s="143" t="s">
         <v>14</v>
       </c>
       <c r="B73" s="38" t="s">
@@ -20396,7 +22283,7 @@
       <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:27" ht="75">
-      <c r="A74" s="141"/>
+      <c r="A74" s="146"/>
       <c r="B74" s="38" t="s">
         <v>621</v>
       </c>
@@ -20429,7 +22316,7 @@
       </c>
     </row>
     <row r="75" spans="1:27" ht="75">
-      <c r="A75" s="141"/>
+      <c r="A75" s="146"/>
       <c r="B75" s="38" t="s">
         <v>622</v>
       </c>
@@ -20462,7 +22349,7 @@
       </c>
     </row>
     <row r="76" spans="1:27" ht="79.2" customHeight="1">
-      <c r="A76" s="141"/>
+      <c r="A76" s="146"/>
       <c r="B76" s="38" t="s">
         <v>623</v>
       </c>
@@ -20493,7 +22380,7 @@
       <c r="K76" s="41"/>
     </row>
     <row r="77" spans="1:27" ht="69" customHeight="1">
-      <c r="A77" s="141"/>
+      <c r="A77" s="146"/>
       <c r="B77" s="38" t="s">
         <v>633</v>
       </c>
@@ -20524,7 +22411,7 @@
       <c r="K77" s="41"/>
     </row>
     <row r="78" spans="1:27" ht="69" customHeight="1">
-      <c r="A78" s="141"/>
+      <c r="A78" s="146"/>
       <c r="B78" s="38" t="s">
         <v>637</v>
       </c>
@@ -20555,7 +22442,7 @@
       <c r="K78" s="41"/>
     </row>
     <row r="79" spans="1:27" ht="69" customHeight="1">
-      <c r="A79" s="141"/>
+      <c r="A79" s="146"/>
       <c r="B79" s="38" t="s">
         <v>641</v>
       </c>
@@ -20588,7 +22475,7 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="75" customHeight="1">
-      <c r="A80" s="141"/>
+      <c r="A80" s="146"/>
       <c r="B80" s="38" t="s">
         <v>645</v>
       </c>
@@ -20619,7 +22506,7 @@
       <c r="K80" s="41"/>
     </row>
     <row r="81" spans="1:11" ht="93" customHeight="1">
-      <c r="A81" s="141"/>
+      <c r="A81" s="146"/>
       <c r="B81" s="38" t="s">
         <v>649</v>
       </c>
@@ -20650,7 +22537,7 @@
       <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A82" s="141"/>
+      <c r="A82" s="146"/>
       <c r="B82" s="38" t="s">
         <v>653</v>
       </c>
@@ -20681,7 +22568,7 @@
       <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" ht="110.4" customHeight="1">
-      <c r="A83" s="141"/>
+      <c r="A83" s="146"/>
       <c r="B83" s="38" t="s">
         <v>657</v>
       </c>
@@ -20712,7 +22599,7 @@
       <c r="K83" s="41"/>
     </row>
     <row r="84" spans="1:11" ht="109.2" customHeight="1">
-      <c r="A84" s="141"/>
+      <c r="A84" s="146"/>
       <c r="B84" s="38" t="s">
         <v>661</v>
       </c>
@@ -20743,7 +22630,7 @@
       <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" ht="67.8" customHeight="1">
-      <c r="A85" s="141"/>
+      <c r="A85" s="146"/>
       <c r="B85" s="38" t="s">
         <v>665</v>
       </c>
@@ -20784,8 +22671,8 @@
     </row>
     <row r="88" spans="1:11" ht="13.2">
       <c r="A88" s="37"/>
-      <c r="B88" s="142"/>
-      <c r="C88" s="143"/>
+      <c r="B88" s="147"/>
+      <c r="C88" s="148"/>
       <c r="D88" s="10"/>
     </row>
     <row r="89" spans="1:11" ht="13.2">
@@ -23743,6 +25630,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A73:A85"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="A10:A19"/>
+    <mergeCell ref="A20:A30"/>
+    <mergeCell ref="A31:A38"/>
+    <mergeCell ref="A39:A49"/>
+    <mergeCell ref="A50:A63"/>
+    <mergeCell ref="A64:A72"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="A1:A2"/>
@@ -23752,15 +25648,6 @@
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A73:A85"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="A10:A19"/>
-    <mergeCell ref="A20:A30"/>
-    <mergeCell ref="A31:A38"/>
-    <mergeCell ref="A39:A49"/>
-    <mergeCell ref="A50:A63"/>
-    <mergeCell ref="A64:A72"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
@@ -23822,45 +25709,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.4" customHeight="1">
-      <c r="A1" s="152" t="s">
+      <c r="A1" s="154" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="71"/>
-      <c r="C1" s="152" t="s">
+      <c r="C1" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="154" t="s">
+      <c r="D1" s="162" t="s">
         <v>704</v>
       </c>
-      <c r="E1" s="152" t="s">
+      <c r="E1" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="152" t="s">
+      <c r="F1" s="154" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="152" t="s">
+      <c r="G1" s="154" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="152" t="s">
+      <c r="H1" s="154" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="158" t="s">
+      <c r="I1" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="159"/>
-      <c r="K1" s="159"/>
-    </row>
-    <row r="2" spans="1:11" ht="55.8">
-      <c r="A2" s="153"/>
+      <c r="J1" s="157"/>
+      <c r="K1" s="157"/>
+    </row>
+    <row r="2" spans="1:11" ht="42">
+      <c r="A2" s="155"/>
       <c r="B2" s="71" t="s">
         <v>705</v>
       </c>
-      <c r="C2" s="153"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="163"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
       <c r="I2" s="73" t="s">
         <v>46</v>
       </c>
@@ -23976,7 +25863,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="124.8">
+    <row r="6" spans="1:11" ht="115.2">
       <c r="A6" s="74">
         <v>4</v>
       </c>
@@ -24502,58 +26389,58 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="62.4" customHeight="1">
-      <c r="A21" s="160" t="s">
+      <c r="A21" s="158" t="s">
         <v>842</v>
       </c>
-      <c r="B21" s="160"/>
-      <c r="C21" s="160"/>
-      <c r="D21" s="160"/>
-      <c r="E21" s="160"/>
-      <c r="F21" s="160"/>
-      <c r="G21" s="160"/>
-      <c r="H21" s="160"/>
-      <c r="I21" s="160"/>
-      <c r="J21" s="160"/>
-      <c r="K21" s="160"/>
+      <c r="B21" s="158"/>
+      <c r="C21" s="158"/>
+      <c r="D21" s="158"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="158"/>
+      <c r="H21" s="158"/>
+      <c r="I21" s="158"/>
+      <c r="J21" s="158"/>
+      <c r="K21" s="158"/>
     </row>
     <row r="22" spans="1:11" ht="14.4">
-      <c r="A22" s="161" t="s">
+      <c r="A22" s="159" t="s">
         <v>35</v>
       </c>
       <c r="B22" s="89"/>
-      <c r="C22" s="161" t="s">
+      <c r="C22" s="159" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="161" t="s">
+      <c r="D22" s="159" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="161" t="s">
+      <c r="E22" s="159" t="s">
         <v>807</v>
       </c>
-      <c r="F22" s="161" t="s">
+      <c r="F22" s="159" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="161" t="s">
+      <c r="G22" s="159" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="162" t="s">
+      <c r="H22" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="156" t="s">
+      <c r="I22" s="152" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="157"/>
-      <c r="K22" s="157"/>
-    </row>
-    <row r="23" spans="1:11" ht="55.2">
-      <c r="A23" s="153"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
+    </row>
+    <row r="23" spans="1:11" ht="41.4">
+      <c r="A23" s="155"/>
       <c r="B23" s="89"/>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153"/>
-      <c r="G23" s="153"/>
-      <c r="H23" s="163"/>
+      <c r="C23" s="155"/>
+      <c r="D23" s="155"/>
+      <c r="E23" s="155"/>
+      <c r="F23" s="155"/>
+      <c r="G23" s="155"/>
+      <c r="H23" s="161"/>
       <c r="I23" s="90" t="s">
         <v>46</v>
       </c>
@@ -25724,6 +27611,7 @@
     <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:K1"/>
@@ -25740,7 +27628,6 @@
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Minor">

--- a/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
+++ b/Свод(чек-лист+тест-кейс+баг-репор+автоматизация)/Тестирование сайта Стейк'S Свод_документов.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hidden\Desktop\Финальный проект_АКАДЕМИЯ ТОП\Мой_ДИПЛОМНЫЙ_ПРОЕКТ\Свод(чек-лист+тест-кейс+баг-репор+автоматизация)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D64D26-D236-4C38-8440-38F1336B433B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664B5402-3EA7-4BB6-B7BE-2AA0769C4157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Чек-лист" sheetId="1" r:id="rId1"/>
@@ -4314,10 +4314,26 @@
     <xf numFmtId="0" fontId="55" fillId="27" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="50" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="51" fillId="27" borderId="0" xfId="6" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4325,33 +4341,8 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4362,17 +4353,26 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="19" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="3" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="3" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -13864,27 +13864,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13.8">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="131" t="s">
+      <c r="B1" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="132"/>
-      <c r="D1" s="136" t="s">
+      <c r="C1" s="133"/>
+      <c r="D1" s="131" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="137"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="138" t="s">
+      <c r="E1" s="132"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="134" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="134" t="s">
+      <c r="H1" s="127" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="55.2">
-      <c r="A2" s="130"/>
+      <c r="A2" s="138"/>
       <c r="B2" s="23" t="s">
         <v>5</v>
       </c>
@@ -13900,11 +13900,11 @@
       <c r="F2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="139"/>
-      <c r="H2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="128"/>
     </row>
     <row r="3" spans="1:25" ht="13.8">
-      <c r="A3" s="133" t="s">
+      <c r="A3" s="129" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -13926,7 +13926,7 @@
       <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:25" ht="13.8">
-      <c r="A4" s="128"/>
+      <c r="A4" s="130"/>
       <c r="B4" s="13" t="s">
         <v>53</v>
       </c>
@@ -13946,7 +13946,7 @@
       <c r="H4" s="16"/>
     </row>
     <row r="5" spans="1:25" ht="13.8">
-      <c r="A5" s="128"/>
+      <c r="A5" s="130"/>
       <c r="B5" s="13" t="s">
         <v>55</v>
       </c>
@@ -13966,7 +13966,7 @@
       <c r="H5" s="16"/>
     </row>
     <row r="6" spans="1:25" ht="27.6">
-      <c r="A6" s="128"/>
+      <c r="A6" s="130"/>
       <c r="B6" s="13" t="s">
         <v>56</v>
       </c>
@@ -13986,7 +13986,7 @@
       <c r="H6" s="17"/>
     </row>
     <row r="7" spans="1:25" ht="27.6">
-      <c r="A7" s="128"/>
+      <c r="A7" s="130"/>
       <c r="B7" s="13" t="s">
         <v>58</v>
       </c>
@@ -14006,7 +14006,7 @@
       <c r="H7" s="16"/>
     </row>
     <row r="8" spans="1:25" ht="41.4">
-      <c r="A8" s="128"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="27" t="s">
         <v>60</v>
       </c>
@@ -14026,7 +14026,7 @@
       <c r="H8" s="16"/>
     </row>
     <row r="9" spans="1:25" ht="55.2">
-      <c r="A9" s="128"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="13" t="s">
         <v>61</v>
       </c>
@@ -14046,7 +14046,7 @@
       <c r="H9" s="16"/>
     </row>
     <row r="10" spans="1:25" ht="69">
-      <c r="A10" s="128"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="13" t="s">
         <v>63</v>
       </c>
@@ -14066,7 +14066,7 @@
       <c r="H10" s="16"/>
     </row>
     <row r="11" spans="1:25" ht="55.2">
-      <c r="A11" s="128"/>
+      <c r="A11" s="130"/>
       <c r="B11" s="13" t="s">
         <v>66</v>
       </c>
@@ -14103,7 +14103,7 @@
       <c r="Y11" s="2"/>
     </row>
     <row r="12" spans="1:25" ht="55.2">
-      <c r="A12" s="128"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="13" t="s">
         <v>67</v>
       </c>
@@ -14140,7 +14140,7 @@
       <c r="Y12" s="2"/>
     </row>
     <row r="13" spans="1:25" ht="16.8" customHeight="1">
-      <c r="A13" s="133" t="s">
+      <c r="A13" s="129" t="s">
         <v>70</v>
       </c>
       <c r="B13" s="27" t="s">
@@ -14179,7 +14179,7 @@
       <c r="Y13" s="2"/>
     </row>
     <row r="14" spans="1:25" ht="30" customHeight="1">
-      <c r="A14" s="128"/>
+      <c r="A14" s="130"/>
       <c r="B14" s="27" t="s">
         <v>71</v>
       </c>
@@ -14216,7 +14216,7 @@
       <c r="Y14" s="2"/>
     </row>
     <row r="15" spans="1:25" ht="27.6">
-      <c r="A15" s="128"/>
+      <c r="A15" s="130"/>
       <c r="B15" s="27" t="s">
         <v>424</v>
       </c>
@@ -14253,7 +14253,7 @@
       <c r="Y15" s="2"/>
     </row>
     <row r="16" spans="1:25" ht="27.6">
-      <c r="A16" s="128"/>
+      <c r="A16" s="130"/>
       <c r="B16" s="27" t="s">
         <v>426</v>
       </c>
@@ -14273,7 +14273,7 @@
       <c r="H16" s="16"/>
     </row>
     <row r="17" spans="1:8" ht="41.4">
-      <c r="A17" s="128"/>
+      <c r="A17" s="130"/>
       <c r="B17" s="27" t="s">
         <v>73</v>
       </c>
@@ -14293,7 +14293,7 @@
       <c r="H17" s="16"/>
     </row>
     <row r="18" spans="1:8" ht="41.4">
-      <c r="A18" s="128"/>
+      <c r="A18" s="130"/>
       <c r="B18" s="27" t="s">
         <v>76</v>
       </c>
@@ -14313,7 +14313,7 @@
       <c r="H18" s="16"/>
     </row>
     <row r="19" spans="1:8" ht="27.6">
-      <c r="A19" s="128"/>
+      <c r="A19" s="130"/>
       <c r="B19" s="27" t="s">
         <v>79</v>
       </c>
@@ -14333,7 +14333,7 @@
       <c r="H19" s="16"/>
     </row>
     <row r="20" spans="1:8" ht="55.2">
-      <c r="A20" s="128"/>
+      <c r="A20" s="130"/>
       <c r="B20" s="27" t="s">
         <v>81</v>
       </c>
@@ -14353,7 +14353,7 @@
       <c r="H20" s="16"/>
     </row>
     <row r="21" spans="1:8" ht="92.4">
-      <c r="A21" s="128"/>
+      <c r="A21" s="130"/>
       <c r="B21" s="27" t="s">
         <v>82</v>
       </c>
@@ -14377,7 +14377,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="27.6">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="129" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="27" t="s">
@@ -14399,7 +14399,7 @@
       <c r="H22" s="16"/>
     </row>
     <row r="23" spans="1:8" ht="27.6">
-      <c r="A23" s="128"/>
+      <c r="A23" s="130"/>
       <c r="B23" s="13" t="s">
         <v>179</v>
       </c>
@@ -14419,7 +14419,7 @@
       <c r="H23" s="16"/>
     </row>
     <row r="24" spans="1:8" ht="27.6">
-      <c r="A24" s="128"/>
+      <c r="A24" s="130"/>
       <c r="B24" s="13" t="s">
         <v>182</v>
       </c>
@@ -14439,7 +14439,7 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="41.4">
-      <c r="A25" s="128"/>
+      <c r="A25" s="130"/>
       <c r="B25" s="13" t="s">
         <v>180</v>
       </c>
@@ -14463,7 +14463,7 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="52.8">
-      <c r="A26" s="128"/>
+      <c r="A26" s="130"/>
       <c r="B26" s="13" t="s">
         <v>186</v>
       </c>
@@ -14487,7 +14487,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="41.4">
-      <c r="A27" s="128"/>
+      <c r="A27" s="130"/>
       <c r="B27" s="13" t="s">
         <v>190</v>
       </c>
@@ -14507,7 +14507,7 @@
       <c r="H27" s="16"/>
     </row>
     <row r="28" spans="1:8" ht="41.4">
-      <c r="A28" s="128"/>
+      <c r="A28" s="130"/>
       <c r="B28" s="13" t="s">
         <v>192</v>
       </c>
@@ -14527,7 +14527,7 @@
       <c r="H28" s="16"/>
     </row>
     <row r="29" spans="1:8" ht="27.6">
-      <c r="A29" s="128"/>
+      <c r="A29" s="130"/>
       <c r="B29" s="13" t="s">
         <v>194</v>
       </c>
@@ -14547,7 +14547,7 @@
       <c r="H29" s="16"/>
     </row>
     <row r="30" spans="1:8" ht="27.6">
-      <c r="A30" s="128"/>
+      <c r="A30" s="130"/>
       <c r="B30" s="13" t="s">
         <v>196</v>
       </c>
@@ -14567,7 +14567,7 @@
       <c r="H30" s="16"/>
     </row>
     <row r="31" spans="1:8" ht="27.6">
-      <c r="A31" s="128"/>
+      <c r="A31" s="130"/>
       <c r="B31" s="13" t="s">
         <v>200</v>
       </c>
@@ -14587,7 +14587,7 @@
       <c r="H31" s="16"/>
     </row>
     <row r="32" spans="1:8" ht="52.8">
-      <c r="A32" s="128"/>
+      <c r="A32" s="130"/>
       <c r="B32" s="13" t="s">
         <v>280</v>
       </c>
@@ -14611,7 +14611,7 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="55.2">
-      <c r="A33" s="128"/>
+      <c r="A33" s="130"/>
       <c r="B33" s="13" t="s">
         <v>202</v>
       </c>
@@ -14631,7 +14631,7 @@
       <c r="H33" s="16"/>
     </row>
     <row r="34" spans="1:8" ht="41.4">
-      <c r="A34" s="128"/>
+      <c r="A34" s="130"/>
       <c r="B34" s="13" t="s">
         <v>204</v>
       </c>
@@ -14655,7 +14655,7 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="27.6">
-      <c r="A35" s="133" t="s">
+      <c r="A35" s="129" t="s">
         <v>11</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -14677,7 +14677,7 @@
       <c r="H35" s="16"/>
     </row>
     <row r="36" spans="1:8" ht="13.8">
-      <c r="A36" s="128"/>
+      <c r="A36" s="130"/>
       <c r="B36" s="13" t="s">
         <v>87</v>
       </c>
@@ -14697,7 +14697,7 @@
       <c r="H36" s="16"/>
     </row>
     <row r="37" spans="1:8" ht="79.2">
-      <c r="A37" s="128"/>
+      <c r="A37" s="130"/>
       <c r="B37" s="13" t="s">
         <v>89</v>
       </c>
@@ -14721,7 +14721,7 @@
       </c>
     </row>
     <row r="38" spans="1:8" ht="76.2" customHeight="1">
-      <c r="A38" s="128"/>
+      <c r="A38" s="130"/>
       <c r="B38" s="13" t="s">
         <v>276</v>
       </c>
@@ -14745,7 +14745,7 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="55.2">
-      <c r="A39" s="128"/>
+      <c r="A39" s="130"/>
       <c r="B39" s="13" t="s">
         <v>95</v>
       </c>
@@ -14765,7 +14765,7 @@
       <c r="H39" s="16"/>
     </row>
     <row r="40" spans="1:8" ht="69">
-      <c r="A40" s="128"/>
+      <c r="A40" s="130"/>
       <c r="B40" s="13" t="s">
         <v>97</v>
       </c>
@@ -14785,7 +14785,7 @@
       <c r="H40" s="16"/>
     </row>
     <row r="41" spans="1:8" ht="79.2">
-      <c r="A41" s="128"/>
+      <c r="A41" s="130"/>
       <c r="B41" s="13" t="s">
         <v>99</v>
       </c>
@@ -14809,7 +14809,7 @@
       </c>
     </row>
     <row r="42" spans="1:8" ht="69">
-      <c r="A42" s="128"/>
+      <c r="A42" s="130"/>
       <c r="B42" s="13" t="s">
         <v>104</v>
       </c>
@@ -14829,7 +14829,7 @@
       <c r="H42" s="16"/>
     </row>
     <row r="43" spans="1:8" ht="92.4">
-      <c r="A43" s="128"/>
+      <c r="A43" s="130"/>
       <c r="B43" s="13" t="s">
         <v>105</v>
       </c>
@@ -14853,7 +14853,7 @@
       </c>
     </row>
     <row r="44" spans="1:8" ht="27.6">
-      <c r="A44" s="128"/>
+      <c r="A44" s="130"/>
       <c r="B44" s="13" t="s">
         <v>109</v>
       </c>
@@ -14873,7 +14873,7 @@
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:8" ht="27.6">
-      <c r="A45" s="128"/>
+      <c r="A45" s="130"/>
       <c r="B45" s="13" t="s">
         <v>112</v>
       </c>
@@ -14893,7 +14893,7 @@
       <c r="H45" s="16"/>
     </row>
     <row r="46" spans="1:8" ht="27.6">
-      <c r="A46" s="133" t="s">
+      <c r="A46" s="129" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -14915,7 +14915,7 @@
       <c r="H46" s="16"/>
     </row>
     <row r="47" spans="1:8" ht="27.6">
-      <c r="A47" s="128"/>
+      <c r="A47" s="130"/>
       <c r="B47" s="13" t="s">
         <v>115</v>
       </c>
@@ -14935,7 +14935,7 @@
       <c r="H47" s="16"/>
     </row>
     <row r="48" spans="1:8" ht="66">
-      <c r="A48" s="128"/>
+      <c r="A48" s="130"/>
       <c r="B48" s="13" t="s">
         <v>273</v>
       </c>
@@ -14959,7 +14959,7 @@
       </c>
     </row>
     <row r="49" spans="1:8" ht="27.6">
-      <c r="A49" s="128"/>
+      <c r="A49" s="130"/>
       <c r="B49" s="13" t="s">
         <v>117</v>
       </c>
@@ -14979,7 +14979,7 @@
       <c r="H49" s="16"/>
     </row>
     <row r="50" spans="1:8" ht="27.6">
-      <c r="A50" s="128"/>
+      <c r="A50" s="130"/>
       <c r="B50" s="13" t="s">
         <v>119</v>
       </c>
@@ -14999,7 +14999,7 @@
       <c r="H50" s="16"/>
     </row>
     <row r="51" spans="1:8" ht="27.6">
-      <c r="A51" s="128"/>
+      <c r="A51" s="130"/>
       <c r="B51" s="13" t="s">
         <v>121</v>
       </c>
@@ -15019,7 +15019,7 @@
       <c r="H51" s="16"/>
     </row>
     <row r="52" spans="1:8" ht="27.6">
-      <c r="A52" s="128"/>
+      <c r="A52" s="130"/>
       <c r="B52" s="13" t="s">
         <v>123</v>
       </c>
@@ -15039,7 +15039,7 @@
       <c r="H52" s="16"/>
     </row>
     <row r="53" spans="1:8" ht="27.6">
-      <c r="A53" s="128"/>
+      <c r="A53" s="130"/>
       <c r="B53" s="13" t="s">
         <v>125</v>
       </c>
@@ -15059,7 +15059,7 @@
       <c r="H53" s="16"/>
     </row>
     <row r="54" spans="1:8" ht="27.6">
-      <c r="A54" s="128"/>
+      <c r="A54" s="130"/>
       <c r="B54" s="13" t="s">
         <v>127</v>
       </c>
@@ -15079,7 +15079,7 @@
       <c r="H54" s="16"/>
     </row>
     <row r="55" spans="1:8" ht="41.4">
-      <c r="A55" s="128"/>
+      <c r="A55" s="130"/>
       <c r="B55" s="13" t="s">
         <v>129</v>
       </c>
@@ -15099,7 +15099,7 @@
       <c r="H55" s="16"/>
     </row>
     <row r="56" spans="1:8" ht="27.6">
-      <c r="A56" s="128"/>
+      <c r="A56" s="130"/>
       <c r="B56" s="13" t="s">
         <v>130</v>
       </c>
@@ -15119,7 +15119,7 @@
       <c r="H56" s="16"/>
     </row>
     <row r="57" spans="1:8" ht="27.6">
-      <c r="A57" s="128"/>
+      <c r="A57" s="130"/>
       <c r="B57" s="13" t="s">
         <v>132</v>
       </c>
@@ -15139,7 +15139,7 @@
       <c r="H57" s="16"/>
     </row>
     <row r="58" spans="1:8" ht="27.6">
-      <c r="A58" s="128"/>
+      <c r="A58" s="130"/>
       <c r="B58" s="13" t="s">
         <v>134</v>
       </c>
@@ -15159,7 +15159,7 @@
       <c r="H58" s="16"/>
     </row>
     <row r="59" spans="1:8" ht="41.4">
-      <c r="A59" s="128"/>
+      <c r="A59" s="130"/>
       <c r="B59" s="13" t="s">
         <v>136</v>
       </c>
@@ -15179,7 +15179,7 @@
       <c r="H59" s="16"/>
     </row>
     <row r="60" spans="1:8" ht="41.4">
-      <c r="A60" s="128"/>
+      <c r="A60" s="130"/>
       <c r="B60" s="13" t="s">
         <v>137</v>
       </c>
@@ -15199,7 +15199,7 @@
       <c r="H60" s="16"/>
     </row>
     <row r="61" spans="1:8" ht="28.8" customHeight="1">
-      <c r="A61" s="128"/>
+      <c r="A61" s="130"/>
       <c r="B61" s="13" t="s">
         <v>138</v>
       </c>
@@ -15219,7 +15219,7 @@
       <c r="H61" s="16"/>
     </row>
     <row r="62" spans="1:8" ht="27.6">
-      <c r="A62" s="128"/>
+      <c r="A62" s="130"/>
       <c r="B62" s="13" t="s">
         <v>140</v>
       </c>
@@ -15239,7 +15239,7 @@
       <c r="H62" s="16"/>
     </row>
     <row r="63" spans="1:8" ht="27.6">
-      <c r="A63" s="128"/>
+      <c r="A63" s="130"/>
       <c r="B63" s="13" t="s">
         <v>142</v>
       </c>
@@ -15259,7 +15259,7 @@
       <c r="H63" s="16"/>
     </row>
     <row r="64" spans="1:8" ht="27.6">
-      <c r="A64" s="128"/>
+      <c r="A64" s="130"/>
       <c r="B64" s="13" t="s">
         <v>144</v>
       </c>
@@ -15279,7 +15279,7 @@
       <c r="H64" s="16"/>
     </row>
     <row r="65" spans="1:14" ht="52.2" customHeight="1">
-      <c r="A65" s="128"/>
+      <c r="A65" s="130"/>
       <c r="B65" s="13" t="s">
         <v>282</v>
       </c>
@@ -15303,7 +15303,7 @@
       </c>
     </row>
     <row r="66" spans="1:14" ht="41.4">
-      <c r="A66" s="128"/>
+      <c r="A66" s="130"/>
       <c r="B66" s="13" t="s">
         <v>147</v>
       </c>
@@ -15323,7 +15323,7 @@
       <c r="H66" s="16"/>
     </row>
     <row r="67" spans="1:14" ht="27.6">
-      <c r="A67" s="128"/>
+      <c r="A67" s="130"/>
       <c r="B67" s="13" t="s">
         <v>151</v>
       </c>
@@ -15343,7 +15343,7 @@
       <c r="H67" s="16"/>
     </row>
     <row r="68" spans="1:14" ht="27.6">
-      <c r="A68" s="128"/>
+      <c r="A68" s="130"/>
       <c r="B68" s="13" t="s">
         <v>149</v>
       </c>
@@ -15363,7 +15363,7 @@
       <c r="H68" s="16"/>
     </row>
     <row r="69" spans="1:14" ht="55.2">
-      <c r="A69" s="133" t="s">
+      <c r="A69" s="129" t="s">
         <v>208</v>
       </c>
       <c r="B69" s="21" t="s">
@@ -15385,7 +15385,7 @@
       <c r="H69" s="16"/>
     </row>
     <row r="70" spans="1:14" ht="42" customHeight="1">
-      <c r="A70" s="128"/>
+      <c r="A70" s="130"/>
       <c r="B70" s="21" t="s">
         <v>211</v>
       </c>
@@ -15410,7 +15410,7 @@
       <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A71" s="128"/>
+      <c r="A71" s="130"/>
       <c r="B71" s="21" t="s">
         <v>213</v>
       </c>
@@ -15435,7 +15435,7 @@
       <c r="N71" s="4"/>
     </row>
     <row r="72" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A72" s="128"/>
+      <c r="A72" s="130"/>
       <c r="B72" s="21" t="s">
         <v>215</v>
       </c>
@@ -15460,7 +15460,7 @@
       <c r="N72" s="4"/>
     </row>
     <row r="73" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A73" s="128"/>
+      <c r="A73" s="130"/>
       <c r="B73" s="21" t="s">
         <v>217</v>
       </c>
@@ -15485,7 +15485,7 @@
       <c r="N73" s="4"/>
     </row>
     <row r="74" spans="1:14" ht="63.6" customHeight="1">
-      <c r="A74" s="128"/>
+      <c r="A74" s="130"/>
       <c r="B74" s="21" t="s">
         <v>219</v>
       </c>
@@ -15510,7 +15510,7 @@
       <c r="N74" s="4"/>
     </row>
     <row r="75" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A75" s="128"/>
+      <c r="A75" s="130"/>
       <c r="B75" s="21" t="s">
         <v>221</v>
       </c>
@@ -15535,7 +15535,7 @@
       <c r="N75" s="4"/>
     </row>
     <row r="76" spans="1:14" ht="54.6" customHeight="1">
-      <c r="A76" s="128"/>
+      <c r="A76" s="130"/>
       <c r="B76" s="21" t="s">
         <v>223</v>
       </c>
@@ -15560,7 +15560,7 @@
       <c r="N76" s="4"/>
     </row>
     <row r="77" spans="1:14" ht="42" customHeight="1">
-      <c r="A77" s="128"/>
+      <c r="A77" s="130"/>
       <c r="B77" s="21" t="s">
         <v>225</v>
       </c>
@@ -15585,7 +15585,7 @@
       <c r="N77" s="4"/>
     </row>
     <row r="78" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A78" s="128"/>
+      <c r="A78" s="130"/>
       <c r="B78" s="21" t="s">
         <v>227</v>
       </c>
@@ -15610,7 +15610,7 @@
       <c r="N78" s="4"/>
     </row>
     <row r="79" spans="1:14" ht="42.6" customHeight="1">
-      <c r="A79" s="128"/>
+      <c r="A79" s="130"/>
       <c r="B79" s="21" t="s">
         <v>229</v>
       </c>
@@ -15635,7 +15635,7 @@
       <c r="N79" s="4"/>
     </row>
     <row r="80" spans="1:14" ht="41.4" customHeight="1">
-      <c r="A80" s="128"/>
+      <c r="A80" s="130"/>
       <c r="B80" s="21" t="s">
         <v>231</v>
       </c>
@@ -15660,7 +15660,7 @@
       <c r="N80" s="4"/>
     </row>
     <row r="81" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A81" s="128"/>
+      <c r="A81" s="130"/>
       <c r="B81" s="21" t="s">
         <v>233</v>
       </c>
@@ -15685,7 +15685,7 @@
       <c r="N81" s="4"/>
     </row>
     <row r="82" spans="1:14" ht="42" customHeight="1">
-      <c r="A82" s="128"/>
+      <c r="A82" s="130"/>
       <c r="B82" s="21" t="s">
         <v>235</v>
       </c>
@@ -15714,7 +15714,7 @@
       <c r="N82" s="4"/>
     </row>
     <row r="83" spans="1:14" ht="42" customHeight="1">
-      <c r="A83" s="128"/>
+      <c r="A83" s="130"/>
       <c r="B83" s="21" t="s">
         <v>239</v>
       </c>
@@ -15743,7 +15743,7 @@
       <c r="N83" s="4"/>
     </row>
     <row r="84" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A84" s="128"/>
+      <c r="A84" s="130"/>
       <c r="B84" s="21" t="s">
         <v>243</v>
       </c>
@@ -15772,7 +15772,7 @@
       <c r="N84" s="4"/>
     </row>
     <row r="85" spans="1:14" ht="70.2" customHeight="1">
-      <c r="A85" s="128"/>
+      <c r="A85" s="130"/>
       <c r="B85" s="21" t="s">
         <v>245</v>
       </c>
@@ -15801,7 +15801,7 @@
       <c r="N85" s="4"/>
     </row>
     <row r="86" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A86" s="128"/>
+      <c r="A86" s="130"/>
       <c r="B86" s="21" t="s">
         <v>252</v>
       </c>
@@ -15830,7 +15830,7 @@
       <c r="N86" s="4"/>
     </row>
     <row r="87" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A87" s="128"/>
+      <c r="A87" s="130"/>
       <c r="B87" s="21" t="s">
         <v>255</v>
       </c>
@@ -15859,7 +15859,7 @@
       <c r="N87" s="4"/>
     </row>
     <row r="88" spans="1:14" ht="55.2" customHeight="1">
-      <c r="A88" s="128"/>
+      <c r="A88" s="130"/>
       <c r="B88" s="21" t="s">
         <v>258</v>
       </c>
@@ -15884,7 +15884,7 @@
       <c r="N88" s="4"/>
     </row>
     <row r="89" spans="1:14" ht="55.8" customHeight="1">
-      <c r="A89" s="128"/>
+      <c r="A89" s="130"/>
       <c r="B89" s="21" t="s">
         <v>260</v>
       </c>
@@ -15913,7 +15913,7 @@
       <c r="N89" s="4"/>
     </row>
     <row r="90" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A90" s="128"/>
+      <c r="A90" s="130"/>
       <c r="B90" s="21" t="s">
         <v>265</v>
       </c>
@@ -15938,7 +15938,7 @@
       <c r="N90" s="4"/>
     </row>
     <row r="91" spans="1:14" ht="56.4" customHeight="1">
-      <c r="A91" s="128"/>
+      <c r="A91" s="130"/>
       <c r="B91" s="21" t="s">
         <v>269</v>
       </c>
@@ -15967,7 +15967,7 @@
       <c r="N91" s="4"/>
     </row>
     <row r="92" spans="1:14" ht="42" customHeight="1">
-      <c r="A92" s="133" t="s">
+      <c r="A92" s="129" t="s">
         <v>13</v>
       </c>
       <c r="B92" s="27" t="s">
@@ -15994,7 +15994,7 @@
       <c r="N92" s="4"/>
     </row>
     <row r="93" spans="1:14" s="63" customFormat="1" ht="27.6">
-      <c r="A93" s="128"/>
+      <c r="A93" s="130"/>
       <c r="B93" s="27" t="s">
         <v>160</v>
       </c>
@@ -16016,7 +16016,7 @@
       <c r="K93" s="64"/>
     </row>
     <row r="94" spans="1:14" ht="61.2" customHeight="1">
-      <c r="A94" s="128"/>
+      <c r="A94" s="130"/>
       <c r="B94" s="27" t="s">
         <v>586</v>
       </c>
@@ -16041,7 +16041,7 @@
       <c r="N94" s="2"/>
     </row>
     <row r="95" spans="1:14" ht="27.6">
-      <c r="A95" s="128"/>
+      <c r="A95" s="130"/>
       <c r="B95" s="27" t="s">
         <v>161</v>
       </c>
@@ -16066,7 +16066,7 @@
       <c r="N95" s="2"/>
     </row>
     <row r="96" spans="1:14" ht="27.6">
-      <c r="A96" s="128"/>
+      <c r="A96" s="130"/>
       <c r="B96" s="21" t="s">
         <v>155</v>
       </c>
@@ -16091,7 +16091,7 @@
       <c r="N96" s="2"/>
     </row>
     <row r="97" spans="1:14" ht="41.4">
-      <c r="A97" s="128"/>
+      <c r="A97" s="130"/>
       <c r="B97" s="21" t="s">
         <v>156</v>
       </c>
@@ -16116,7 +16116,7 @@
       <c r="N97" s="2"/>
     </row>
     <row r="98" spans="1:14" ht="41.4">
-      <c r="A98" s="128"/>
+      <c r="A98" s="130"/>
       <c r="B98" s="21" t="s">
         <v>158</v>
       </c>
@@ -16141,7 +16141,7 @@
       <c r="N98" s="2"/>
     </row>
     <row r="99" spans="1:14" ht="41.4">
-      <c r="A99" s="128"/>
+      <c r="A99" s="130"/>
       <c r="B99" s="27" t="s">
         <v>162</v>
       </c>
@@ -16166,7 +16166,7 @@
       <c r="N99" s="2"/>
     </row>
     <row r="100" spans="1:14" ht="41.4">
-      <c r="A100" s="128"/>
+      <c r="A100" s="130"/>
       <c r="B100" s="27" t="s">
         <v>164</v>
       </c>
@@ -16191,7 +16191,7 @@
       <c r="N100" s="2"/>
     </row>
     <row r="101" spans="1:14" ht="39" customHeight="1">
-      <c r="A101" s="128"/>
+      <c r="A101" s="130"/>
       <c r="B101" s="27" t="s">
         <v>587</v>
       </c>
@@ -16216,7 +16216,7 @@
       <c r="N101" s="2"/>
     </row>
     <row r="102" spans="1:14" ht="41.4">
-      <c r="A102" s="128"/>
+      <c r="A102" s="130"/>
       <c r="B102" s="27" t="s">
         <v>166</v>
       </c>
@@ -16241,7 +16241,7 @@
       <c r="N102" s="2"/>
     </row>
     <row r="103" spans="1:14" s="63" customFormat="1" ht="69.599999999999994" customHeight="1">
-      <c r="A103" s="128"/>
+      <c r="A103" s="130"/>
       <c r="B103" s="27" t="s">
         <v>168</v>
       </c>
@@ -16266,7 +16266,7 @@
       <c r="N103" s="65"/>
     </row>
     <row r="104" spans="1:14" ht="27.6">
-      <c r="A104" s="128"/>
+      <c r="A104" s="130"/>
       <c r="B104" s="21" t="s">
         <v>169</v>
       </c>
@@ -16291,7 +16291,7 @@
       <c r="N104" s="2"/>
     </row>
     <row r="105" spans="1:14" ht="55.2">
-      <c r="A105" s="128"/>
+      <c r="A105" s="130"/>
       <c r="B105" s="21" t="s">
         <v>171</v>
       </c>
@@ -16316,7 +16316,7 @@
       <c r="N105" s="2"/>
     </row>
     <row r="106" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A106" s="128"/>
+      <c r="A106" s="130"/>
       <c r="B106" s="27" t="s">
         <v>600</v>
       </c>
@@ -16341,7 +16341,7 @@
       <c r="N106" s="2"/>
     </row>
     <row r="107" spans="1:14" ht="55.2">
-      <c r="A107" s="128"/>
+      <c r="A107" s="130"/>
       <c r="B107" s="21" t="s">
         <v>173</v>
       </c>
@@ -16366,7 +16366,7 @@
       <c r="N107" s="2"/>
     </row>
     <row r="108" spans="1:14" ht="69">
-      <c r="A108" s="128"/>
+      <c r="A108" s="130"/>
       <c r="B108" s="27" t="s">
         <v>175</v>
       </c>
@@ -16391,7 +16391,7 @@
       <c r="N108" s="2"/>
     </row>
     <row r="109" spans="1:14" ht="61.8" customHeight="1">
-      <c r="A109" s="127" t="s">
+      <c r="A109" s="136" t="s">
         <v>14</v>
       </c>
       <c r="B109" s="21" t="s">
@@ -16418,7 +16418,7 @@
       <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" ht="60" customHeight="1">
-      <c r="A110" s="128"/>
+      <c r="A110" s="130"/>
       <c r="B110" s="21" t="s">
         <v>288</v>
       </c>
@@ -16447,7 +16447,7 @@
       <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" ht="63" customHeight="1">
-      <c r="A111" s="128"/>
+      <c r="A111" s="130"/>
       <c r="B111" s="21" t="s">
         <v>292</v>
       </c>
@@ -16472,7 +16472,7 @@
       <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" ht="74.400000000000006" customHeight="1">
-      <c r="A112" s="128"/>
+      <c r="A112" s="130"/>
       <c r="B112" s="21" t="s">
         <v>294</v>
       </c>
@@ -16501,7 +16501,7 @@
       <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" ht="59.4" customHeight="1">
-      <c r="A113" s="128"/>
+      <c r="A113" s="130"/>
       <c r="B113" s="21" t="s">
         <v>299</v>
       </c>
@@ -16526,7 +16526,7 @@
       <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" ht="41.4">
-      <c r="A114" s="128"/>
+      <c r="A114" s="130"/>
       <c r="B114" s="21" t="s">
         <v>300</v>
       </c>
@@ -16551,7 +16551,7 @@
       <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" ht="40.799999999999997" customHeight="1">
-      <c r="A115" s="128"/>
+      <c r="A115" s="130"/>
       <c r="B115" s="21" t="s">
         <v>302</v>
       </c>
@@ -16576,7 +16576,7 @@
       <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" ht="45.6" customHeight="1">
-      <c r="A116" s="128"/>
+      <c r="A116" s="130"/>
       <c r="B116" s="21" t="s">
         <v>304</v>
       </c>
@@ -16601,7 +16601,7 @@
       <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" ht="44.4" customHeight="1">
-      <c r="A117" s="128"/>
+      <c r="A117" s="130"/>
       <c r="B117" s="21" t="s">
         <v>306</v>
       </c>
@@ -16626,7 +16626,7 @@
       <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" ht="77.400000000000006" customHeight="1">
-      <c r="A118" s="128"/>
+      <c r="A118" s="130"/>
       <c r="B118" s="21" t="s">
         <v>308</v>
       </c>
@@ -16655,7 +16655,7 @@
       <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" ht="65.400000000000006" customHeight="1">
-      <c r="A119" s="128"/>
+      <c r="A119" s="130"/>
       <c r="B119" s="21" t="s">
         <v>312</v>
       </c>
@@ -16680,7 +16680,7 @@
       <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" ht="60.6" customHeight="1">
-      <c r="A120" s="128"/>
+      <c r="A120" s="130"/>
       <c r="B120" s="21" t="s">
         <v>314</v>
       </c>
@@ -16705,7 +16705,7 @@
       <c r="N120" s="4"/>
     </row>
     <row r="121" spans="1:14" ht="40.200000000000003" customHeight="1">
-      <c r="A121" s="128"/>
+      <c r="A121" s="130"/>
       <c r="B121" s="21" t="s">
         <v>316</v>
       </c>
@@ -16730,7 +16730,7 @@
       <c r="N121" s="4"/>
     </row>
     <row r="122" spans="1:14" ht="69">
-      <c r="A122" s="128"/>
+      <c r="A122" s="130"/>
       <c r="B122" s="21" t="s">
         <v>318</v>
       </c>
@@ -16755,7 +16755,7 @@
       <c r="N122" s="4"/>
     </row>
     <row r="123" spans="1:14" ht="60" customHeight="1">
-      <c r="A123" s="128"/>
+      <c r="A123" s="130"/>
       <c r="B123" s="21" t="s">
         <v>320</v>
       </c>
@@ -16780,7 +16780,7 @@
       <c r="N123" s="4"/>
     </row>
     <row r="124" spans="1:14" ht="69">
-      <c r="A124" s="128"/>
+      <c r="A124" s="130"/>
       <c r="B124" s="21" t="s">
         <v>322</v>
       </c>
@@ -16805,7 +16805,7 @@
       <c r="N124" s="4"/>
     </row>
     <row r="125" spans="1:14" ht="67.8" customHeight="1">
-      <c r="A125" s="128"/>
+      <c r="A125" s="130"/>
       <c r="B125" s="27" t="s">
         <v>324</v>
       </c>
@@ -19804,12 +19804,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="A3:A12"/>
-    <mergeCell ref="A13:A21"/>
-    <mergeCell ref="A92:A108"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A109:A125"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:C1"/>
@@ -19817,6 +19811,12 @@
     <mergeCell ref="A35:A45"/>
     <mergeCell ref="A46:A68"/>
     <mergeCell ref="A69:A91"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A13:A21"/>
+    <mergeCell ref="A92:A108"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:F1048576 C2">
@@ -19870,44 +19870,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="13.2">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="151" t="s">
         <v>368</v>
       </c>
-      <c r="B1" s="145" t="s">
+      <c r="B1" s="151" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="145" t="s">
+      <c r="C1" s="151" t="s">
         <v>367</v>
       </c>
-      <c r="D1" s="145" t="s">
+      <c r="D1" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="145" t="s">
+      <c r="E1" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="145" t="s">
+      <c r="F1" s="151" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="145" t="s">
+      <c r="G1" s="151" t="s">
         <v>835</v>
       </c>
-      <c r="H1" s="140" t="s">
+      <c r="H1" s="148" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="141"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="143" t="s">
+      <c r="I1" s="149"/>
+      <c r="J1" s="150"/>
+      <c r="K1" s="140" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="27.6">
-      <c r="A2" s="144"/>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
       <c r="H2" s="36" t="s">
         <v>21</v>
       </c>
@@ -19917,10 +19917,10 @@
       <c r="J2" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="144"/>
+      <c r="K2" s="146"/>
     </row>
     <row r="3" spans="1:11" ht="18" customHeight="1">
-      <c r="A3" s="149" t="s">
+      <c r="A3" s="144" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="38" t="s">
@@ -19953,7 +19953,7 @@
       <c r="K3" s="41"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A4" s="150"/>
+      <c r="A4" s="145"/>
       <c r="B4" s="38" t="s">
         <v>336</v>
       </c>
@@ -19984,7 +19984,7 @@
       <c r="K4" s="41"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A5" s="150"/>
+      <c r="A5" s="145"/>
       <c r="B5" s="38" t="s">
         <v>337</v>
       </c>
@@ -20015,7 +20015,7 @@
       <c r="K5" s="41"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A6" s="150"/>
+      <c r="A6" s="145"/>
       <c r="B6" s="38" t="s">
         <v>338</v>
       </c>
@@ -20046,7 +20046,7 @@
       <c r="K6" s="41"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A7" s="150"/>
+      <c r="A7" s="145"/>
       <c r="B7" s="38" t="s">
         <v>339</v>
       </c>
@@ -20077,7 +20077,7 @@
       <c r="K7" s="41"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A8" s="150"/>
+      <c r="A8" s="145"/>
       <c r="B8" s="38" t="s">
         <v>340</v>
       </c>
@@ -20108,7 +20108,7 @@
       <c r="K8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="15" customHeight="1">
-      <c r="A9" s="144"/>
+      <c r="A9" s="146"/>
       <c r="B9" s="38" t="s">
         <v>341</v>
       </c>
@@ -20139,7 +20139,7 @@
       <c r="K9" s="41"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A10" s="149" t="s">
+      <c r="A10" s="144" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -20172,7 +20172,7 @@
       <c r="K10" s="41"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A11" s="150"/>
+      <c r="A11" s="145"/>
       <c r="B11" s="38" t="s">
         <v>343</v>
       </c>
@@ -20203,7 +20203,7 @@
       <c r="K11" s="41"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A12" s="150"/>
+      <c r="A12" s="145"/>
       <c r="B12" s="38" t="s">
         <v>344</v>
       </c>
@@ -20234,7 +20234,7 @@
       <c r="K12" s="41"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A13" s="150"/>
+      <c r="A13" s="145"/>
       <c r="B13" s="38" t="s">
         <v>345</v>
       </c>
@@ -20265,7 +20265,7 @@
       <c r="K13" s="41"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A14" s="150"/>
+      <c r="A14" s="145"/>
       <c r="B14" s="38" t="s">
         <v>346</v>
       </c>
@@ -20296,7 +20296,7 @@
       <c r="K14" s="41"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A15" s="150"/>
+      <c r="A15" s="145"/>
       <c r="B15" s="38" t="s">
         <v>347</v>
       </c>
@@ -20327,7 +20327,7 @@
       <c r="K15" s="41"/>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A16" s="150"/>
+      <c r="A16" s="145"/>
       <c r="B16" s="38" t="s">
         <v>348</v>
       </c>
@@ -20358,7 +20358,7 @@
       <c r="K16" s="41"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A17" s="150"/>
+      <c r="A17" s="145"/>
       <c r="B17" s="38" t="s">
         <v>349</v>
       </c>
@@ -20391,7 +20391,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A18" s="150"/>
+      <c r="A18" s="145"/>
       <c r="B18" s="38" t="s">
         <v>436</v>
       </c>
@@ -20422,7 +20422,7 @@
       <c r="K18" s="41"/>
     </row>
     <row r="19" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A19" s="144"/>
+      <c r="A19" s="146"/>
       <c r="B19" s="38" t="s">
         <v>437</v>
       </c>
@@ -20453,7 +20453,7 @@
       <c r="K19" s="41"/>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A20" s="149" t="s">
+      <c r="A20" s="144" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="38" t="s">
@@ -20486,7 +20486,7 @@
       <c r="K20" s="41"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A21" s="150"/>
+      <c r="A21" s="145"/>
       <c r="B21" s="38" t="s">
         <v>351</v>
       </c>
@@ -20517,7 +20517,7 @@
       <c r="K21" s="41"/>
     </row>
     <row r="22" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A22" s="150"/>
+      <c r="A22" s="145"/>
       <c r="B22" s="38" t="s">
         <v>352</v>
       </c>
@@ -20550,7 +20550,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A23" s="150"/>
+      <c r="A23" s="145"/>
       <c r="B23" s="38" t="s">
         <v>353</v>
       </c>
@@ -20583,7 +20583,7 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A24" s="150"/>
+      <c r="A24" s="145"/>
       <c r="B24" s="38" t="s">
         <v>446</v>
       </c>
@@ -20614,7 +20614,7 @@
       <c r="K24" s="41"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A25" s="150"/>
+      <c r="A25" s="145"/>
       <c r="B25" s="38" t="s">
         <v>354</v>
       </c>
@@ -20645,7 +20645,7 @@
       <c r="K25" s="41"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A26" s="150"/>
+      <c r="A26" s="145"/>
       <c r="B26" s="38" t="s">
         <v>355</v>
       </c>
@@ -20676,7 +20676,7 @@
       <c r="K26" s="41"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A27" s="150"/>
+      <c r="A27" s="145"/>
       <c r="B27" s="38" t="s">
         <v>356</v>
       </c>
@@ -20709,7 +20709,7 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A28" s="150"/>
+      <c r="A28" s="145"/>
       <c r="B28" s="38" t="s">
         <v>357</v>
       </c>
@@ -20742,7 +20742,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A29" s="150"/>
+      <c r="A29" s="145"/>
       <c r="B29" s="38" t="s">
         <v>389</v>
       </c>
@@ -20773,7 +20773,7 @@
       <c r="K29" s="41"/>
     </row>
     <row r="30" spans="1:11" ht="15.75" customHeight="1">
-      <c r="A30" s="150"/>
+      <c r="A30" s="145"/>
       <c r="B30" s="38" t="s">
         <v>390</v>
       </c>
@@ -20804,7 +20804,7 @@
       <c r="K30" s="41"/>
     </row>
     <row r="31" spans="1:11" ht="85.8" customHeight="1">
-      <c r="A31" s="151" t="s">
+      <c r="A31" s="147" t="s">
         <v>11</v>
       </c>
       <c r="B31" s="38" t="s">
@@ -20837,7 +20837,7 @@
       <c r="K31" s="41"/>
     </row>
     <row r="32" spans="1:11" ht="55.2">
-      <c r="A32" s="150"/>
+      <c r="A32" s="145"/>
       <c r="B32" s="38" t="s">
         <v>451</v>
       </c>
@@ -20870,7 +20870,7 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="82.8">
-      <c r="A33" s="150"/>
+      <c r="A33" s="145"/>
       <c r="B33" s="38" t="s">
         <v>452</v>
       </c>
@@ -20903,7 +20903,7 @@
       </c>
     </row>
     <row r="34" spans="1:11" ht="96.6">
-      <c r="A34" s="150"/>
+      <c r="A34" s="145"/>
       <c r="B34" s="38" t="s">
         <v>453</v>
       </c>
@@ -20934,7 +20934,7 @@
       <c r="K34" s="41"/>
     </row>
     <row r="35" spans="1:11" ht="82.8">
-      <c r="A35" s="150"/>
+      <c r="A35" s="145"/>
       <c r="B35" s="38" t="s">
         <v>454</v>
       </c>
@@ -20967,7 +20967,7 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="69">
-      <c r="A36" s="150"/>
+      <c r="A36" s="145"/>
       <c r="B36" s="38" t="s">
         <v>455</v>
       </c>
@@ -20998,7 +20998,7 @@
       <c r="K36" s="41"/>
     </row>
     <row r="37" spans="1:11" ht="57" customHeight="1">
-      <c r="A37" s="150"/>
+      <c r="A37" s="145"/>
       <c r="B37" s="38" t="s">
         <v>456</v>
       </c>
@@ -21031,7 +21031,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="72" customHeight="1">
-      <c r="A38" s="150"/>
+      <c r="A38" s="145"/>
       <c r="B38" s="38" t="s">
         <v>473</v>
       </c>
@@ -21062,7 +21062,7 @@
       <c r="K38" s="41"/>
     </row>
     <row r="39" spans="1:11" ht="92.4">
-      <c r="A39" s="149" t="s">
+      <c r="A39" s="144" t="s">
         <v>12</v>
       </c>
       <c r="B39" s="38" t="s">
@@ -21095,7 +21095,7 @@
       <c r="K39" s="41"/>
     </row>
     <row r="40" spans="1:11" ht="110.4">
-      <c r="A40" s="150"/>
+      <c r="A40" s="145"/>
       <c r="B40" s="38" t="s">
         <v>482</v>
       </c>
@@ -21126,7 +21126,7 @@
       <c r="K40" s="41"/>
     </row>
     <row r="41" spans="1:11" ht="57.6" customHeight="1">
-      <c r="A41" s="150"/>
+      <c r="A41" s="145"/>
       <c r="B41" s="38" t="s">
         <v>483</v>
       </c>
@@ -21157,7 +21157,7 @@
       <c r="K41" s="41"/>
     </row>
     <row r="42" spans="1:11" ht="61.2" customHeight="1">
-      <c r="A42" s="150"/>
+      <c r="A42" s="145"/>
       <c r="B42" s="38" t="s">
         <v>484</v>
       </c>
@@ -21188,7 +21188,7 @@
       <c r="K42" s="41"/>
     </row>
     <row r="43" spans="1:11" ht="69" customHeight="1">
-      <c r="A43" s="150"/>
+      <c r="A43" s="145"/>
       <c r="B43" s="38" t="s">
         <v>485</v>
       </c>
@@ -21219,7 +21219,7 @@
       <c r="K43" s="41"/>
     </row>
     <row r="44" spans="1:11" ht="73.8" customHeight="1">
-      <c r="A44" s="150"/>
+      <c r="A44" s="145"/>
       <c r="B44" s="38" t="s">
         <v>486</v>
       </c>
@@ -21250,7 +21250,7 @@
       <c r="K44" s="41"/>
     </row>
     <row r="45" spans="1:11" ht="85.2" customHeight="1">
-      <c r="A45" s="150"/>
+      <c r="A45" s="145"/>
       <c r="B45" s="38" t="s">
         <v>487</v>
       </c>
@@ -21281,7 +21281,7 @@
       <c r="K45" s="41"/>
     </row>
     <row r="46" spans="1:11" ht="70.8" customHeight="1">
-      <c r="A46" s="150"/>
+      <c r="A46" s="145"/>
       <c r="B46" s="38" t="s">
         <v>488</v>
       </c>
@@ -21314,7 +21314,7 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="99" customHeight="1">
-      <c r="A47" s="150"/>
+      <c r="A47" s="145"/>
       <c r="B47" s="38" t="s">
         <v>510</v>
       </c>
@@ -21347,7 +21347,7 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="92.4" customHeight="1">
-      <c r="A48" s="150"/>
+      <c r="A48" s="145"/>
       <c r="B48" s="38" t="s">
         <v>513</v>
       </c>
@@ -21378,7 +21378,7 @@
       <c r="K48" s="41"/>
     </row>
     <row r="49" spans="1:11" ht="72" customHeight="1">
-      <c r="A49" s="144"/>
+      <c r="A49" s="146"/>
       <c r="B49" s="38" t="s">
         <v>514</v>
       </c>
@@ -21409,7 +21409,7 @@
       <c r="K49" s="41"/>
     </row>
     <row r="50" spans="1:11" ht="82.8">
-      <c r="A50" s="149" t="s">
+      <c r="A50" s="144" t="s">
         <v>208</v>
       </c>
       <c r="B50" s="38" t="s">
@@ -21442,7 +21442,7 @@
       <c r="K50" s="41"/>
     </row>
     <row r="51" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A51" s="150"/>
+      <c r="A51" s="145"/>
       <c r="B51" s="38" t="s">
         <v>522</v>
       </c>
@@ -21473,7 +21473,7 @@
       <c r="K51" s="41"/>
     </row>
     <row r="52" spans="1:11" ht="96.6">
-      <c r="A52" s="150"/>
+      <c r="A52" s="145"/>
       <c r="B52" s="38" t="s">
         <v>523</v>
       </c>
@@ -21504,7 +21504,7 @@
       <c r="K52" s="41"/>
     </row>
     <row r="53" spans="1:11" ht="82.2" customHeight="1">
-      <c r="A53" s="150"/>
+      <c r="A53" s="145"/>
       <c r="B53" s="38" t="s">
         <v>524</v>
       </c>
@@ -21535,7 +21535,7 @@
       <c r="K53" s="44"/>
     </row>
     <row r="54" spans="1:11" ht="82.8">
-      <c r="A54" s="150"/>
+      <c r="A54" s="145"/>
       <c r="B54" s="38" t="s">
         <v>525</v>
       </c>
@@ -21568,7 +21568,7 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="55.2">
-      <c r="A55" s="150"/>
+      <c r="A55" s="145"/>
       <c r="B55" s="38" t="s">
         <v>526</v>
       </c>
@@ -21601,7 +21601,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="41.4">
-      <c r="A56" s="150"/>
+      <c r="A56" s="145"/>
       <c r="B56" s="38" t="s">
         <v>527</v>
       </c>
@@ -21634,7 +21634,7 @@
       </c>
     </row>
     <row r="57" spans="1:11" ht="55.8">
-      <c r="A57" s="150"/>
+      <c r="A57" s="145"/>
       <c r="B57" s="38" t="s">
         <v>528</v>
       </c>
@@ -21667,7 +21667,7 @@
       </c>
     </row>
     <row r="58" spans="1:11" ht="82.8">
-      <c r="A58" s="150"/>
+      <c r="A58" s="145"/>
       <c r="B58" s="38" t="s">
         <v>529</v>
       </c>
@@ -21698,7 +21698,7 @@
       <c r="K58" s="41"/>
     </row>
     <row r="59" spans="1:11" ht="82.8">
-      <c r="A59" s="150"/>
+      <c r="A59" s="145"/>
       <c r="B59" s="38" t="s">
         <v>530</v>
       </c>
@@ -21731,7 +21731,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="55.2">
-      <c r="A60" s="150"/>
+      <c r="A60" s="145"/>
       <c r="B60" s="38" t="s">
         <v>531</v>
       </c>
@@ -21762,7 +21762,7 @@
       <c r="K60" s="41"/>
     </row>
     <row r="61" spans="1:11" ht="69">
-      <c r="A61" s="150"/>
+      <c r="A61" s="145"/>
       <c r="B61" s="38" t="s">
         <v>532</v>
       </c>
@@ -21795,7 +21795,7 @@
       </c>
     </row>
     <row r="62" spans="1:11" ht="69.599999999999994">
-      <c r="A62" s="150"/>
+      <c r="A62" s="145"/>
       <c r="B62" s="38" t="s">
         <v>533</v>
       </c>
@@ -21826,7 +21826,7 @@
       <c r="K62" s="44"/>
     </row>
     <row r="63" spans="1:11" ht="117.6" customHeight="1">
-      <c r="A63" s="150"/>
+      <c r="A63" s="145"/>
       <c r="B63" s="38" t="s">
         <v>534</v>
       </c>
@@ -21857,7 +21857,7 @@
       <c r="K63" s="41"/>
     </row>
     <row r="64" spans="1:11" ht="83.4">
-      <c r="A64" s="149" t="s">
+      <c r="A64" s="144" t="s">
         <v>13</v>
       </c>
       <c r="B64" s="38" t="s">
@@ -21890,7 +21890,7 @@
       <c r="K64" s="41"/>
     </row>
     <row r="65" spans="1:27" ht="69.599999999999994">
-      <c r="A65" s="150"/>
+      <c r="A65" s="145"/>
       <c r="B65" s="38" t="s">
         <v>574</v>
       </c>
@@ -21937,7 +21937,7 @@
       <c r="AA65" s="2"/>
     </row>
     <row r="66" spans="1:27" ht="83.4">
-      <c r="A66" s="150"/>
+      <c r="A66" s="145"/>
       <c r="B66" s="38" t="s">
         <v>575</v>
       </c>
@@ -21984,7 +21984,7 @@
       <c r="AA66" s="2"/>
     </row>
     <row r="67" spans="1:27" ht="104.4" customHeight="1">
-      <c r="A67" s="150"/>
+      <c r="A67" s="145"/>
       <c r="B67" s="38" t="s">
         <v>576</v>
       </c>
@@ -22031,7 +22031,7 @@
       <c r="AA67" s="2"/>
     </row>
     <row r="68" spans="1:27" ht="75" customHeight="1">
-      <c r="A68" s="150"/>
+      <c r="A68" s="145"/>
       <c r="B68" s="38" t="s">
         <v>577</v>
       </c>
@@ -22078,7 +22078,7 @@
       <c r="AA68" s="2"/>
     </row>
     <row r="69" spans="1:27" ht="83.4">
-      <c r="A69" s="150"/>
+      <c r="A69" s="145"/>
       <c r="B69" s="38" t="s">
         <v>578</v>
       </c>
@@ -22125,7 +22125,7 @@
       <c r="AA69" s="2"/>
     </row>
     <row r="70" spans="1:27" ht="42">
-      <c r="A70" s="150"/>
+      <c r="A70" s="145"/>
       <c r="B70" s="38" t="s">
         <v>579</v>
       </c>
@@ -22172,7 +22172,7 @@
       <c r="AA70" s="2"/>
     </row>
     <row r="71" spans="1:27" ht="78">
-      <c r="A71" s="150"/>
+      <c r="A71" s="145"/>
       <c r="B71" s="38" t="s">
         <v>580</v>
       </c>
@@ -22219,7 +22219,7 @@
       <c r="AA71" s="2"/>
     </row>
     <row r="72" spans="1:27" ht="78">
-      <c r="A72" s="150"/>
+      <c r="A72" s="145"/>
       <c r="B72" s="38" t="s">
         <v>581</v>
       </c>
@@ -22250,7 +22250,7 @@
       <c r="K72" s="41"/>
     </row>
     <row r="73" spans="1:27" ht="94.8" customHeight="1">
-      <c r="A73" s="143" t="s">
+      <c r="A73" s="140" t="s">
         <v>14</v>
       </c>
       <c r="B73" s="38" t="s">
@@ -22283,7 +22283,7 @@
       <c r="K73" s="41"/>
     </row>
     <row r="74" spans="1:27" ht="75">
-      <c r="A74" s="146"/>
+      <c r="A74" s="141"/>
       <c r="B74" s="38" t="s">
         <v>621</v>
       </c>
@@ -22316,7 +22316,7 @@
       </c>
     </row>
     <row r="75" spans="1:27" ht="75">
-      <c r="A75" s="146"/>
+      <c r="A75" s="141"/>
       <c r="B75" s="38" t="s">
         <v>622</v>
       </c>
@@ -22349,7 +22349,7 @@
       </c>
     </row>
     <row r="76" spans="1:27" ht="79.2" customHeight="1">
-      <c r="A76" s="146"/>
+      <c r="A76" s="141"/>
       <c r="B76" s="38" t="s">
         <v>623</v>
       </c>
@@ -22380,7 +22380,7 @@
       <c r="K76" s="41"/>
     </row>
     <row r="77" spans="1:27" ht="69" customHeight="1">
-      <c r="A77" s="146"/>
+      <c r="A77" s="141"/>
       <c r="B77" s="38" t="s">
         <v>633</v>
       </c>
@@ -22411,7 +22411,7 @@
       <c r="K77" s="41"/>
     </row>
     <row r="78" spans="1:27" ht="69" customHeight="1">
-      <c r="A78" s="146"/>
+      <c r="A78" s="141"/>
       <c r="B78" s="38" t="s">
         <v>637</v>
       </c>
@@ -22442,7 +22442,7 @@
       <c r="K78" s="41"/>
     </row>
     <row r="79" spans="1:27" ht="69" customHeight="1">
-      <c r="A79" s="146"/>
+      <c r="A79" s="141"/>
       <c r="B79" s="38" t="s">
         <v>641</v>
       </c>
@@ -22475,7 +22475,7 @@
       </c>
     </row>
     <row r="80" spans="1:27" ht="75" customHeight="1">
-      <c r="A80" s="146"/>
+      <c r="A80" s="141"/>
       <c r="B80" s="38" t="s">
         <v>645</v>
       </c>
@@ -22506,7 +22506,7 @@
       <c r="K80" s="41"/>
     </row>
     <row r="81" spans="1:11" ht="93" customHeight="1">
-      <c r="A81" s="146"/>
+      <c r="A81" s="141"/>
       <c r="B81" s="38" t="s">
         <v>649</v>
       </c>
@@ -22537,7 +22537,7 @@
       <c r="K81" s="41"/>
     </row>
     <row r="82" spans="1:11" ht="112.8" customHeight="1">
-      <c r="A82" s="146"/>
+      <c r="A82" s="141"/>
       <c r="B82" s="38" t="s">
         <v>653</v>
       </c>
@@ -22568,7 +22568,7 @@
       <c r="K82" s="41"/>
     </row>
     <row r="83" spans="1:11" ht="110.4" customHeight="1">
-      <c r="A83" s="146"/>
+      <c r="A83" s="141"/>
       <c r="B83" s="38" t="s">
         <v>657</v>
       </c>
@@ -22576,7 +22576,7 @@
         <v>658</v>
       </c>
       <c r="D83" s="43" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E83" s="51" t="s">
         <v>659</v>
@@ -22599,7 +22599,7 @@
       <c r="K83" s="41"/>
     </row>
     <row r="84" spans="1:11" ht="109.2" customHeight="1">
-      <c r="A84" s="146"/>
+      <c r="A84" s="141"/>
       <c r="B84" s="38" t="s">
         <v>661</v>
       </c>
@@ -22630,7 +22630,7 @@
       <c r="K84" s="41"/>
     </row>
     <row r="85" spans="1:11" ht="67.8" customHeight="1">
-      <c r="A85" s="146"/>
+      <c r="A85" s="141"/>
       <c r="B85" s="38" t="s">
         <v>665</v>
       </c>
@@ -22671,8 +22671,8 @@
     </row>
     <row r="88" spans="1:11" ht="13.2">
       <c r="A88" s="37"/>
-      <c r="B88" s="147"/>
-      <c r="C88" s="148"/>
+      <c r="B88" s="142"/>
+      <c r="C88" s="143"/>
       <c r="D88" s="10"/>
     </row>
     <row r="89" spans="1:11" ht="13.2">
@@ -25630,6 +25630,15 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A73:A85"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="A3:A9"/>
@@ -25639,15 +25648,6 @@
     <mergeCell ref="A39:A49"/>
     <mergeCell ref="A50:A63"/>
     <mergeCell ref="A64:A72"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="D1:D1048576">
@@ -25709,26 +25709,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.4" customHeight="1">
-      <c r="A1" s="154" t="s">
+      <c r="A1" s="152" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="71"/>
-      <c r="C1" s="154" t="s">
+      <c r="C1" s="152" t="s">
         <v>36</v>
       </c>
       <c r="D1" s="162" t="s">
         <v>704</v>
       </c>
-      <c r="E1" s="154" t="s">
+      <c r="E1" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="154" t="s">
+      <c r="F1" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="154" t="s">
+      <c r="G1" s="152" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="154" t="s">
+      <c r="H1" s="152" t="s">
         <v>41</v>
       </c>
       <c r="I1" s="156" t="s">
@@ -25738,16 +25738,16 @@
       <c r="K1" s="157"/>
     </row>
     <row r="2" spans="1:11" ht="42">
-      <c r="A2" s="155"/>
+      <c r="A2" s="153"/>
       <c r="B2" s="71" t="s">
         <v>705</v>
       </c>
-      <c r="C2" s="155"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="163"/>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
       <c r="I2" s="73" t="s">
         <v>46</v>
       </c>
@@ -26426,20 +26426,20 @@
       <c r="H22" s="160" t="s">
         <v>45</v>
       </c>
-      <c r="I22" s="152" t="s">
+      <c r="I22" s="154" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="153"/>
-      <c r="K22" s="153"/>
+      <c r="J22" s="155"/>
+      <c r="K22" s="155"/>
     </row>
     <row r="23" spans="1:11" ht="41.4">
-      <c r="A23" s="155"/>
+      <c r="A23" s="153"/>
       <c r="B23" s="89"/>
-      <c r="C23" s="155"/>
-      <c r="D23" s="155"/>
-      <c r="E23" s="155"/>
-      <c r="F23" s="155"/>
-      <c r="G23" s="155"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
       <c r="H23" s="161"/>
       <c r="I23" s="90" t="s">
         <v>46</v>
@@ -27611,6 +27611,7 @@
     <row r="1009" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="F1:F2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="H1:H2"/>
@@ -27627,7 +27628,6 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="D1:D1048576">
     <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Minor">
